--- a/NFLX.xlsx
+++ b/NFLX.xlsx
@@ -47,7 +47,7 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>3</xdr:colOff>
+                <xdr:colOff>2</xdr:colOff>
                 <xdr:row>27</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
@@ -55,7 +55,7 @@
                 <xdr:col>2</xdr:col>
                 <xdr:colOff>-1</xdr:colOff>
                 <xdr:row>30</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -109,13 +109,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>23</xdr:row>
-                <xdr:rowOff>3</xdr:rowOff>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>3</xdr:colOff>
+                <xdr:colOff>2</xdr:colOff>
                 <xdr:row>46</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -160,7 +160,7 @@
                 <xdr:col>28</xdr:col>
                 <xdr:colOff>1</xdr:colOff>
                 <xdr:row>19</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -185,15 +185,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>25</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>39</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>26</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>43</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -226,7 +226,7 @@
                 <xdr:col>29</xdr:col>
                 <xdr:colOff>1</xdr:colOff>
                 <xdr:row>109</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -251,13 +251,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>26</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>27</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -285,13 +285,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>27</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>28</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -326,7 +326,7 @@
                 <xdr:col>44</xdr:col>
                 <xdr:colOff>1</xdr:colOff>
                 <xdr:row>109</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -352,13 +352,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>41</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>42</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -385,15 +385,15 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>41</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>139</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>42</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>143</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -419,13 +419,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>42</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>43</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -452,13 +452,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>43</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
+                <xdr:colOff>3</xdr:colOff>
                 <xdr:row>0</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>44</xdr:col>
-                <xdr:colOff>6</xdr:colOff>
+                <xdr:colOff>4</xdr:colOff>
                 <xdr:row>4</xdr:row>
                 <xdr:rowOff>1</xdr:rowOff>
               </xdr:to>
@@ -1490,7 +1490,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1848,10 +1848,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1904,6 +1904,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="19" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2284,11 +2288,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="54681227"/>
-        <c:axId val="30884169"/>
+        <c:axId val="78693276"/>
+        <c:axId val="12033908"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54681227"/>
+        <c:axId val="78693276"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2321,7 +2325,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30884169"/>
+        <c:crossAx val="12033908"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2329,7 +2333,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30884169"/>
+        <c:axId val="12033908"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2371,7 +2375,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54681227"/>
+        <c:crossAx val="78693276"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2627,9 +2631,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>98640</xdr:colOff>
+      <xdr:colOff>99000</xdr:colOff>
       <xdr:row>149</xdr:row>
-      <xdr:rowOff>111960</xdr:rowOff>
+      <xdr:rowOff>112320</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2639,9 +2643,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="24943680" y="153360"/>
-          <a:ext cx="21600" cy="23303880"/>
+          <a:ext cx="21960" cy="23304240"/>
           <a:chOff x="24943680" y="153360"/>
-          <a:chExt cx="21600" cy="23303880"/>
+          <a:chExt cx="21960" cy="23304240"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -2652,7 +2656,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="24943680" y="153360"/>
-            <a:ext cx="21960" cy="23304240"/>
+            <a:ext cx="22320" cy="23304600"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -2677,9 +2681,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>58320</xdr:colOff>
+      <xdr:colOff>58680</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>66600</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2689,9 +2693,9 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="36494280" y="242280"/>
-          <a:ext cx="4320" cy="23006520"/>
+          <a:ext cx="4680" cy="23006880"/>
           <a:chOff x="36494280" y="242280"/>
-          <a:chExt cx="4320" cy="23006520"/>
+          <a:chExt cx="4680" cy="23006880"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp>
@@ -2702,7 +2706,7 @@
         <xdr:spPr>
           <a:xfrm flipH="1">
             <a:off x="36494280" y="242280"/>
-            <a:ext cx="4680" cy="23006880"/>
+            <a:ext cx="5040" cy="23007240"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -2727,9 +2731,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>40</xdr:col>
-      <xdr:colOff>145080</xdr:colOff>
+      <xdr:colOff>144720</xdr:colOff>
       <xdr:row>187</xdr:row>
-      <xdr:rowOff>88560</xdr:rowOff>
+      <xdr:rowOff>88200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2738,7 +2742,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="30827160" y="26226720"/>
-        <a:ext cx="5758200" cy="3238200"/>
+        <a:ext cx="5757840" cy="3237840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3065,7 +3069,7 @@
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">+(G3/(G3+G5))*B10+(G5/(G3+G5))*B11*(1-Model!AN52)</f>
-        <v>0.121301298536298</v>
+        <v>0.118728823881187</v>
       </c>
       <c r="G9" s="6"/>
       <c r="K9" s="9"/>
@@ -3092,8 +3096,8 @@
         <v>22</v>
       </c>
       <c r="B11" s="19" t="n">
-        <f aca="false">+0.045 + (B17/10)</f>
-        <v>0.123478260869565</v>
+        <f aca="false">+0.045 + (B17/100)</f>
+        <v>0.0528478260869565</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="1" t="s">
@@ -19105,7 +19109,7 @@
       </c>
       <c r="BD50" s="86" t="n">
         <f aca="false">+Main!E9</f>
-        <v>0.121301298536298</v>
+        <v>0.118728823881187</v>
       </c>
       <c r="BE50" s="6"/>
       <c r="BF50" s="6" t="s">
@@ -19365,7 +19369,7 @@
       </c>
       <c r="BD51" s="94" t="n">
         <f aca="false">NPV(BD50,AO40:DN40)+(Main!G4)-(Main!G5)</f>
-        <v>284891.075633423</v>
+        <v>294976.569431278</v>
       </c>
       <c r="BE51" s="65"/>
       <c r="BF51" s="65"/>
@@ -19629,7 +19633,7 @@
       </c>
       <c r="BD52" s="97" t="n">
         <f aca="false">BD51/Main!G2</f>
-        <v>68.4186366280641</v>
+        <v>70.8407403525693</v>
       </c>
       <c r="BE52" s="77"/>
       <c r="BF52" s="77"/>
@@ -19694,7 +19698,7 @@
       <c r="DM52" s="77"/>
       <c r="DN52" s="77"/>
     </row>
-    <row r="53" s="106" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="68"/>
       <c r="B53" s="101"/>
       <c r="C53" s="101"/>
@@ -19754,21 +19758,21 @@
       </c>
       <c r="BD53" s="103" t="n">
         <f aca="false">BD52/Main!G1-1</f>
-        <v>-0.122837991947896</v>
+        <v>-0.0917853800952653</v>
       </c>
       <c r="BE53" s="6"/>
       <c r="BF53" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="BG53" s="90" t="n">
+      <c r="BG53" s="104" t="n">
         <f aca="false">BG49/BG48</f>
         <v>0.0399005748501472</v>
       </c>
       <c r="BH53" s="98"/>
-      <c r="BI53" s="104" t="s">
+      <c r="BI53" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="BJ53" s="105" t="n">
+      <c r="BJ53" s="106" t="n">
         <f aca="false">+(-AA80-AA81+AA96+AA97)/SUM(X58:AA58)</f>
         <v>0.351807928163698</v>
       </c>
@@ -19860,11 +19864,11 @@
       <c r="AA54" s="70"/>
       <c r="AB54" s="70"/>
       <c r="AC54" s="70"/>
-      <c r="AD54" s="107"/>
-      <c r="AE54" s="107"/>
-      <c r="AF54" s="107"/>
-      <c r="AG54" s="107"/>
-      <c r="AH54" s="107"/>
+      <c r="AD54" s="108"/>
+      <c r="AE54" s="108"/>
+      <c r="AF54" s="108"/>
+      <c r="AG54" s="108"/>
+      <c r="AH54" s="108"/>
       <c r="AI54" s="70"/>
       <c r="AJ54" s="70"/>
       <c r="AK54" s="70"/>
@@ -19876,133 +19880,133 @@
       <c r="AQ54" s="70"/>
       <c r="AR54" s="70"/>
       <c r="AS54" s="70"/>
-      <c r="AX54" s="106"/>
+      <c r="AX54" s="107"/>
       <c r="BF54" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="BG54" s="90" t="n">
+      <c r="BG54" s="104" t="n">
         <v>0.04722</v>
       </c>
-      <c r="BH54" s="106"/>
-      <c r="BI54" s="108" t="s">
+      <c r="BH54" s="107"/>
+      <c r="BI54" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="BJ54" s="109" t="n">
+      <c r="BJ54" s="110" t="n">
         <v>0</v>
       </c>
-      <c r="BK54" s="106"/>
-      <c r="BL54" s="106"/>
-      <c r="BM54" s="106"/>
-      <c r="BN54" s="106"/>
-      <c r="BO54" s="106"/>
-      <c r="BP54" s="106"/>
-      <c r="BQ54" s="106"/>
-      <c r="BR54" s="106"/>
-      <c r="BS54" s="106"/>
-      <c r="BT54" s="106"/>
-      <c r="BU54" s="106"/>
-      <c r="BV54" s="106"/>
-      <c r="BW54" s="106"/>
-      <c r="BX54" s="106"/>
-      <c r="BY54" s="106"/>
-      <c r="BZ54" s="106"/>
-      <c r="CA54" s="106"/>
-      <c r="CB54" s="106"/>
-      <c r="CC54" s="106"/>
-      <c r="CD54" s="106"/>
-      <c r="CE54" s="106"/>
-      <c r="CF54" s="106"/>
-      <c r="CG54" s="106"/>
-      <c r="CH54" s="106"/>
-      <c r="CI54" s="106"/>
-      <c r="CJ54" s="106"/>
-      <c r="CK54" s="106"/>
-      <c r="CL54" s="106"/>
-      <c r="CM54" s="106"/>
-      <c r="CN54" s="106"/>
-      <c r="CO54" s="106"/>
-      <c r="CP54" s="106"/>
-      <c r="CQ54" s="106"/>
-      <c r="CR54" s="106"/>
-      <c r="CS54" s="106"/>
-      <c r="CT54" s="106"/>
-      <c r="CU54" s="106"/>
-      <c r="CV54" s="106"/>
-      <c r="CW54" s="106"/>
-      <c r="CX54" s="106"/>
-      <c r="CY54" s="106"/>
-      <c r="CZ54" s="106"/>
-      <c r="DA54" s="106"/>
-      <c r="DB54" s="106"/>
-      <c r="DC54" s="106"/>
-      <c r="DD54" s="106"/>
-      <c r="DE54" s="106"/>
-      <c r="DF54" s="106"/>
-      <c r="DG54" s="106"/>
-      <c r="DH54" s="106"/>
-      <c r="DI54" s="106"/>
-      <c r="DJ54" s="106"/>
-      <c r="DK54" s="106"/>
-      <c r="DL54" s="106"/>
-      <c r="DM54" s="106"/>
-      <c r="DN54" s="106"/>
-    </row>
-    <row r="55" s="113" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="110" t="s">
+      <c r="BK54" s="107"/>
+      <c r="BL54" s="107"/>
+      <c r="BM54" s="107"/>
+      <c r="BN54" s="107"/>
+      <c r="BO54" s="107"/>
+      <c r="BP54" s="107"/>
+      <c r="BQ54" s="107"/>
+      <c r="BR54" s="107"/>
+      <c r="BS54" s="107"/>
+      <c r="BT54" s="107"/>
+      <c r="BU54" s="107"/>
+      <c r="BV54" s="107"/>
+      <c r="BW54" s="107"/>
+      <c r="BX54" s="107"/>
+      <c r="BY54" s="107"/>
+      <c r="BZ54" s="107"/>
+      <c r="CA54" s="107"/>
+      <c r="CB54" s="107"/>
+      <c r="CC54" s="107"/>
+      <c r="CD54" s="107"/>
+      <c r="CE54" s="107"/>
+      <c r="CF54" s="107"/>
+      <c r="CG54" s="107"/>
+      <c r="CH54" s="107"/>
+      <c r="CI54" s="107"/>
+      <c r="CJ54" s="107"/>
+      <c r="CK54" s="107"/>
+      <c r="CL54" s="107"/>
+      <c r="CM54" s="107"/>
+      <c r="CN54" s="107"/>
+      <c r="CO54" s="107"/>
+      <c r="CP54" s="107"/>
+      <c r="CQ54" s="107"/>
+      <c r="CR54" s="107"/>
+      <c r="CS54" s="107"/>
+      <c r="CT54" s="107"/>
+      <c r="CU54" s="107"/>
+      <c r="CV54" s="107"/>
+      <c r="CW54" s="107"/>
+      <c r="CX54" s="107"/>
+      <c r="CY54" s="107"/>
+      <c r="CZ54" s="107"/>
+      <c r="DA54" s="107"/>
+      <c r="DB54" s="107"/>
+      <c r="DC54" s="107"/>
+      <c r="DD54" s="107"/>
+      <c r="DE54" s="107"/>
+      <c r="DF54" s="107"/>
+      <c r="DG54" s="107"/>
+      <c r="DH54" s="107"/>
+      <c r="DI54" s="107"/>
+      <c r="DJ54" s="107"/>
+      <c r="DK54" s="107"/>
+      <c r="DL54" s="107"/>
+      <c r="DM54" s="107"/>
+      <c r="DN54" s="107"/>
+    </row>
+    <row r="55" s="114" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="111" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="110"/>
-      <c r="C55" s="110"/>
-      <c r="D55" s="110"/>
-      <c r="E55" s="110"/>
-      <c r="F55" s="110"/>
-      <c r="G55" s="110"/>
-      <c r="H55" s="110"/>
-      <c r="I55" s="110"/>
-      <c r="J55" s="110"/>
-      <c r="K55" s="110"/>
-      <c r="L55" s="110"/>
-      <c r="M55" s="110"/>
-      <c r="N55" s="110"/>
-      <c r="O55" s="110"/>
-      <c r="P55" s="110"/>
-      <c r="Q55" s="110"/>
-      <c r="R55" s="110"/>
-      <c r="S55" s="110"/>
-      <c r="T55" s="110"/>
-      <c r="U55" s="110"/>
-      <c r="V55" s="110"/>
-      <c r="W55" s="110"/>
-      <c r="X55" s="110"/>
-      <c r="Y55" s="110"/>
-      <c r="Z55" s="111" t="n">
+      <c r="B55" s="111"/>
+      <c r="C55" s="111"/>
+      <c r="D55" s="111"/>
+      <c r="E55" s="111"/>
+      <c r="F55" s="111"/>
+      <c r="G55" s="111"/>
+      <c r="H55" s="111"/>
+      <c r="I55" s="111"/>
+      <c r="J55" s="111"/>
+      <c r="K55" s="111"/>
+      <c r="L55" s="111"/>
+      <c r="M55" s="111"/>
+      <c r="N55" s="111"/>
+      <c r="O55" s="111"/>
+      <c r="P55" s="111"/>
+      <c r="Q55" s="111"/>
+      <c r="R55" s="111"/>
+      <c r="S55" s="111"/>
+      <c r="T55" s="111"/>
+      <c r="U55" s="111"/>
+      <c r="V55" s="111"/>
+      <c r="W55" s="111"/>
+      <c r="X55" s="111"/>
+      <c r="Y55" s="111"/>
+      <c r="Z55" s="112" t="n">
         <f aca="false">+Z48*(Z16-Y16)</f>
         <v>103.373878157991</v>
       </c>
-      <c r="AA55" s="110"/>
-      <c r="AB55" s="110"/>
-      <c r="AC55" s="110"/>
+      <c r="AA55" s="111"/>
+      <c r="AB55" s="111"/>
+      <c r="AC55" s="111"/>
       <c r="AD55" s="84"/>
       <c r="AE55" s="84"/>
       <c r="AF55" s="84"/>
       <c r="AG55" s="84"/>
       <c r="AH55" s="84"/>
-      <c r="AI55" s="110"/>
-      <c r="AJ55" s="110"/>
-      <c r="AK55" s="110"/>
-      <c r="AL55" s="110"/>
-      <c r="AM55" s="110"/>
-      <c r="AN55" s="110"/>
-      <c r="AO55" s="110"/>
-      <c r="AP55" s="110"/>
-      <c r="AQ55" s="110"/>
-      <c r="AR55" s="110"/>
-      <c r="AS55" s="110"/>
+      <c r="AI55" s="111"/>
+      <c r="AJ55" s="111"/>
+      <c r="AK55" s="111"/>
+      <c r="AL55" s="111"/>
+      <c r="AM55" s="111"/>
+      <c r="AN55" s="111"/>
+      <c r="AO55" s="111"/>
+      <c r="AP55" s="111"/>
+      <c r="AQ55" s="111"/>
+      <c r="AR55" s="111"/>
+      <c r="AS55" s="111"/>
       <c r="AT55" s="84"/>
       <c r="AU55" s="84"/>
       <c r="AV55" s="84"/>
       <c r="AW55" s="84"/>
-      <c r="AX55" s="112"/>
+      <c r="AX55" s="113"/>
       <c r="AY55" s="84"/>
       <c r="AZ55" s="84"/>
       <c r="BA55" s="84"/>
@@ -20012,121 +20016,121 @@
       <c r="BE55" s="84"/>
       <c r="BF55" s="84"/>
       <c r="BG55" s="84"/>
-      <c r="BH55" s="112"/>
-      <c r="BI55" s="112"/>
-      <c r="BJ55" s="112"/>
-      <c r="BK55" s="112"/>
-      <c r="BL55" s="112"/>
-      <c r="BM55" s="112"/>
-      <c r="BN55" s="112"/>
-      <c r="BO55" s="112"/>
-      <c r="BP55" s="112"/>
-      <c r="BQ55" s="112"/>
-      <c r="BR55" s="112"/>
-      <c r="BS55" s="112"/>
-      <c r="BT55" s="112"/>
-      <c r="BU55" s="112"/>
-      <c r="BV55" s="112"/>
-      <c r="BW55" s="112"/>
-      <c r="BX55" s="112"/>
-      <c r="BY55" s="112"/>
-      <c r="BZ55" s="112"/>
-      <c r="CA55" s="112"/>
-      <c r="CB55" s="112"/>
-      <c r="CC55" s="112"/>
-      <c r="CD55" s="112"/>
-      <c r="CE55" s="112"/>
-      <c r="CF55" s="112"/>
-      <c r="CG55" s="112"/>
-      <c r="CH55" s="112"/>
-      <c r="CI55" s="112"/>
-      <c r="CJ55" s="112"/>
-      <c r="CK55" s="112"/>
-      <c r="CL55" s="112"/>
-      <c r="CM55" s="112"/>
-      <c r="CN55" s="112"/>
-      <c r="CO55" s="112"/>
-      <c r="CP55" s="112"/>
-      <c r="CQ55" s="112"/>
-      <c r="CR55" s="112"/>
-      <c r="CS55" s="112"/>
-      <c r="CT55" s="112"/>
-      <c r="CU55" s="112"/>
-      <c r="CV55" s="112"/>
-      <c r="CW55" s="112"/>
-      <c r="CX55" s="112"/>
-      <c r="CY55" s="112"/>
-      <c r="CZ55" s="112"/>
-      <c r="DA55" s="112"/>
-      <c r="DB55" s="112"/>
-      <c r="DC55" s="112"/>
-      <c r="DD55" s="112"/>
-      <c r="DE55" s="112"/>
-      <c r="DF55" s="112"/>
-      <c r="DG55" s="112"/>
-      <c r="DH55" s="112"/>
-      <c r="DI55" s="112"/>
-      <c r="DJ55" s="112"/>
-      <c r="DK55" s="112"/>
-      <c r="DL55" s="112"/>
-      <c r="DM55" s="112"/>
-      <c r="DN55" s="112"/>
+      <c r="BH55" s="113"/>
+      <c r="BI55" s="113"/>
+      <c r="BJ55" s="113"/>
+      <c r="BK55" s="113"/>
+      <c r="BL55" s="113"/>
+      <c r="BM55" s="113"/>
+      <c r="BN55" s="113"/>
+      <c r="BO55" s="113"/>
+      <c r="BP55" s="113"/>
+      <c r="BQ55" s="113"/>
+      <c r="BR55" s="113"/>
+      <c r="BS55" s="113"/>
+      <c r="BT55" s="113"/>
+      <c r="BU55" s="113"/>
+      <c r="BV55" s="113"/>
+      <c r="BW55" s="113"/>
+      <c r="BX55" s="113"/>
+      <c r="BY55" s="113"/>
+      <c r="BZ55" s="113"/>
+      <c r="CA55" s="113"/>
+      <c r="CB55" s="113"/>
+      <c r="CC55" s="113"/>
+      <c r="CD55" s="113"/>
+      <c r="CE55" s="113"/>
+      <c r="CF55" s="113"/>
+      <c r="CG55" s="113"/>
+      <c r="CH55" s="113"/>
+      <c r="CI55" s="113"/>
+      <c r="CJ55" s="113"/>
+      <c r="CK55" s="113"/>
+      <c r="CL55" s="113"/>
+      <c r="CM55" s="113"/>
+      <c r="CN55" s="113"/>
+      <c r="CO55" s="113"/>
+      <c r="CP55" s="113"/>
+      <c r="CQ55" s="113"/>
+      <c r="CR55" s="113"/>
+      <c r="CS55" s="113"/>
+      <c r="CT55" s="113"/>
+      <c r="CU55" s="113"/>
+      <c r="CV55" s="113"/>
+      <c r="CW55" s="113"/>
+      <c r="CX55" s="113"/>
+      <c r="CY55" s="113"/>
+      <c r="CZ55" s="113"/>
+      <c r="DA55" s="113"/>
+      <c r="DB55" s="113"/>
+      <c r="DC55" s="113"/>
+      <c r="DD55" s="113"/>
+      <c r="DE55" s="113"/>
+      <c r="DF55" s="113"/>
+      <c r="DG55" s="113"/>
+      <c r="DH55" s="113"/>
+      <c r="DI55" s="113"/>
+      <c r="DJ55" s="113"/>
+      <c r="DK55" s="113"/>
+      <c r="DL55" s="113"/>
+      <c r="DM55" s="113"/>
+      <c r="DN55" s="113"/>
       <c r="DO55" s="42"/>
     </row>
-    <row r="56" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="110"/>
-      <c r="B56" s="110"/>
-      <c r="C56" s="110"/>
-      <c r="D56" s="110"/>
-      <c r="E56" s="110"/>
-      <c r="F56" s="110"/>
-      <c r="G56" s="110"/>
-      <c r="H56" s="110"/>
-      <c r="I56" s="110"/>
-      <c r="J56" s="110"/>
-      <c r="K56" s="110"/>
-      <c r="L56" s="110"/>
-      <c r="M56" s="110"/>
-      <c r="N56" s="110"/>
-      <c r="O56" s="110"/>
-      <c r="P56" s="110"/>
-      <c r="Q56" s="110"/>
-      <c r="R56" s="110"/>
-      <c r="S56" s="110"/>
-      <c r="T56" s="110"/>
-      <c r="U56" s="110"/>
-      <c r="V56" s="110"/>
-      <c r="W56" s="110"/>
-      <c r="X56" s="110"/>
-      <c r="Y56" s="110"/>
-      <c r="Z56" s="110" t="n">
+    <row r="56" s="108" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="111"/>
+      <c r="B56" s="111"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="111"/>
+      <c r="N56" s="111"/>
+      <c r="O56" s="111"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="111"/>
+      <c r="S56" s="111"/>
+      <c r="T56" s="111"/>
+      <c r="U56" s="111"/>
+      <c r="V56" s="111"/>
+      <c r="W56" s="111"/>
+      <c r="X56" s="111"/>
+      <c r="Y56" s="111"/>
+      <c r="Z56" s="111" t="n">
         <f aca="false">+Y24/(Z55*12)</f>
         <v>0.897531707106236</v>
       </c>
-      <c r="AA56" s="110"/>
-      <c r="AB56" s="110"/>
-      <c r="AC56" s="110"/>
+      <c r="AA56" s="111"/>
+      <c r="AB56" s="111"/>
+      <c r="AC56" s="111"/>
       <c r="AD56" s="84"/>
       <c r="AE56" s="84"/>
       <c r="AF56" s="84"/>
       <c r="AG56" s="84"/>
       <c r="AH56" s="84"/>
-      <c r="AI56" s="110"/>
-      <c r="AJ56" s="110"/>
-      <c r="AK56" s="110"/>
-      <c r="AL56" s="110"/>
-      <c r="AM56" s="110"/>
-      <c r="AN56" s="110"/>
-      <c r="AO56" s="110"/>
-      <c r="AP56" s="110"/>
-      <c r="AQ56" s="110"/>
-      <c r="AR56" s="110"/>
-      <c r="AS56" s="110"/>
+      <c r="AI56" s="111"/>
+      <c r="AJ56" s="111"/>
+      <c r="AK56" s="111"/>
+      <c r="AL56" s="111"/>
+      <c r="AM56" s="111"/>
+      <c r="AN56" s="111"/>
+      <c r="AO56" s="111"/>
+      <c r="AP56" s="111"/>
+      <c r="AQ56" s="111"/>
+      <c r="AR56" s="111"/>
+      <c r="AS56" s="111"/>
       <c r="AT56" s="84"/>
       <c r="AU56" s="84"/>
       <c r="AV56" s="84"/>
       <c r="AW56" s="84"/>
-      <c r="AX56" s="112"/>
+      <c r="AX56" s="113"/>
       <c r="AY56" s="84"/>
       <c r="AZ56" s="84"/>
       <c r="BA56" s="84"/>
@@ -20136,68 +20140,68 @@
       <c r="BE56" s="84"/>
       <c r="BF56" s="84"/>
       <c r="BG56" s="84"/>
-      <c r="BH56" s="112"/>
-      <c r="BI56" s="112"/>
-      <c r="BJ56" s="112"/>
-      <c r="BK56" s="112"/>
-      <c r="BL56" s="112"/>
-      <c r="BM56" s="112"/>
-      <c r="BN56" s="112"/>
-      <c r="BO56" s="112"/>
-      <c r="BP56" s="112"/>
-      <c r="BQ56" s="112"/>
-      <c r="BR56" s="112"/>
-      <c r="BS56" s="112"/>
-      <c r="BT56" s="112"/>
-      <c r="BU56" s="112"/>
-      <c r="BV56" s="112"/>
-      <c r="BW56" s="112"/>
-      <c r="BX56" s="112"/>
-      <c r="BY56" s="112"/>
-      <c r="BZ56" s="112"/>
-      <c r="CA56" s="112"/>
-      <c r="CB56" s="112"/>
-      <c r="CC56" s="112"/>
-      <c r="CD56" s="112"/>
-      <c r="CE56" s="112"/>
-      <c r="CF56" s="112"/>
-      <c r="CG56" s="112"/>
-      <c r="CH56" s="112"/>
-      <c r="CI56" s="112"/>
-      <c r="CJ56" s="112"/>
-      <c r="CK56" s="112"/>
-      <c r="CL56" s="112"/>
-      <c r="CM56" s="112"/>
-      <c r="CN56" s="112"/>
-      <c r="CO56" s="112"/>
-      <c r="CP56" s="112"/>
-      <c r="CQ56" s="112"/>
-      <c r="CR56" s="112"/>
-      <c r="CS56" s="112"/>
-      <c r="CT56" s="112"/>
-      <c r="CU56" s="112"/>
-      <c r="CV56" s="112"/>
-      <c r="CW56" s="112"/>
-      <c r="CX56" s="112"/>
-      <c r="CY56" s="112"/>
-      <c r="CZ56" s="112"/>
-      <c r="DA56" s="112"/>
-      <c r="DB56" s="112"/>
-      <c r="DC56" s="112"/>
-      <c r="DD56" s="112"/>
-      <c r="DE56" s="112"/>
-      <c r="DF56" s="112"/>
-      <c r="DG56" s="112"/>
-      <c r="DH56" s="112"/>
-      <c r="DI56" s="112"/>
-      <c r="DJ56" s="112"/>
-      <c r="DK56" s="112"/>
-      <c r="DL56" s="112"/>
-      <c r="DM56" s="112"/>
-      <c r="DN56" s="112"/>
+      <c r="BH56" s="113"/>
+      <c r="BI56" s="113"/>
+      <c r="BJ56" s="113"/>
+      <c r="BK56" s="113"/>
+      <c r="BL56" s="113"/>
+      <c r="BM56" s="113"/>
+      <c r="BN56" s="113"/>
+      <c r="BO56" s="113"/>
+      <c r="BP56" s="113"/>
+      <c r="BQ56" s="113"/>
+      <c r="BR56" s="113"/>
+      <c r="BS56" s="113"/>
+      <c r="BT56" s="113"/>
+      <c r="BU56" s="113"/>
+      <c r="BV56" s="113"/>
+      <c r="BW56" s="113"/>
+      <c r="BX56" s="113"/>
+      <c r="BY56" s="113"/>
+      <c r="BZ56" s="113"/>
+      <c r="CA56" s="113"/>
+      <c r="CB56" s="113"/>
+      <c r="CC56" s="113"/>
+      <c r="CD56" s="113"/>
+      <c r="CE56" s="113"/>
+      <c r="CF56" s="113"/>
+      <c r="CG56" s="113"/>
+      <c r="CH56" s="113"/>
+      <c r="CI56" s="113"/>
+      <c r="CJ56" s="113"/>
+      <c r="CK56" s="113"/>
+      <c r="CL56" s="113"/>
+      <c r="CM56" s="113"/>
+      <c r="CN56" s="113"/>
+      <c r="CO56" s="113"/>
+      <c r="CP56" s="113"/>
+      <c r="CQ56" s="113"/>
+      <c r="CR56" s="113"/>
+      <c r="CS56" s="113"/>
+      <c r="CT56" s="113"/>
+      <c r="CU56" s="113"/>
+      <c r="CV56" s="113"/>
+      <c r="CW56" s="113"/>
+      <c r="CX56" s="113"/>
+      <c r="CY56" s="113"/>
+      <c r="CZ56" s="113"/>
+      <c r="DA56" s="113"/>
+      <c r="DB56" s="113"/>
+      <c r="DC56" s="113"/>
+      <c r="DD56" s="113"/>
+      <c r="DE56" s="113"/>
+      <c r="DF56" s="113"/>
+      <c r="DG56" s="113"/>
+      <c r="DH56" s="113"/>
+      <c r="DI56" s="113"/>
+      <c r="DJ56" s="113"/>
+      <c r="DK56" s="113"/>
+      <c r="DL56" s="113"/>
+      <c r="DM56" s="113"/>
+      <c r="DN56" s="113"/>
       <c r="DO56" s="42"/>
     </row>
-    <row r="57" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" s="108" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="36"/>
       <c r="B57" s="70"/>
       <c r="C57" s="70"/>
@@ -20242,7 +20246,7 @@
       <c r="AU57" s="6"/>
       <c r="AV57" s="6"/>
       <c r="AW57" s="6"/>
-      <c r="AX57" s="106"/>
+      <c r="AX57" s="107"/>
       <c r="AY57" s="6"/>
       <c r="AZ57" s="6"/>
       <c r="BA57" s="6"/>
@@ -20251,69 +20255,69 @@
       <c r="BD57" s="6"/>
       <c r="BE57" s="6"/>
       <c r="BF57" s="6"/>
-      <c r="BG57" s="90"/>
-      <c r="BH57" s="106"/>
-      <c r="BI57" s="106"/>
-      <c r="BJ57" s="106"/>
-      <c r="BK57" s="106"/>
-      <c r="BL57" s="106"/>
-      <c r="BM57" s="106"/>
-      <c r="BN57" s="106"/>
-      <c r="BO57" s="106"/>
-      <c r="BP57" s="106"/>
-      <c r="BQ57" s="106"/>
-      <c r="BR57" s="106"/>
-      <c r="BS57" s="106"/>
-      <c r="BT57" s="106"/>
-      <c r="BU57" s="106"/>
-      <c r="BV57" s="106"/>
-      <c r="BW57" s="106"/>
-      <c r="BX57" s="106"/>
-      <c r="BY57" s="106"/>
-      <c r="BZ57" s="106"/>
-      <c r="CA57" s="106"/>
-      <c r="CB57" s="106"/>
-      <c r="CC57" s="106"/>
-      <c r="CD57" s="106"/>
-      <c r="CE57" s="106"/>
-      <c r="CF57" s="106"/>
-      <c r="CG57" s="106"/>
-      <c r="CH57" s="106"/>
-      <c r="CI57" s="106"/>
-      <c r="CJ57" s="106"/>
-      <c r="CK57" s="106"/>
-      <c r="CL57" s="106"/>
-      <c r="CM57" s="106"/>
-      <c r="CN57" s="106"/>
-      <c r="CO57" s="106"/>
-      <c r="CP57" s="106"/>
-      <c r="CQ57" s="106"/>
-      <c r="CR57" s="106"/>
-      <c r="CS57" s="106"/>
-      <c r="CT57" s="106"/>
-      <c r="CU57" s="106"/>
-      <c r="CV57" s="106"/>
-      <c r="CW57" s="106"/>
-      <c r="CX57" s="106"/>
-      <c r="CY57" s="106"/>
-      <c r="CZ57" s="106"/>
-      <c r="DA57" s="106"/>
-      <c r="DB57" s="106"/>
-      <c r="DC57" s="106"/>
-      <c r="DD57" s="106"/>
-      <c r="DE57" s="106"/>
-      <c r="DF57" s="106"/>
-      <c r="DG57" s="106"/>
-      <c r="DH57" s="106"/>
-      <c r="DI57" s="106"/>
-      <c r="DJ57" s="106"/>
-      <c r="DK57" s="106"/>
-      <c r="DL57" s="106"/>
-      <c r="DM57" s="106"/>
-      <c r="DN57" s="106"/>
+      <c r="BG57" s="104"/>
+      <c r="BH57" s="107"/>
+      <c r="BI57" s="107"/>
+      <c r="BJ57" s="107"/>
+      <c r="BK57" s="107"/>
+      <c r="BL57" s="107"/>
+      <c r="BM57" s="107"/>
+      <c r="BN57" s="107"/>
+      <c r="BO57" s="107"/>
+      <c r="BP57" s="107"/>
+      <c r="BQ57" s="107"/>
+      <c r="BR57" s="107"/>
+      <c r="BS57" s="107"/>
+      <c r="BT57" s="107"/>
+      <c r="BU57" s="107"/>
+      <c r="BV57" s="107"/>
+      <c r="BW57" s="107"/>
+      <c r="BX57" s="107"/>
+      <c r="BY57" s="107"/>
+      <c r="BZ57" s="107"/>
+      <c r="CA57" s="107"/>
+      <c r="CB57" s="107"/>
+      <c r="CC57" s="107"/>
+      <c r="CD57" s="107"/>
+      <c r="CE57" s="107"/>
+      <c r="CF57" s="107"/>
+      <c r="CG57" s="107"/>
+      <c r="CH57" s="107"/>
+      <c r="CI57" s="107"/>
+      <c r="CJ57" s="107"/>
+      <c r="CK57" s="107"/>
+      <c r="CL57" s="107"/>
+      <c r="CM57" s="107"/>
+      <c r="CN57" s="107"/>
+      <c r="CO57" s="107"/>
+      <c r="CP57" s="107"/>
+      <c r="CQ57" s="107"/>
+      <c r="CR57" s="107"/>
+      <c r="CS57" s="107"/>
+      <c r="CT57" s="107"/>
+      <c r="CU57" s="107"/>
+      <c r="CV57" s="107"/>
+      <c r="CW57" s="107"/>
+      <c r="CX57" s="107"/>
+      <c r="CY57" s="107"/>
+      <c r="CZ57" s="107"/>
+      <c r="DA57" s="107"/>
+      <c r="DB57" s="107"/>
+      <c r="DC57" s="107"/>
+      <c r="DD57" s="107"/>
+      <c r="DE57" s="107"/>
+      <c r="DF57" s="107"/>
+      <c r="DG57" s="107"/>
+      <c r="DH57" s="107"/>
+      <c r="DI57" s="107"/>
+      <c r="DJ57" s="107"/>
+      <c r="DK57" s="107"/>
+      <c r="DL57" s="107"/>
+      <c r="DM57" s="107"/>
+      <c r="DN57" s="107"/>
       <c r="DO57" s="42"/>
     </row>
-    <row r="58" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" s="108" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="98" t="s">
         <v>124</v>
       </c>
@@ -20690,163 +20694,163 @@
       </c>
       <c r="DO59" s="42"/>
     </row>
-    <row r="60" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="90" t="s">
+    <row r="60" s="108" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="104" t="s">
         <v>125</v>
       </c>
-      <c r="F60" s="107" t="n">
+      <c r="F60" s="108" t="n">
         <f aca="false">(F30-B30)/(F16-B16)</f>
         <v>0.717699316070604</v>
       </c>
-      <c r="G60" s="107" t="n">
+      <c r="G60" s="108" t="n">
         <f aca="false">(G30-C30)/(G16-C16)</f>
         <v>0.410332095682574</v>
       </c>
-      <c r="H60" s="107" t="n">
+      <c r="H60" s="108" t="n">
         <f aca="false">(H30-D30)/(H16-D16)</f>
         <v>0.420397179924692</v>
       </c>
-      <c r="I60" s="107" t="n">
+      <c r="I60" s="108" t="n">
         <f aca="false">(I30-E30)/(I16-E16)</f>
         <v>-0.301717174970535</v>
       </c>
-      <c r="J60" s="107" t="n">
+      <c r="J60" s="108" t="n">
         <f aca="false">(J30-F30)/(J16-F16)</f>
         <v>0.016736181574163</v>
       </c>
-      <c r="K60" s="107" t="n">
+      <c r="K60" s="108" t="n">
         <f aca="false">(K30-G30)/(K16-G16)</f>
         <v>-0.428802560644527</v>
       </c>
-      <c r="L60" s="107" t="n">
+      <c r="L60" s="108" t="n">
         <f aca="false">(L30-H30)/(L16-H16)</f>
         <v>-0.502932440957746</v>
       </c>
-      <c r="M60" s="107" t="n">
+      <c r="M60" s="108" t="n">
         <f aca="false">(M30-I30)/(M16-I16)</f>
         <v>-0.581675381336467</v>
       </c>
-      <c r="N60" s="107" t="n">
+      <c r="N60" s="108" t="n">
         <f aca="false">(N30-J30)/(N16-J16)</f>
         <v>-0.873376493081837</v>
       </c>
-      <c r="O60" s="107" t="n">
+      <c r="O60" s="108" t="n">
         <f aca="false">(O30-K30)/(O16-K16)</f>
         <v>1.15486283990027</v>
       </c>
-      <c r="P60" s="107" t="n">
+      <c r="P60" s="108" t="n">
         <f aca="false">(P30-L30)/(P16-L16)</f>
         <v>0.624980619781886</v>
       </c>
-      <c r="Q60" s="107" t="n">
+      <c r="Q60" s="108" t="n">
         <f aca="false">(Q30-M30)/(Q16-M16)</f>
         <v>0.976440633306774</v>
       </c>
-      <c r="R60" s="107" t="n">
+      <c r="R60" s="108" t="n">
         <f aca="false">(R30-N30)/(R16-N16)</f>
         <v>0.759542839875237</v>
       </c>
-      <c r="S60" s="107" t="n">
+      <c r="S60" s="108" t="n">
         <f aca="false">(S30-O30)/(S16-O16)</f>
         <v>0.532806472145756</v>
       </c>
-      <c r="T60" s="107" t="n">
+      <c r="T60" s="108" t="n">
         <f aca="false">(T30-P30)/(T16-P16)</f>
         <v>0.773792567405276</v>
       </c>
-      <c r="U60" s="107" t="n">
+      <c r="U60" s="108" t="n">
         <f aca="false">(U30-Q30)/(U16-Q16)</f>
         <v>0.542762499701764</v>
       </c>
-      <c r="V60" s="107" t="n">
+      <c r="V60" s="108" t="n">
         <f aca="false">(V30-R30)/(V16-R16)</f>
         <v>0.647916170141623</v>
       </c>
-      <c r="W60" s="107" t="n">
+      <c r="W60" s="108" t="n">
         <f aca="false">(W30-S30)/(W16-S16)</f>
         <v>0.800005015321552</v>
       </c>
-      <c r="X60" s="107" t="n">
+      <c r="X60" s="108" t="n">
         <f aca="false">(X30-T30)/(X16-T16)</f>
         <v>0.201066292421859</v>
       </c>
-      <c r="Y60" s="107" t="n">
+      <c r="Y60" s="108" t="n">
         <f aca="false">(Y30-U30)/(Y16-U16)</f>
         <v>0.377893056696885</v>
       </c>
-      <c r="Z60" s="107" t="n">
+      <c r="Z60" s="108" t="n">
         <f aca="false">(Z30-V30)/(Z16-V16)</f>
         <v>0.330444786076552</v>
       </c>
-      <c r="AA60" s="107" t="n">
+      <c r="AA60" s="108" t="n">
         <f aca="false">(AA30-W30)/(AA16-W16)</f>
         <v>0.281310162284882</v>
       </c>
-      <c r="AJ60" s="107" t="n">
+      <c r="AJ60" s="108" t="n">
         <f aca="false">(AJ30-AI30)/(AJ16-AI16)</f>
         <v>0.342257046760907</v>
       </c>
-      <c r="AK60" s="107" t="n">
+      <c r="AK60" s="108" t="n">
         <f aca="false">(AK30-AJ30)/(AK16-AJ16)</f>
         <v>-0.292892404422266</v>
       </c>
-      <c r="AL60" s="107" t="n">
+      <c r="AL60" s="108" t="n">
         <f aca="false">(AL30-AK30)/(AL16-AK16)</f>
         <v>0.626820785932931</v>
       </c>
-      <c r="AM60" s="107" t="n">
+      <c r="AM60" s="108" t="n">
         <f aca="false">(AM30-AL30)/(AM16-AL16)</f>
         <v>0.656280198269686</v>
       </c>
-      <c r="AN60" s="107" t="n">
+      <c r="AN60" s="108" t="n">
         <f aca="false">(AN30-AM30)/(AN16-AM16)</f>
         <v>0.470521507924923</v>
       </c>
-      <c r="AO60" s="107" t="n">
+      <c r="AO60" s="108" t="n">
         <f aca="false">(AO30-AN30)/(AO16-AN16)</f>
         <v>0.461411025444239</v>
       </c>
-      <c r="AP60" s="107" t="n">
+      <c r="AP60" s="108" t="n">
         <f aca="false">(AP30-AO30)/(AP16-AO16)</f>
         <v>0.439489051094891</v>
       </c>
-      <c r="AQ60" s="107" t="n">
+      <c r="AQ60" s="108" t="n">
         <f aca="false">(AQ30-AP30)/(AQ16-AP16)</f>
         <v>0.416923472002848</v>
       </c>
-      <c r="AR60" s="107" t="n">
+      <c r="AR60" s="108" t="n">
         <f aca="false">(AR30-AQ30)/(AR16-AQ16)</f>
         <v>0.383461538461539</v>
       </c>
-      <c r="AS60" s="107" t="n">
+      <c r="AS60" s="108" t="n">
         <f aca="false">(AS30-AR30)/(AS16-AR16)</f>
         <v>0.438333891981994</v>
       </c>
-      <c r="AT60" s="107" t="n">
+      <c r="AT60" s="108" t="n">
         <f aca="false">(AT30-AS30)/(AT16-AS16)</f>
         <v>0.401666666666667</v>
       </c>
-      <c r="AU60" s="107" t="n">
+      <c r="AU60" s="108" t="n">
         <f aca="false">(AU30-AT30)/(AU16-AT16)</f>
         <v>0.410454545454546</v>
       </c>
-      <c r="AV60" s="107" t="n">
+      <c r="AV60" s="108" t="n">
         <f aca="false">(AV30-AU30)/(AV16-AU16)</f>
         <v>0.415454545454545</v>
       </c>
-      <c r="AW60" s="107" t="n">
+      <c r="AW60" s="108" t="n">
         <f aca="false">(AW30-AV30)/(AW16-AV16)</f>
         <v>0.420454939771381</v>
       </c>
-      <c r="AX60" s="107" t="n">
+      <c r="AX60" s="108" t="n">
         <f aca="false">(AX30-AW30)/(AX16-AW16)</f>
         <v>0.425454900694938</v>
       </c>
-      <c r="AY60" s="107" t="n">
+      <c r="AY60" s="108" t="n">
         <f aca="false">(AY30-AX30)/(AY16-AX16)</f>
         <v>0.38</v>
       </c>
-      <c r="AZ60" s="113"/>
+      <c r="AZ60" s="114"/>
       <c r="BA60" s="6"/>
       <c r="BB60" s="6"/>
       <c r="BC60" s="6"/>
@@ -20915,7 +20919,7 @@
       <c r="DN60" s="6"/>
       <c r="DO60" s="42"/>
     </row>
-    <row r="61" s="113" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" s="114" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="98"/>
       <c r="B61" s="98"/>
       <c r="C61" s="98"/>
@@ -20969,7 +20973,7 @@
       <c r="AZ61" s="6"/>
       <c r="DO61" s="42"/>
     </row>
-    <row r="62" s="113" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" s="114" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="74" t="s">
         <v>126</v>
       </c>
@@ -21107,16 +21111,16 @@
       <c r="AQ62" s="74"/>
       <c r="AR62" s="74"/>
       <c r="AS62" s="74"/>
-      <c r="AT62" s="107"/>
-      <c r="AU62" s="107"/>
-      <c r="AV62" s="107"/>
-      <c r="AW62" s="107"/>
+      <c r="AT62" s="108"/>
+      <c r="AU62" s="108"/>
+      <c r="AV62" s="108"/>
+      <c r="AW62" s="108"/>
       <c r="AX62" s="6"/>
       <c r="AY62" s="6"/>
       <c r="AZ62" s="6"/>
       <c r="BA62" s="6"/>
       <c r="BB62" s="6"/>
-      <c r="BC62" s="114"/>
+      <c r="BC62" s="115"/>
       <c r="BD62" s="6"/>
       <c r="BE62" s="6"/>
       <c r="BF62" s="6"/>
@@ -21320,12 +21324,12 @@
       <c r="AQ63" s="74"/>
       <c r="AR63" s="74"/>
       <c r="AS63" s="74"/>
-      <c r="AT63" s="107"/>
-      <c r="AU63" s="107"/>
-      <c r="AV63" s="107"/>
-      <c r="AW63" s="107"/>
-      <c r="AY63" s="115"/>
-      <c r="AZ63" s="115"/>
+      <c r="AT63" s="108"/>
+      <c r="AU63" s="108"/>
+      <c r="AV63" s="108"/>
+      <c r="AW63" s="108"/>
+      <c r="AY63" s="116"/>
+      <c r="AZ63" s="116"/>
       <c r="BC63" s="77"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21466,291 +21470,291 @@
       <c r="AQ64" s="74"/>
       <c r="AR64" s="74"/>
       <c r="AS64" s="74"/>
-      <c r="AT64" s="107"/>
-      <c r="AU64" s="107"/>
-      <c r="AV64" s="107"/>
-      <c r="AW64" s="107"/>
-      <c r="AX64" s="107"/>
+      <c r="AT64" s="108"/>
+      <c r="AU64" s="108"/>
+      <c r="AV64" s="108"/>
+      <c r="AW64" s="108"/>
+      <c r="AX64" s="108"/>
       <c r="AY64" s="70"/>
       <c r="AZ64" s="70"/>
-      <c r="BA64" s="107"/>
-      <c r="BB64" s="107"/>
-      <c r="BC64" s="107"/>
-      <c r="BD64" s="107"/>
-      <c r="BE64" s="107"/>
-      <c r="BF64" s="107"/>
-      <c r="BG64" s="107"/>
-      <c r="BH64" s="107"/>
-      <c r="BI64" s="107"/>
-      <c r="BJ64" s="107"/>
-      <c r="BK64" s="107"/>
-      <c r="BL64" s="107"/>
-      <c r="BM64" s="107"/>
-      <c r="BN64" s="107"/>
-      <c r="BO64" s="107"/>
-      <c r="BP64" s="107"/>
-      <c r="BQ64" s="107"/>
-      <c r="BR64" s="107"/>
-      <c r="BS64" s="107"/>
-      <c r="BT64" s="107"/>
-      <c r="BU64" s="107"/>
-      <c r="BV64" s="107"/>
-      <c r="BW64" s="107"/>
-      <c r="BX64" s="107"/>
-      <c r="BY64" s="107"/>
-      <c r="BZ64" s="107"/>
-      <c r="CA64" s="107"/>
-      <c r="CB64" s="107"/>
-      <c r="CC64" s="107"/>
-      <c r="CD64" s="107"/>
-      <c r="CE64" s="107"/>
-      <c r="CF64" s="107"/>
-      <c r="CG64" s="107"/>
-      <c r="CH64" s="107"/>
-      <c r="CI64" s="107"/>
-      <c r="CJ64" s="107"/>
-      <c r="CK64" s="107"/>
-      <c r="CL64" s="107"/>
-      <c r="CM64" s="107"/>
-      <c r="CN64" s="107"/>
-      <c r="CO64" s="107"/>
-      <c r="CP64" s="107"/>
-      <c r="CQ64" s="107"/>
-      <c r="CR64" s="107"/>
-      <c r="CS64" s="107"/>
-      <c r="CT64" s="107"/>
-      <c r="CU64" s="107"/>
-      <c r="CV64" s="107"/>
-      <c r="CW64" s="107"/>
-      <c r="CX64" s="107"/>
-      <c r="CY64" s="107"/>
-      <c r="CZ64" s="107"/>
-      <c r="DA64" s="107"/>
-      <c r="DB64" s="107"/>
-      <c r="DC64" s="107"/>
-      <c r="DD64" s="107"/>
-      <c r="DE64" s="107"/>
-      <c r="DF64" s="107"/>
-      <c r="DG64" s="107"/>
-      <c r="DH64" s="107"/>
-      <c r="DI64" s="107"/>
-      <c r="DJ64" s="107"/>
-      <c r="DK64" s="107"/>
-      <c r="DL64" s="107"/>
-      <c r="DM64" s="107"/>
-      <c r="DN64" s="107"/>
+      <c r="BA64" s="108"/>
+      <c r="BB64" s="108"/>
+      <c r="BC64" s="108"/>
+      <c r="BD64" s="108"/>
+      <c r="BE64" s="108"/>
+      <c r="BF64" s="108"/>
+      <c r="BG64" s="108"/>
+      <c r="BH64" s="108"/>
+      <c r="BI64" s="108"/>
+      <c r="BJ64" s="108"/>
+      <c r="BK64" s="108"/>
+      <c r="BL64" s="108"/>
+      <c r="BM64" s="108"/>
+      <c r="BN64" s="108"/>
+      <c r="BO64" s="108"/>
+      <c r="BP64" s="108"/>
+      <c r="BQ64" s="108"/>
+      <c r="BR64" s="108"/>
+      <c r="BS64" s="108"/>
+      <c r="BT64" s="108"/>
+      <c r="BU64" s="108"/>
+      <c r="BV64" s="108"/>
+      <c r="BW64" s="108"/>
+      <c r="BX64" s="108"/>
+      <c r="BY64" s="108"/>
+      <c r="BZ64" s="108"/>
+      <c r="CA64" s="108"/>
+      <c r="CB64" s="108"/>
+      <c r="CC64" s="108"/>
+      <c r="CD64" s="108"/>
+      <c r="CE64" s="108"/>
+      <c r="CF64" s="108"/>
+      <c r="CG64" s="108"/>
+      <c r="CH64" s="108"/>
+      <c r="CI64" s="108"/>
+      <c r="CJ64" s="108"/>
+      <c r="CK64" s="108"/>
+      <c r="CL64" s="108"/>
+      <c r="CM64" s="108"/>
+      <c r="CN64" s="108"/>
+      <c r="CO64" s="108"/>
+      <c r="CP64" s="108"/>
+      <c r="CQ64" s="108"/>
+      <c r="CR64" s="108"/>
+      <c r="CS64" s="108"/>
+      <c r="CT64" s="108"/>
+      <c r="CU64" s="108"/>
+      <c r="CV64" s="108"/>
+      <c r="CW64" s="108"/>
+      <c r="CX64" s="108"/>
+      <c r="CY64" s="108"/>
+      <c r="CZ64" s="108"/>
+      <c r="DA64" s="108"/>
+      <c r="DB64" s="108"/>
+      <c r="DC64" s="108"/>
+      <c r="DD64" s="108"/>
+      <c r="DE64" s="108"/>
+      <c r="DF64" s="108"/>
+      <c r="DG64" s="108"/>
+      <c r="DH64" s="108"/>
+      <c r="DI64" s="108"/>
+      <c r="DJ64" s="108"/>
+      <c r="DK64" s="108"/>
+      <c r="DL64" s="108"/>
+      <c r="DM64" s="108"/>
+      <c r="DN64" s="108"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="116" t="s">
+      <c r="A65" s="117" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="116"/>
-      <c r="C65" s="116" t="n">
+      <c r="B65" s="117"/>
+      <c r="C65" s="117" t="n">
         <f aca="false">+AVERAGE(B87:C87)/AVERAGE(B105:C105)</f>
         <v>4.00520172902542</v>
       </c>
-      <c r="D65" s="116" t="n">
+      <c r="D65" s="117" t="n">
         <f aca="false">+AVERAGE(C87:D87)/AVERAGE(C105:D105)</f>
         <v>4.09226275638292</v>
       </c>
-      <c r="E65" s="116" t="n">
+      <c r="E65" s="117" t="n">
         <f aca="false">+AVERAGE(D87:E87)/AVERAGE(D105:E105)</f>
         <v>3.84659520153267</v>
       </c>
-      <c r="F65" s="116" t="n">
+      <c r="F65" s="117" t="n">
         <f aca="false">+AVERAGE(E87:F87)/AVERAGE(E105:F105)</f>
         <v>3.31552729155532</v>
       </c>
-      <c r="G65" s="116" t="n">
+      <c r="G65" s="117" t="n">
         <f aca="false">+AVERAGE(F87:G87)/AVERAGE(F105:G105)</f>
         <v>3.03189914307506</v>
       </c>
-      <c r="H65" s="116" t="n">
+      <c r="H65" s="117" t="n">
         <f aca="false">+AVERAGE(G87:H87)/AVERAGE(G105:H105)</f>
         <v>2.86899882101338</v>
       </c>
-      <c r="I65" s="116" t="n">
+      <c r="I65" s="117" t="n">
         <f aca="false">+AVERAGE(H87:I87)/AVERAGE(H105:I105)</f>
         <v>2.80209473140396</v>
       </c>
-      <c r="J65" s="116" t="n">
+      <c r="J65" s="117" t="n">
         <f aca="false">+AVERAGE(I87:J87)/AVERAGE(I105:J105)</f>
         <v>2.69260392772225</v>
       </c>
-      <c r="K65" s="116" t="n">
+      <c r="K65" s="117" t="n">
         <f aca="false">+AVERAGE(J87:K87)/AVERAGE(J105:K105)</f>
         <v>2.50357317429499</v>
       </c>
-      <c r="L65" s="116" t="n">
+      <c r="L65" s="117" t="n">
         <f aca="false">+AVERAGE(K87:L87)/AVERAGE(K105:L105)</f>
         <v>2.37126870382434</v>
       </c>
-      <c r="M65" s="116" t="n">
+      <c r="M65" s="117" t="n">
         <f aca="false">+AVERAGE(L87:M87)/AVERAGE(L105:M105)</f>
         <v>2.32792405872327</v>
       </c>
-      <c r="N65" s="116" t="n">
+      <c r="N65" s="117" t="n">
         <f aca="false">+AVERAGE(M87:N87)/AVERAGE(M105:N105)</f>
         <v>2.30214807443153</v>
       </c>
-      <c r="O65" s="116" t="n">
+      <c r="O65" s="117" t="n">
         <f aca="false">+AVERAGE(N87:O87)/AVERAGE(N105:O105)</f>
         <v>2.24598246772875</v>
       </c>
-      <c r="P65" s="116" t="n">
+      <c r="P65" s="117" t="n">
         <f aca="false">+AVERAGE(O87:P87)/AVERAGE(O105:P105)</f>
         <v>2.23227057696249</v>
       </c>
-      <c r="Q65" s="116" t="n">
+      <c r="Q65" s="117" t="n">
         <f aca="false">+AVERAGE(P87:Q87)/AVERAGE(P105:Q105)</f>
         <v>2.30075974225832</v>
       </c>
-      <c r="R65" s="116" t="n">
+      <c r="R65" s="117" t="n">
         <f aca="false">+AVERAGE(Q87:R87)/AVERAGE(Q105:R105)</f>
         <v>2.32541355211472</v>
       </c>
-      <c r="S65" s="116" t="n">
+      <c r="S65" s="117" t="n">
         <f aca="false">+AVERAGE(R87:S87)/AVERAGE(R105:S105)</f>
         <v>2.25232703361002</v>
       </c>
-      <c r="T65" s="116" t="n">
+      <c r="T65" s="117" t="n">
         <f aca="false">+AVERAGE(S87:T87)/AVERAGE(S105:T105)</f>
         <v>2.26126920859314</v>
       </c>
-      <c r="U65" s="116" t="n">
+      <c r="U65" s="117" t="n">
         <f aca="false">+AVERAGE(T87:U87)/AVERAGE(T105:U105)</f>
         <v>2.23138614852231</v>
       </c>
-      <c r="V65" s="116" t="n">
+      <c r="V65" s="117" t="n">
         <f aca="false">+AVERAGE(U87:V87)/AVERAGE(U105:V105)</f>
         <v>2.16760546630717</v>
       </c>
-      <c r="W65" s="116" t="n">
+      <c r="W65" s="117" t="n">
         <f aca="false">+AVERAGE(V87:W87)/AVERAGE(V105:W105)</f>
         <v>2.14756461323931</v>
       </c>
-      <c r="X65" s="116" t="n">
+      <c r="X65" s="117" t="n">
         <f aca="false">+AVERAGE(W87:X87)/AVERAGE(W105:X105)</f>
         <v>2.1222106998255</v>
       </c>
-      <c r="Y65" s="116" t="n">
+      <c r="Y65" s="117" t="n">
         <f aca="false">+AVERAGE(X87:Y87)/AVERAGE(X105:Y105)</f>
         <v>2.10254945233547</v>
       </c>
-      <c r="Z65" s="116" t="n">
+      <c r="Z65" s="117" t="n">
         <f aca="false">+AVERAGE(Y87:Z87)/AVERAGE(Y105:Z105)</f>
         <v>2.0195483299449</v>
       </c>
-      <c r="AA65" s="116" t="n">
+      <c r="AA65" s="117" t="n">
         <f aca="false">+AVERAGE(Z87:AA87)/AVERAGE(Z105:AA105)</f>
         <v>1.94956551692209</v>
       </c>
-      <c r="AB65" s="116"/>
-      <c r="AC65" s="116"/>
-      <c r="AD65" s="116"/>
-      <c r="AE65" s="116"/>
-      <c r="AF65" s="116"/>
-      <c r="AG65" s="116"/>
-      <c r="AH65" s="116"/>
-      <c r="AI65" s="116"/>
-      <c r="AJ65" s="116" t="n">
+      <c r="AB65" s="117"/>
+      <c r="AC65" s="117"/>
+      <c r="AD65" s="117"/>
+      <c r="AE65" s="117"/>
+      <c r="AF65" s="117"/>
+      <c r="AG65" s="117"/>
+      <c r="AH65" s="117"/>
+      <c r="AI65" s="117"/>
+      <c r="AJ65" s="117" t="n">
         <f aca="false">+AVERAGE(AI87:AJ87)/AVERAGE(AI105:AJ105)</f>
         <v>3.11598666879689</v>
       </c>
-      <c r="AK65" s="116" t="n">
+      <c r="AK65" s="117" t="n">
         <f aca="false">+AVERAGE(AJ87:AK87)/AVERAGE(AJ105:AK105)</f>
         <v>2.54401843463921</v>
       </c>
-      <c r="AL65" s="116" t="n">
+      <c r="AL65" s="117" t="n">
         <f aca="false">+AVERAGE(AK87:AL87)/AVERAGE(AK105:AL105)</f>
         <v>2.35282626143462</v>
       </c>
-      <c r="AM65" s="116" t="n">
+      <c r="AM65" s="117" t="n">
         <f aca="false">+AVERAGE(AL87:AM87)/AVERAGE(AL105:AM105)</f>
         <v>2.25804767965905</v>
       </c>
-      <c r="AN65" s="116" t="n">
+      <c r="AN65" s="117" t="n">
         <f aca="false">+AVERAGE(AM87:AN87)/AVERAGE(AM105:AN105)</f>
         <v>2.12671973845034</v>
       </c>
-      <c r="AO65" s="116"/>
-      <c r="AP65" s="116"/>
-      <c r="AQ65" s="116"/>
-      <c r="AR65" s="116"/>
-      <c r="AS65" s="116"/>
-      <c r="AT65" s="117"/>
-      <c r="AU65" s="117"/>
-      <c r="AV65" s="117"/>
-      <c r="AW65" s="117"/>
-      <c r="AX65" s="107"/>
+      <c r="AO65" s="117"/>
+      <c r="AP65" s="117"/>
+      <c r="AQ65" s="117"/>
+      <c r="AR65" s="117"/>
+      <c r="AS65" s="117"/>
+      <c r="AT65" s="118"/>
+      <c r="AU65" s="118"/>
+      <c r="AV65" s="118"/>
+      <c r="AW65" s="118"/>
+      <c r="AX65" s="108"/>
       <c r="AY65" s="70"/>
       <c r="AZ65" s="70"/>
-      <c r="BA65" s="107"/>
-      <c r="BB65" s="107"/>
-      <c r="BC65" s="107"/>
-      <c r="BD65" s="107"/>
-      <c r="BE65" s="107"/>
-      <c r="BF65" s="107"/>
-      <c r="BG65" s="107"/>
-      <c r="BH65" s="107"/>
-      <c r="BI65" s="107"/>
-      <c r="BJ65" s="107"/>
-      <c r="BK65" s="107"/>
-      <c r="BL65" s="107"/>
-      <c r="BM65" s="107"/>
-      <c r="BN65" s="107"/>
-      <c r="BO65" s="107"/>
-      <c r="BP65" s="107"/>
-      <c r="BQ65" s="107"/>
-      <c r="BR65" s="107"/>
-      <c r="BS65" s="107"/>
-      <c r="BT65" s="107"/>
-      <c r="BU65" s="107"/>
-      <c r="BV65" s="107"/>
-      <c r="BW65" s="107"/>
-      <c r="BX65" s="107"/>
-      <c r="BY65" s="107"/>
-      <c r="BZ65" s="107"/>
-      <c r="CA65" s="107"/>
-      <c r="CB65" s="107"/>
-      <c r="CC65" s="107"/>
-      <c r="CD65" s="107"/>
-      <c r="CE65" s="107"/>
-      <c r="CF65" s="107"/>
-      <c r="CG65" s="107"/>
-      <c r="CH65" s="107"/>
-      <c r="CI65" s="107"/>
-      <c r="CJ65" s="107"/>
-      <c r="CK65" s="107"/>
-      <c r="CL65" s="107"/>
-      <c r="CM65" s="107"/>
-      <c r="CN65" s="107"/>
-      <c r="CO65" s="107"/>
-      <c r="CP65" s="107"/>
-      <c r="CQ65" s="107"/>
-      <c r="CR65" s="107"/>
-      <c r="CS65" s="107"/>
-      <c r="CT65" s="107"/>
-      <c r="CU65" s="107"/>
-      <c r="CV65" s="107"/>
-      <c r="CW65" s="107"/>
-      <c r="CX65" s="107"/>
-      <c r="CY65" s="107"/>
-      <c r="CZ65" s="107"/>
-      <c r="DA65" s="107"/>
-      <c r="DB65" s="107"/>
-      <c r="DC65" s="107"/>
-      <c r="DD65" s="107"/>
-      <c r="DE65" s="107"/>
-      <c r="DF65" s="107"/>
-      <c r="DG65" s="107"/>
-      <c r="DH65" s="107"/>
-      <c r="DI65" s="107"/>
-      <c r="DJ65" s="107"/>
-      <c r="DK65" s="107"/>
-      <c r="DL65" s="107"/>
-      <c r="DM65" s="107"/>
-      <c r="DN65" s="107"/>
+      <c r="BA65" s="108"/>
+      <c r="BB65" s="108"/>
+      <c r="BC65" s="108"/>
+      <c r="BD65" s="108"/>
+      <c r="BE65" s="108"/>
+      <c r="BF65" s="108"/>
+      <c r="BG65" s="108"/>
+      <c r="BH65" s="108"/>
+      <c r="BI65" s="108"/>
+      <c r="BJ65" s="108"/>
+      <c r="BK65" s="108"/>
+      <c r="BL65" s="108"/>
+      <c r="BM65" s="108"/>
+      <c r="BN65" s="108"/>
+      <c r="BO65" s="108"/>
+      <c r="BP65" s="108"/>
+      <c r="BQ65" s="108"/>
+      <c r="BR65" s="108"/>
+      <c r="BS65" s="108"/>
+      <c r="BT65" s="108"/>
+      <c r="BU65" s="108"/>
+      <c r="BV65" s="108"/>
+      <c r="BW65" s="108"/>
+      <c r="BX65" s="108"/>
+      <c r="BY65" s="108"/>
+      <c r="BZ65" s="108"/>
+      <c r="CA65" s="108"/>
+      <c r="CB65" s="108"/>
+      <c r="CC65" s="108"/>
+      <c r="CD65" s="108"/>
+      <c r="CE65" s="108"/>
+      <c r="CF65" s="108"/>
+      <c r="CG65" s="108"/>
+      <c r="CH65" s="108"/>
+      <c r="CI65" s="108"/>
+      <c r="CJ65" s="108"/>
+      <c r="CK65" s="108"/>
+      <c r="CL65" s="108"/>
+      <c r="CM65" s="108"/>
+      <c r="CN65" s="108"/>
+      <c r="CO65" s="108"/>
+      <c r="CP65" s="108"/>
+      <c r="CQ65" s="108"/>
+      <c r="CR65" s="108"/>
+      <c r="CS65" s="108"/>
+      <c r="CT65" s="108"/>
+      <c r="CU65" s="108"/>
+      <c r="CV65" s="108"/>
+      <c r="CW65" s="108"/>
+      <c r="CX65" s="108"/>
+      <c r="CY65" s="108"/>
+      <c r="CZ65" s="108"/>
+      <c r="DA65" s="108"/>
+      <c r="DB65" s="108"/>
+      <c r="DC65" s="108"/>
+      <c r="DD65" s="108"/>
+      <c r="DE65" s="108"/>
+      <c r="DF65" s="108"/>
+      <c r="DG65" s="108"/>
+      <c r="DH65" s="108"/>
+      <c r="DI65" s="108"/>
+      <c r="DJ65" s="108"/>
+      <c r="DK65" s="108"/>
+      <c r="DL65" s="108"/>
+      <c r="DM65" s="108"/>
+      <c r="DN65" s="108"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="74" t="s">
@@ -21890,79 +21894,79 @@
       <c r="AQ66" s="74"/>
       <c r="AR66" s="74"/>
       <c r="AS66" s="74"/>
-      <c r="AT66" s="107"/>
-      <c r="AU66" s="107"/>
-      <c r="AV66" s="107"/>
-      <c r="AW66" s="107"/>
-      <c r="AX66" s="107"/>
+      <c r="AT66" s="108"/>
+      <c r="AU66" s="108"/>
+      <c r="AV66" s="108"/>
+      <c r="AW66" s="108"/>
+      <c r="AX66" s="108"/>
       <c r="AY66" s="70"/>
       <c r="AZ66" s="70"/>
-      <c r="BA66" s="107"/>
-      <c r="BB66" s="107"/>
-      <c r="BC66" s="107"/>
-      <c r="BD66" s="107"/>
-      <c r="BE66" s="107"/>
-      <c r="BF66" s="107"/>
-      <c r="BG66" s="107"/>
-      <c r="BH66" s="107"/>
-      <c r="BI66" s="107"/>
-      <c r="BJ66" s="107"/>
-      <c r="BK66" s="107"/>
-      <c r="BL66" s="107"/>
-      <c r="BM66" s="107"/>
-      <c r="BN66" s="107"/>
-      <c r="BO66" s="107"/>
-      <c r="BP66" s="107"/>
-      <c r="BQ66" s="107"/>
-      <c r="BR66" s="107"/>
-      <c r="BS66" s="107"/>
-      <c r="BT66" s="107"/>
-      <c r="BU66" s="107"/>
-      <c r="BV66" s="107"/>
-      <c r="BW66" s="107"/>
-      <c r="BX66" s="107"/>
-      <c r="BY66" s="107"/>
-      <c r="BZ66" s="107"/>
-      <c r="CA66" s="107"/>
-      <c r="CB66" s="107"/>
-      <c r="CC66" s="107"/>
-      <c r="CD66" s="107"/>
-      <c r="CE66" s="107"/>
-      <c r="CF66" s="107"/>
-      <c r="CG66" s="107"/>
-      <c r="CH66" s="107"/>
-      <c r="CI66" s="107"/>
-      <c r="CJ66" s="107"/>
-      <c r="CK66" s="107"/>
-      <c r="CL66" s="107"/>
-      <c r="CM66" s="107"/>
-      <c r="CN66" s="107"/>
-      <c r="CO66" s="107"/>
-      <c r="CP66" s="107"/>
-      <c r="CQ66" s="107"/>
-      <c r="CR66" s="107"/>
-      <c r="CS66" s="107"/>
-      <c r="CT66" s="107"/>
-      <c r="CU66" s="107"/>
-      <c r="CV66" s="107"/>
-      <c r="CW66" s="107"/>
-      <c r="CX66" s="107"/>
-      <c r="CY66" s="107"/>
-      <c r="CZ66" s="107"/>
-      <c r="DA66" s="107"/>
-      <c r="DB66" s="107"/>
-      <c r="DC66" s="107"/>
-      <c r="DD66" s="107"/>
-      <c r="DE66" s="107"/>
-      <c r="DF66" s="107"/>
-      <c r="DG66" s="107"/>
-      <c r="DH66" s="107"/>
-      <c r="DI66" s="107"/>
-      <c r="DJ66" s="107"/>
-      <c r="DK66" s="107"/>
-      <c r="DL66" s="107"/>
-      <c r="DM66" s="107"/>
-      <c r="DN66" s="107"/>
+      <c r="BA66" s="108"/>
+      <c r="BB66" s="108"/>
+      <c r="BC66" s="108"/>
+      <c r="BD66" s="108"/>
+      <c r="BE66" s="108"/>
+      <c r="BF66" s="108"/>
+      <c r="BG66" s="108"/>
+      <c r="BH66" s="108"/>
+      <c r="BI66" s="108"/>
+      <c r="BJ66" s="108"/>
+      <c r="BK66" s="108"/>
+      <c r="BL66" s="108"/>
+      <c r="BM66" s="108"/>
+      <c r="BN66" s="108"/>
+      <c r="BO66" s="108"/>
+      <c r="BP66" s="108"/>
+      <c r="BQ66" s="108"/>
+      <c r="BR66" s="108"/>
+      <c r="BS66" s="108"/>
+      <c r="BT66" s="108"/>
+      <c r="BU66" s="108"/>
+      <c r="BV66" s="108"/>
+      <c r="BW66" s="108"/>
+      <c r="BX66" s="108"/>
+      <c r="BY66" s="108"/>
+      <c r="BZ66" s="108"/>
+      <c r="CA66" s="108"/>
+      <c r="CB66" s="108"/>
+      <c r="CC66" s="108"/>
+      <c r="CD66" s="108"/>
+      <c r="CE66" s="108"/>
+      <c r="CF66" s="108"/>
+      <c r="CG66" s="108"/>
+      <c r="CH66" s="108"/>
+      <c r="CI66" s="108"/>
+      <c r="CJ66" s="108"/>
+      <c r="CK66" s="108"/>
+      <c r="CL66" s="108"/>
+      <c r="CM66" s="108"/>
+      <c r="CN66" s="108"/>
+      <c r="CO66" s="108"/>
+      <c r="CP66" s="108"/>
+      <c r="CQ66" s="108"/>
+      <c r="CR66" s="108"/>
+      <c r="CS66" s="108"/>
+      <c r="CT66" s="108"/>
+      <c r="CU66" s="108"/>
+      <c r="CV66" s="108"/>
+      <c r="CW66" s="108"/>
+      <c r="CX66" s="108"/>
+      <c r="CY66" s="108"/>
+      <c r="CZ66" s="108"/>
+      <c r="DA66" s="108"/>
+      <c r="DB66" s="108"/>
+      <c r="DC66" s="108"/>
+      <c r="DD66" s="108"/>
+      <c r="DE66" s="108"/>
+      <c r="DF66" s="108"/>
+      <c r="DG66" s="108"/>
+      <c r="DH66" s="108"/>
+      <c r="DI66" s="108"/>
+      <c r="DJ66" s="108"/>
+      <c r="DK66" s="108"/>
+      <c r="DL66" s="108"/>
+      <c r="DM66" s="108"/>
+      <c r="DN66" s="108"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="98"/>
@@ -22010,525 +22014,525 @@
       <c r="AQ67" s="98"/>
       <c r="AR67" s="98"/>
       <c r="AS67" s="98"/>
-      <c r="AX67" s="117"/>
-      <c r="AY67" s="111"/>
-      <c r="AZ67" s="111"/>
-      <c r="BA67" s="117"/>
-      <c r="BB67" s="117"/>
-      <c r="BC67" s="117"/>
-      <c r="BD67" s="117"/>
-      <c r="BE67" s="117"/>
-      <c r="BF67" s="117"/>
-      <c r="BG67" s="117"/>
-      <c r="BH67" s="117"/>
-      <c r="BI67" s="117"/>
-      <c r="BJ67" s="117"/>
-      <c r="BK67" s="117"/>
-      <c r="BL67" s="117"/>
-      <c r="BM67" s="117"/>
-      <c r="BN67" s="117"/>
-      <c r="BO67" s="117"/>
-      <c r="BP67" s="117"/>
-      <c r="BQ67" s="117"/>
-      <c r="BR67" s="117"/>
-      <c r="BS67" s="117"/>
-      <c r="BT67" s="117"/>
-      <c r="BU67" s="117"/>
-      <c r="BV67" s="117"/>
-      <c r="BW67" s="117"/>
-      <c r="BX67" s="117"/>
-      <c r="BY67" s="117"/>
-      <c r="BZ67" s="117"/>
-      <c r="CA67" s="117"/>
-      <c r="CB67" s="117"/>
-      <c r="CC67" s="117"/>
-      <c r="CD67" s="117"/>
-      <c r="CE67" s="117"/>
-      <c r="CF67" s="117"/>
-      <c r="CG67" s="117"/>
-      <c r="CH67" s="117"/>
-      <c r="CI67" s="117"/>
-      <c r="CJ67" s="117"/>
-      <c r="CK67" s="117"/>
-      <c r="CL67" s="117"/>
-      <c r="CM67" s="117"/>
-      <c r="CN67" s="117"/>
-      <c r="CO67" s="117"/>
-      <c r="CP67" s="117"/>
-      <c r="CQ67" s="117"/>
-      <c r="CR67" s="117"/>
-      <c r="CS67" s="117"/>
-      <c r="CT67" s="117"/>
-      <c r="CU67" s="117"/>
-      <c r="CV67" s="117"/>
-      <c r="CW67" s="117"/>
-      <c r="CX67" s="117"/>
-      <c r="CY67" s="117"/>
-      <c r="CZ67" s="117"/>
-      <c r="DA67" s="117"/>
-      <c r="DB67" s="117"/>
-      <c r="DC67" s="117"/>
-      <c r="DD67" s="117"/>
-      <c r="DE67" s="117"/>
-      <c r="DF67" s="117"/>
-      <c r="DG67" s="117"/>
-      <c r="DH67" s="117"/>
-      <c r="DI67" s="117"/>
-      <c r="DJ67" s="117"/>
-      <c r="DK67" s="117"/>
-      <c r="DL67" s="117"/>
-      <c r="DM67" s="117"/>
-      <c r="DN67" s="117"/>
+      <c r="AX67" s="118"/>
+      <c r="AY67" s="112"/>
+      <c r="AZ67" s="112"/>
+      <c r="BA67" s="118"/>
+      <c r="BB67" s="118"/>
+      <c r="BC67" s="118"/>
+      <c r="BD67" s="118"/>
+      <c r="BE67" s="118"/>
+      <c r="BF67" s="118"/>
+      <c r="BG67" s="118"/>
+      <c r="BH67" s="118"/>
+      <c r="BI67" s="118"/>
+      <c r="BJ67" s="118"/>
+      <c r="BK67" s="118"/>
+      <c r="BL67" s="118"/>
+      <c r="BM67" s="118"/>
+      <c r="BN67" s="118"/>
+      <c r="BO67" s="118"/>
+      <c r="BP67" s="118"/>
+      <c r="BQ67" s="118"/>
+      <c r="BR67" s="118"/>
+      <c r="BS67" s="118"/>
+      <c r="BT67" s="118"/>
+      <c r="BU67" s="118"/>
+      <c r="BV67" s="118"/>
+      <c r="BW67" s="118"/>
+      <c r="BX67" s="118"/>
+      <c r="BY67" s="118"/>
+      <c r="BZ67" s="118"/>
+      <c r="CA67" s="118"/>
+      <c r="CB67" s="118"/>
+      <c r="CC67" s="118"/>
+      <c r="CD67" s="118"/>
+      <c r="CE67" s="118"/>
+      <c r="CF67" s="118"/>
+      <c r="CG67" s="118"/>
+      <c r="CH67" s="118"/>
+      <c r="CI67" s="118"/>
+      <c r="CJ67" s="118"/>
+      <c r="CK67" s="118"/>
+      <c r="CL67" s="118"/>
+      <c r="CM67" s="118"/>
+      <c r="CN67" s="118"/>
+      <c r="CO67" s="118"/>
+      <c r="CP67" s="118"/>
+      <c r="CQ67" s="118"/>
+      <c r="CR67" s="118"/>
+      <c r="CS67" s="118"/>
+      <c r="CT67" s="118"/>
+      <c r="CU67" s="118"/>
+      <c r="CV67" s="118"/>
+      <c r="CW67" s="118"/>
+      <c r="CX67" s="118"/>
+      <c r="CY67" s="118"/>
+      <c r="CZ67" s="118"/>
+      <c r="DA67" s="118"/>
+      <c r="DB67" s="118"/>
+      <c r="DC67" s="118"/>
+      <c r="DD67" s="118"/>
+      <c r="DE67" s="118"/>
+      <c r="DF67" s="118"/>
+      <c r="DG67" s="118"/>
+      <c r="DH67" s="118"/>
+      <c r="DI67" s="118"/>
+      <c r="DJ67" s="118"/>
+      <c r="DK67" s="118"/>
+      <c r="DL67" s="118"/>
+      <c r="DM67" s="118"/>
+      <c r="DN67" s="118"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B68" s="90"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="90"/>
-      <c r="E68" s="90"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="90"/>
-      <c r="H68" s="90"/>
-      <c r="I68" s="90"/>
-      <c r="J68" s="90"/>
-      <c r="K68" s="90"/>
-      <c r="L68" s="90"/>
-      <c r="M68" s="90"/>
-      <c r="N68" s="90"/>
-      <c r="O68" s="90"/>
-      <c r="P68" s="90"/>
-      <c r="Q68" s="90"/>
-      <c r="R68" s="90"/>
-      <c r="S68" s="90"/>
-      <c r="T68" s="90"/>
-      <c r="U68" s="90"/>
-      <c r="V68" s="90"/>
-      <c r="W68" s="90"/>
-      <c r="X68" s="90"/>
-      <c r="Y68" s="90"/>
-      <c r="Z68" s="90"/>
-      <c r="AA68" s="90"/>
-      <c r="AB68" s="90"/>
-      <c r="AC68" s="90"/>
-      <c r="AD68" s="90"/>
-      <c r="AE68" s="90"/>
-      <c r="AF68" s="90"/>
-      <c r="AG68" s="90"/>
-      <c r="AH68" s="90"/>
-      <c r="AI68" s="90"/>
-      <c r="AJ68" s="90"/>
-      <c r="AK68" s="90"/>
-      <c r="AL68" s="90"/>
-      <c r="AM68" s="90"/>
-      <c r="AN68" s="90"/>
-      <c r="AT68" s="118"/>
-      <c r="AU68" s="118"/>
-      <c r="AV68" s="118"/>
-      <c r="AW68" s="118"/>
-      <c r="AX68" s="107"/>
+      <c r="B68" s="104"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
+      <c r="J68" s="104"/>
+      <c r="K68" s="104"/>
+      <c r="L68" s="104"/>
+      <c r="M68" s="104"/>
+      <c r="N68" s="104"/>
+      <c r="O68" s="104"/>
+      <c r="P68" s="104"/>
+      <c r="Q68" s="104"/>
+      <c r="R68" s="104"/>
+      <c r="S68" s="104"/>
+      <c r="T68" s="104"/>
+      <c r="U68" s="104"/>
+      <c r="V68" s="104"/>
+      <c r="W68" s="104"/>
+      <c r="X68" s="104"/>
+      <c r="Y68" s="104"/>
+      <c r="Z68" s="104"/>
+      <c r="AA68" s="104"/>
+      <c r="AB68" s="104"/>
+      <c r="AC68" s="104"/>
+      <c r="AD68" s="104"/>
+      <c r="AE68" s="104"/>
+      <c r="AF68" s="104"/>
+      <c r="AG68" s="104"/>
+      <c r="AH68" s="104"/>
+      <c r="AI68" s="104"/>
+      <c r="AJ68" s="104"/>
+      <c r="AK68" s="104"/>
+      <c r="AL68" s="104"/>
+      <c r="AM68" s="104"/>
+      <c r="AN68" s="104"/>
+      <c r="AT68" s="119"/>
+      <c r="AU68" s="119"/>
+      <c r="AV68" s="119"/>
+      <c r="AW68" s="119"/>
+      <c r="AX68" s="108"/>
       <c r="AY68" s="70"/>
       <c r="AZ68" s="70"/>
-      <c r="BA68" s="107"/>
-      <c r="BB68" s="107"/>
-      <c r="BC68" s="107"/>
-      <c r="BD68" s="107"/>
-      <c r="BE68" s="107"/>
-      <c r="BF68" s="107"/>
-      <c r="BG68" s="107"/>
-      <c r="BH68" s="107"/>
-      <c r="BI68" s="107"/>
-      <c r="BJ68" s="107"/>
-      <c r="BK68" s="107"/>
-      <c r="BL68" s="107"/>
-      <c r="BM68" s="107"/>
-      <c r="BN68" s="107"/>
-      <c r="BO68" s="107"/>
-      <c r="BP68" s="107"/>
-      <c r="BQ68" s="107"/>
-      <c r="BR68" s="107"/>
-      <c r="BS68" s="107"/>
-      <c r="BT68" s="107"/>
-      <c r="BU68" s="107"/>
-      <c r="BV68" s="107"/>
-      <c r="BW68" s="107"/>
-      <c r="BX68" s="107"/>
-      <c r="BY68" s="107"/>
-      <c r="BZ68" s="107"/>
-      <c r="CA68" s="107"/>
-      <c r="CB68" s="107"/>
-      <c r="CC68" s="107"/>
-      <c r="CD68" s="107"/>
-      <c r="CE68" s="107"/>
-      <c r="CF68" s="107"/>
-      <c r="CG68" s="107"/>
-      <c r="CH68" s="107"/>
-      <c r="CI68" s="107"/>
-      <c r="CJ68" s="107"/>
-      <c r="CK68" s="107"/>
-      <c r="CL68" s="107"/>
-      <c r="CM68" s="107"/>
-      <c r="CN68" s="107"/>
-      <c r="CO68" s="107"/>
-      <c r="CP68" s="107"/>
-      <c r="CQ68" s="107"/>
-      <c r="CR68" s="107"/>
-      <c r="CS68" s="107"/>
-      <c r="CT68" s="107"/>
-      <c r="CU68" s="107"/>
-      <c r="CV68" s="107"/>
-      <c r="CW68" s="107"/>
-      <c r="CX68" s="107"/>
-      <c r="CY68" s="107"/>
-      <c r="CZ68" s="107"/>
-      <c r="DA68" s="107"/>
-      <c r="DB68" s="107"/>
-      <c r="DC68" s="107"/>
-      <c r="DD68" s="107"/>
-      <c r="DE68" s="107"/>
-      <c r="DF68" s="107"/>
-      <c r="DG68" s="107"/>
-      <c r="DH68" s="107"/>
-      <c r="DI68" s="107"/>
-      <c r="DJ68" s="107"/>
-      <c r="DK68" s="107"/>
-      <c r="DL68" s="107"/>
-      <c r="DM68" s="107"/>
-      <c r="DN68" s="107"/>
+      <c r="BA68" s="108"/>
+      <c r="BB68" s="108"/>
+      <c r="BC68" s="108"/>
+      <c r="BD68" s="108"/>
+      <c r="BE68" s="108"/>
+      <c r="BF68" s="108"/>
+      <c r="BG68" s="108"/>
+      <c r="BH68" s="108"/>
+      <c r="BI68" s="108"/>
+      <c r="BJ68" s="108"/>
+      <c r="BK68" s="108"/>
+      <c r="BL68" s="108"/>
+      <c r="BM68" s="108"/>
+      <c r="BN68" s="108"/>
+      <c r="BO68" s="108"/>
+      <c r="BP68" s="108"/>
+      <c r="BQ68" s="108"/>
+      <c r="BR68" s="108"/>
+      <c r="BS68" s="108"/>
+      <c r="BT68" s="108"/>
+      <c r="BU68" s="108"/>
+      <c r="BV68" s="108"/>
+      <c r="BW68" s="108"/>
+      <c r="BX68" s="108"/>
+      <c r="BY68" s="108"/>
+      <c r="BZ68" s="108"/>
+      <c r="CA68" s="108"/>
+      <c r="CB68" s="108"/>
+      <c r="CC68" s="108"/>
+      <c r="CD68" s="108"/>
+      <c r="CE68" s="108"/>
+      <c r="CF68" s="108"/>
+      <c r="CG68" s="108"/>
+      <c r="CH68" s="108"/>
+      <c r="CI68" s="108"/>
+      <c r="CJ68" s="108"/>
+      <c r="CK68" s="108"/>
+      <c r="CL68" s="108"/>
+      <c r="CM68" s="108"/>
+      <c r="CN68" s="108"/>
+      <c r="CO68" s="108"/>
+      <c r="CP68" s="108"/>
+      <c r="CQ68" s="108"/>
+      <c r="CR68" s="108"/>
+      <c r="CS68" s="108"/>
+      <c r="CT68" s="108"/>
+      <c r="CU68" s="108"/>
+      <c r="CV68" s="108"/>
+      <c r="CW68" s="108"/>
+      <c r="CX68" s="108"/>
+      <c r="CY68" s="108"/>
+      <c r="CZ68" s="108"/>
+      <c r="DA68" s="108"/>
+      <c r="DB68" s="108"/>
+      <c r="DC68" s="108"/>
+      <c r="DD68" s="108"/>
+      <c r="DE68" s="108"/>
+      <c r="DF68" s="108"/>
+      <c r="DG68" s="108"/>
+      <c r="DH68" s="108"/>
+      <c r="DI68" s="108"/>
+      <c r="DJ68" s="108"/>
+      <c r="DK68" s="108"/>
+      <c r="DL68" s="108"/>
+      <c r="DM68" s="108"/>
+      <c r="DN68" s="108"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="113" t="s">
+      <c r="A69" s="114" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="113" t="n">
+      <c r="B69" s="114" t="n">
         <f aca="false">B30*(1-B52)</f>
         <v>853.61910386496</v>
       </c>
-      <c r="C69" s="113" t="n">
+      <c r="C69" s="114" t="n">
         <f aca="false">C30*(1-C52)</f>
         <v>944.335657006039</v>
       </c>
-      <c r="D69" s="113" t="n">
+      <c r="D69" s="114" t="n">
         <f aca="false">D30*(1-D52)</f>
         <v>1205.88067753522</v>
       </c>
-      <c r="E69" s="113" t="n">
+      <c r="E69" s="114" t="n">
         <f aca="false">E30*(1-E52)</f>
         <v>1021.46677447576</v>
       </c>
-      <c r="F69" s="113" t="n">
+      <c r="F69" s="114" t="n">
         <f aca="false">F30*(1-F52)</f>
         <v>1644.07192534472</v>
       </c>
-      <c r="G69" s="113" t="n">
+      <c r="G69" s="114" t="n">
         <f aca="false">G30*(1-G52)</f>
         <v>1568.59251474173</v>
       </c>
-      <c r="H69" s="113" t="n">
+      <c r="H69" s="114" t="n">
         <f aca="false">H30*(1-H52)</f>
         <v>1531.56933188075</v>
       </c>
-      <c r="I69" s="113" t="n">
+      <c r="I69" s="114" t="n">
         <f aca="false">I30*(1-I52)</f>
         <v>697.693667546356</v>
       </c>
-      <c r="J69" s="113" t="n">
+      <c r="J69" s="114" t="n">
         <f aca="false">J30*(1-J52)</f>
         <v>1590.90959972137</v>
       </c>
-      <c r="K69" s="113" t="n">
+      <c r="K69" s="114" t="n">
         <f aca="false">K30*(1-K52)</f>
         <v>1401.16435570631</v>
       </c>
-      <c r="L69" s="113" t="n">
+      <c r="L69" s="114" t="n">
         <f aca="false">L30*(1-L52)</f>
         <v>1310.73315393235</v>
       </c>
-      <c r="M69" s="113" t="n">
+      <c r="M69" s="114" t="n">
         <f aca="false">M30*(1-M52)</f>
         <v>771.77901584871</v>
       </c>
-      <c r="N69" s="113" t="n">
+      <c r="N69" s="114" t="n">
         <f aca="false">N30*(1-N52)</f>
         <v>1523.93746917838</v>
       </c>
-      <c r="O69" s="113" t="n">
+      <c r="O69" s="114" t="n">
         <f aca="false">O30*(1-O52)</f>
         <v>1620.27618882779</v>
       </c>
-      <c r="P69" s="113" t="n">
+      <c r="P69" s="114" t="n">
         <f aca="false">P30*(1-P52)</f>
         <v>1726.42568332557</v>
       </c>
-      <c r="Q69" s="113" t="n">
+      <c r="Q69" s="114" t="n">
         <f aca="false">Q30*(1-Q52)</f>
         <v>1233.38944323883</v>
       </c>
-      <c r="R69" s="113" t="n">
+      <c r="R69" s="114" t="n">
         <f aca="false">R30*(1-R52)</f>
         <v>2348.91406640168</v>
       </c>
-      <c r="S69" s="113" t="n">
+      <c r="S69" s="114" t="n">
         <f aca="false">S30*(1-S52)</f>
         <v>2225.2327478923</v>
       </c>
-      <c r="T69" s="113" t="n">
+      <c r="T69" s="114" t="n">
         <f aca="false">T30*(1-T52)</f>
         <v>2545.98790139383</v>
       </c>
-      <c r="U69" s="113" t="n">
+      <c r="U69" s="114" t="n">
         <f aca="false">U30*(1-U52)</f>
         <v>1992.00995265702</v>
       </c>
-      <c r="V69" s="113" t="n">
+      <c r="V69" s="114" t="n">
         <f aca="false">V30*(1-V52)</f>
         <v>3011.79982724065</v>
       </c>
-      <c r="W69" s="113" t="n">
+      <c r="W69" s="114" t="n">
         <f aca="false">W30*(1-W52)</f>
         <v>3249.94363537867</v>
       </c>
-      <c r="X69" s="113" t="n">
+      <c r="X69" s="114" t="n">
         <f aca="false">X30*(1-X52)</f>
         <v>2662.40386177519</v>
       </c>
-      <c r="Y69" s="113" t="n">
+      <c r="Y69" s="114" t="n">
         <f aca="false">Y30*(1-Y52)</f>
         <v>2583.37551092782</v>
       </c>
-      <c r="Z69" s="113" t="n">
+      <c r="Z69" s="114" t="n">
         <f aca="false">Z30*(1-Z52)</f>
         <v>3192.73317189665</v>
       </c>
-      <c r="AA69" s="113" t="n">
+      <c r="AA69" s="114" t="n">
         <f aca="false">AA30*(1-AA52)</f>
         <v>3504.95383313911</v>
       </c>
-      <c r="AB69" s="113" t="n">
+      <c r="AB69" s="114" t="n">
         <f aca="false">AB30*(1-AB52)</f>
         <v>3613.93837968417</v>
       </c>
-      <c r="AC69" s="113" t="n">
+      <c r="AC69" s="114" t="n">
         <f aca="false">AC30*(1-AC52)</f>
         <v>3663.49523973623</v>
       </c>
-      <c r="AD69" s="113"/>
-      <c r="AE69" s="113"/>
-      <c r="AF69" s="113"/>
-      <c r="AG69" s="113"/>
-      <c r="AH69" s="113"/>
-      <c r="AI69" s="113" t="n">
+      <c r="AD69" s="114"/>
+      <c r="AE69" s="114"/>
+      <c r="AF69" s="114"/>
+      <c r="AG69" s="114"/>
+      <c r="AH69" s="114"/>
+      <c r="AI69" s="114" t="n">
         <f aca="false">AI30*(1-AI52)</f>
         <v>3957.44381791192</v>
       </c>
-      <c r="AJ69" s="113" t="n">
+      <c r="AJ69" s="114" t="n">
         <f aca="false">AJ30*(1-AJ52)</f>
         <v>5426.54223695318</v>
       </c>
-      <c r="AK69" s="113" t="n">
+      <c r="AK69" s="114" t="n">
         <f aca="false">AK30*(1-AK52)</f>
         <v>4806.55553672531</v>
       </c>
-      <c r="AL69" s="113" t="n">
+      <c r="AL69" s="114" t="n">
         <f aca="false">AL30*(1-AL52)</f>
         <v>6060.23007826613</v>
       </c>
-      <c r="AM69" s="113" t="n">
+      <c r="AM69" s="114" t="n">
         <f aca="false">AM30*(1-AM52)</f>
         <v>9106.59560538267</v>
       </c>
-      <c r="AN69" s="113" t="n">
+      <c r="AN69" s="114" t="n">
         <f aca="false">AN30*(1-AN52)</f>
         <v>11502.0875414518</v>
       </c>
-      <c r="AO69" s="113" t="n">
+      <c r="AO69" s="114" t="n">
         <f aca="false">AO30*(1-AO52)</f>
         <v>13754.926880725</v>
       </c>
-      <c r="AP69" s="113" t="n">
+      <c r="AP69" s="114" t="n">
         <f aca="false">AP30*(1-AP52)</f>
         <v>16384.1061379122</v>
       </c>
-      <c r="AQ69" s="113" t="n">
+      <c r="AQ69" s="114" t="n">
         <f aca="false">AQ30*(1-AQ52)</f>
         <v>19075.0939627147</v>
       </c>
-      <c r="AR69" s="113" t="n">
+      <c r="AR69" s="114" t="n">
         <f aca="false">AR30*(1-AR52)</f>
         <v>21871.8568044539</v>
       </c>
-      <c r="AS69" s="113" t="n">
+      <c r="AS69" s="114" t="n">
         <f aca="false">AS30*(1-AS52)</f>
         <v>23130.7117921865</v>
       </c>
-      <c r="AT69" s="113" t="n">
+      <c r="AT69" s="114" t="n">
         <f aca="false">AT30*(1-AT52)</f>
         <v>26271.2903382242</v>
       </c>
-      <c r="AU69" s="113" t="n">
+      <c r="AU69" s="114" t="n">
         <f aca="false">AU30*(1-AU52)</f>
         <v>29566.1612078515</v>
       </c>
-      <c r="AV69" s="113" t="n">
+      <c r="AV69" s="114" t="n">
         <f aca="false">AV30*(1-AV52)</f>
         <v>33268.0197815742</v>
       </c>
-      <c r="AW69" s="113" t="n">
+      <c r="AW69" s="114" t="n">
         <f aca="false">AW30*(1-AW52)</f>
         <v>37426.539316771</v>
       </c>
-      <c r="AX69" s="113" t="n">
+      <c r="AX69" s="114" t="n">
         <f aca="false">AX30*(1-AX52)</f>
         <v>42097.3879782241</v>
       </c>
-      <c r="AY69" s="113" t="n">
+      <c r="AY69" s="114" t="n">
         <f aca="false">AY30*(1-AY52)</f>
         <v>46728.1113808287</v>
       </c>
-      <c r="AZ69" s="115"/>
-      <c r="BC69" s="119" t="s">
+      <c r="AZ69" s="116"/>
+      <c r="BC69" s="120" t="s">
         <v>106</v>
       </c>
-      <c r="BD69" s="120" t="n">
+      <c r="BD69" s="121" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="113" t="s">
+      <c r="A70" s="114" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="113"/>
-      <c r="C70" s="113"/>
-      <c r="D70" s="113"/>
-      <c r="E70" s="113"/>
-      <c r="F70" s="113"/>
-      <c r="G70" s="113"/>
-      <c r="H70" s="113"/>
-      <c r="I70" s="113"/>
-      <c r="J70" s="113"/>
-      <c r="K70" s="113"/>
-      <c r="L70" s="113"/>
-      <c r="M70" s="113"/>
-      <c r="N70" s="113"/>
-      <c r="O70" s="113"/>
-      <c r="P70" s="113"/>
-      <c r="Q70" s="113"/>
-      <c r="R70" s="113"/>
-      <c r="S70" s="113"/>
-      <c r="T70" s="113"/>
-      <c r="U70" s="113"/>
-      <c r="V70" s="113"/>
-      <c r="W70" s="113"/>
-      <c r="X70" s="113"/>
-      <c r="Y70" s="113"/>
-      <c r="Z70" s="113"/>
-      <c r="AA70" s="113"/>
-      <c r="AB70" s="113"/>
-      <c r="AC70" s="113"/>
-      <c r="AD70" s="113"/>
-      <c r="AE70" s="113"/>
-      <c r="AF70" s="113"/>
-      <c r="AG70" s="113"/>
-      <c r="AH70" s="113"/>
-      <c r="AI70" s="113" t="n">
+      <c r="B70" s="114"/>
+      <c r="C70" s="114"/>
+      <c r="D70" s="114"/>
+      <c r="E70" s="114"/>
+      <c r="F70" s="114"/>
+      <c r="G70" s="114"/>
+      <c r="H70" s="114"/>
+      <c r="I70" s="114"/>
+      <c r="J70" s="114"/>
+      <c r="K70" s="114"/>
+      <c r="L70" s="114"/>
+      <c r="M70" s="114"/>
+      <c r="N70" s="114"/>
+      <c r="O70" s="114"/>
+      <c r="P70" s="114"/>
+      <c r="Q70" s="114"/>
+      <c r="R70" s="114"/>
+      <c r="S70" s="114"/>
+      <c r="T70" s="114"/>
+      <c r="U70" s="114"/>
+      <c r="V70" s="114"/>
+      <c r="W70" s="114"/>
+      <c r="X70" s="114"/>
+      <c r="Y70" s="114"/>
+      <c r="Z70" s="114"/>
+      <c r="AA70" s="114"/>
+      <c r="AB70" s="114"/>
+      <c r="AC70" s="114"/>
+      <c r="AD70" s="114"/>
+      <c r="AE70" s="114"/>
+      <c r="AF70" s="114"/>
+      <c r="AG70" s="114"/>
+      <c r="AH70" s="114"/>
+      <c r="AI70" s="114" t="n">
         <f aca="false">(AI87-AI80)-(AI100-0)</f>
         <v>2859.93397803237</v>
       </c>
-      <c r="AJ70" s="113" t="n">
+      <c r="AJ70" s="114" t="n">
         <f aca="false">(AJ87-AJ80)-(AJ100-0)</f>
         <v>9821.46592576888</v>
       </c>
-      <c r="AK70" s="113" t="n">
+      <c r="AK70" s="114" t="n">
         <f aca="false">(AK87-AK80)-(AK100-0)</f>
         <v>15630.1703883058</v>
       </c>
-      <c r="AL70" s="113" t="n">
+      <c r="AL70" s="114" t="n">
         <f aca="false">(AL87-AL80)-(AL100-0)</f>
         <v>13471.1412797773</v>
       </c>
-      <c r="AM70" s="113" t="n">
+      <c r="AM70" s="114" t="n">
         <f aca="false">(AM87-AM80)-(AM100-0)</f>
         <v>16938.1630591311</v>
       </c>
-      <c r="AN70" s="113" t="n">
+      <c r="AN70" s="114" t="n">
         <f aca="false">(AN87-AN80)-(AN100-0)</f>
         <v>17581.8990093554</v>
       </c>
-      <c r="AO70" s="113"/>
-      <c r="AP70" s="113"/>
-      <c r="AQ70" s="113"/>
-      <c r="AR70" s="113"/>
-      <c r="AS70" s="113"/>
-      <c r="AX70" s="118"/>
-      <c r="BA70" s="118"/>
-      <c r="BB70" s="118"/>
+      <c r="AO70" s="114"/>
+      <c r="AP70" s="114"/>
+      <c r="AQ70" s="114"/>
+      <c r="AR70" s="114"/>
+      <c r="AS70" s="114"/>
+      <c r="AX70" s="119"/>
+      <c r="BA70" s="119"/>
+      <c r="BB70" s="119"/>
       <c r="BC70" s="85" t="s">
         <v>110</v>
       </c>
       <c r="BD70" s="86" t="n">
         <f aca="false">+Main!E9</f>
-        <v>0.121301298536298</v>
-      </c>
-      <c r="BE70" s="118"/>
-      <c r="BF70" s="118"/>
-      <c r="BG70" s="118"/>
-      <c r="BH70" s="118"/>
-      <c r="BI70" s="118"/>
-      <c r="BJ70" s="118"/>
-      <c r="BK70" s="118"/>
-      <c r="BL70" s="118"/>
-      <c r="BM70" s="118"/>
-      <c r="BN70" s="118"/>
-      <c r="BO70" s="118"/>
-      <c r="BP70" s="118"/>
-      <c r="BQ70" s="118"/>
-      <c r="BR70" s="118"/>
-      <c r="BS70" s="118"/>
-      <c r="BT70" s="118"/>
-      <c r="BU70" s="118"/>
-      <c r="BV70" s="118"/>
-      <c r="BW70" s="118"/>
-      <c r="BX70" s="118"/>
-      <c r="BY70" s="118"/>
-      <c r="BZ70" s="118"/>
-      <c r="CA70" s="118"/>
-      <c r="CB70" s="118"/>
-      <c r="CC70" s="118"/>
-      <c r="CD70" s="118"/>
-      <c r="CE70" s="118"/>
-      <c r="CF70" s="118"/>
-      <c r="CG70" s="118"/>
-      <c r="CH70" s="118"/>
-      <c r="CI70" s="118"/>
-      <c r="CJ70" s="118"/>
-      <c r="CK70" s="118"/>
-      <c r="CL70" s="118"/>
-      <c r="CM70" s="118"/>
-      <c r="CN70" s="118"/>
-      <c r="CO70" s="118"/>
-      <c r="CP70" s="118"/>
-      <c r="CQ70" s="118"/>
-      <c r="CR70" s="118"/>
-      <c r="CS70" s="118"/>
-      <c r="CT70" s="118"/>
-      <c r="CU70" s="118"/>
-      <c r="CV70" s="118"/>
-      <c r="CW70" s="118"/>
-      <c r="CX70" s="118"/>
-      <c r="CY70" s="118"/>
-      <c r="CZ70" s="118"/>
-      <c r="DA70" s="118"/>
-      <c r="DB70" s="118"/>
-      <c r="DC70" s="118"/>
-      <c r="DD70" s="118"/>
-      <c r="DE70" s="118"/>
-      <c r="DF70" s="118"/>
-      <c r="DG70" s="118"/>
-      <c r="DH70" s="118"/>
-      <c r="DI70" s="118"/>
-      <c r="DJ70" s="118"/>
-      <c r="DK70" s="118"/>
-      <c r="DL70" s="118"/>
-      <c r="DM70" s="118"/>
-      <c r="DN70" s="118"/>
+        <v>0.118728823881187</v>
+      </c>
+      <c r="BE70" s="119"/>
+      <c r="BF70" s="119"/>
+      <c r="BG70" s="119"/>
+      <c r="BH70" s="119"/>
+      <c r="BI70" s="119"/>
+      <c r="BJ70" s="119"/>
+      <c r="BK70" s="119"/>
+      <c r="BL70" s="119"/>
+      <c r="BM70" s="119"/>
+      <c r="BN70" s="119"/>
+      <c r="BO70" s="119"/>
+      <c r="BP70" s="119"/>
+      <c r="BQ70" s="119"/>
+      <c r="BR70" s="119"/>
+      <c r="BS70" s="119"/>
+      <c r="BT70" s="119"/>
+      <c r="BU70" s="119"/>
+      <c r="BV70" s="119"/>
+      <c r="BW70" s="119"/>
+      <c r="BX70" s="119"/>
+      <c r="BY70" s="119"/>
+      <c r="BZ70" s="119"/>
+      <c r="CA70" s="119"/>
+      <c r="CB70" s="119"/>
+      <c r="CC70" s="119"/>
+      <c r="CD70" s="119"/>
+      <c r="CE70" s="119"/>
+      <c r="CF70" s="119"/>
+      <c r="CG70" s="119"/>
+      <c r="CH70" s="119"/>
+      <c r="CI70" s="119"/>
+      <c r="CJ70" s="119"/>
+      <c r="CK70" s="119"/>
+      <c r="CL70" s="119"/>
+      <c r="CM70" s="119"/>
+      <c r="CN70" s="119"/>
+      <c r="CO70" s="119"/>
+      <c r="CP70" s="119"/>
+      <c r="CQ70" s="119"/>
+      <c r="CR70" s="119"/>
+      <c r="CS70" s="119"/>
+      <c r="CT70" s="119"/>
+      <c r="CU70" s="119"/>
+      <c r="CV70" s="119"/>
+      <c r="CW70" s="119"/>
+      <c r="CX70" s="119"/>
+      <c r="CY70" s="119"/>
+      <c r="CZ70" s="119"/>
+      <c r="DA70" s="119"/>
+      <c r="DB70" s="119"/>
+      <c r="DC70" s="119"/>
+      <c r="DD70" s="119"/>
+      <c r="DE70" s="119"/>
+      <c r="DF70" s="119"/>
+      <c r="DG70" s="119"/>
+      <c r="DH70" s="119"/>
+      <c r="DI70" s="119"/>
+      <c r="DJ70" s="119"/>
+      <c r="DK70" s="119"/>
+      <c r="DL70" s="119"/>
+      <c r="DM70" s="119"/>
+      <c r="DN70" s="119"/>
     </row>
     <row r="71" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
@@ -22567,27 +22571,27 @@
       <c r="AF71" s="6"/>
       <c r="AG71" s="6"/>
       <c r="AH71" s="6"/>
-      <c r="AI71" s="90" t="n">
+      <c r="AI71" s="104" t="n">
         <f aca="false">AI69/AI70</f>
         <v>1.38375355805753</v>
       </c>
-      <c r="AJ71" s="90" t="n">
+      <c r="AJ71" s="104" t="n">
         <f aca="false">AJ69/AJ70</f>
         <v>0.552518562704107</v>
       </c>
-      <c r="AK71" s="90" t="n">
+      <c r="AK71" s="104" t="n">
         <f aca="false">AK69/AK70</f>
         <v>0.307517795220038</v>
       </c>
-      <c r="AL71" s="90" t="n">
+      <c r="AL71" s="104" t="n">
         <f aca="false">AL69/AL70</f>
         <v>0.449867606047875</v>
       </c>
-      <c r="AM71" s="90" t="n">
+      <c r="AM71" s="104" t="n">
         <f aca="false">AM69/AM70</f>
         <v>0.537637734008791</v>
       </c>
-      <c r="AN71" s="90" t="n">
+      <c r="AN71" s="104" t="n">
         <f aca="false">AN69/AN70</f>
         <v>0.654200523807556</v>
       </c>
@@ -22596,10 +22600,10 @@
       <c r="AQ71" s="6"/>
       <c r="AR71" s="6"/>
       <c r="AS71" s="6"/>
-      <c r="AT71" s="121"/>
-      <c r="AU71" s="121"/>
-      <c r="AV71" s="121"/>
-      <c r="AW71" s="121"/>
+      <c r="AT71" s="122"/>
+      <c r="AU71" s="122"/>
+      <c r="AV71" s="122"/>
+      <c r="AW71" s="122"/>
       <c r="AX71" s="6"/>
       <c r="AY71" s="6"/>
       <c r="AZ71" s="6"/>
@@ -22610,7 +22614,7 @@
       </c>
       <c r="BD71" s="94" t="n">
         <f aca="false">+NPV(BD70,AO74:AX74,AY74+BD72)</f>
-        <v>369485.830660419</v>
+        <v>382396.632615363</v>
       </c>
       <c r="BE71" s="6"/>
       <c r="BF71" s="6"/>
@@ -22680,107 +22684,107 @@
       <c r="A72" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="B72" s="122" t="n">
+      <c r="B72" s="123" t="n">
         <f aca="false">B87/B100</f>
         <v>1.27174751994084</v>
       </c>
-      <c r="C72" s="122" t="n">
+      <c r="C72" s="123" t="n">
         <f aca="false">C87/C100</f>
         <v>1.33525679456943</v>
       </c>
-      <c r="D72" s="122" t="n">
+      <c r="D72" s="123" t="n">
         <f aca="false">D87/D100</f>
         <v>1.36522934746655</v>
       </c>
-      <c r="E72" s="122" t="n">
+      <c r="E72" s="123" t="n">
         <f aca="false">E87/E100</f>
         <v>1.39215105692053</v>
       </c>
-      <c r="F72" s="122" t="n">
+      <c r="F72" s="123" t="n">
         <f aca="false">F87/F100</f>
         <v>1.47296716530697</v>
       </c>
-      <c r="G72" s="122" t="n">
+      <c r="G72" s="123" t="n">
         <f aca="false">G87/G100</f>
         <v>1.51142008554198</v>
       </c>
-      <c r="H72" s="122" t="n">
+      <c r="H72" s="123" t="n">
         <f aca="false">H87/H100</f>
         <v>1.55840431742744</v>
       </c>
-      <c r="I72" s="122" t="n">
+      <c r="I72" s="123" t="n">
         <f aca="false">I87/I100</f>
         <v>1.55152604781954</v>
       </c>
-      <c r="J72" s="122" t="n">
+      <c r="J72" s="123" t="n">
         <f aca="false">J87/J100</f>
         <v>1.63133392432236</v>
       </c>
-      <c r="K72" s="122" t="n">
+      <c r="K72" s="123" t="n">
         <f aca="false">K87/K100</f>
         <v>1.69996280383649</v>
       </c>
-      <c r="L72" s="122" t="n">
+      <c r="L72" s="123" t="n">
         <f aca="false">L87/L100</f>
         <v>1.75929304566464</v>
       </c>
-      <c r="M72" s="122" t="n">
+      <c r="M72" s="123" t="n">
         <f aca="false">M87/M100</f>
         <v>1.74687726871816</v>
       </c>
-      <c r="N72" s="122" t="n">
+      <c r="N72" s="123" t="n">
         <f aca="false">N87/N100</f>
         <v>1.7891193758416</v>
       </c>
-      <c r="O72" s="122" t="n">
+      <c r="O72" s="123" t="n">
         <f aca="false">O87/O100</f>
         <v>1.81580426794038</v>
       </c>
-      <c r="P72" s="122" t="n">
+      <c r="P72" s="123" t="n">
         <f aca="false">P87/P100</f>
         <v>1.80697579930859</v>
       </c>
-      <c r="Q72" s="122" t="n">
+      <c r="Q72" s="123" t="n">
         <f aca="false">Q87/Q100</f>
         <v>1.73149765098864</v>
       </c>
-      <c r="R72" s="122" t="n">
+      <c r="R72" s="123" t="n">
         <f aca="false">R87/R100</f>
         <v>1.77798832598125</v>
       </c>
-      <c r="S72" s="122" t="n">
+      <c r="S72" s="123" t="n">
         <f aca="false">S87/S100</f>
         <v>1.81921522450286</v>
       </c>
-      <c r="T72" s="122" t="n">
+      <c r="T72" s="123" t="n">
         <f aca="false">T87/T100</f>
         <v>1.76856607376716</v>
       </c>
-      <c r="U72" s="122" t="n">
+      <c r="U72" s="123" t="n">
         <f aca="false">U87/U100</f>
         <v>1.85651109501431</v>
       </c>
-      <c r="V72" s="122" t="n">
+      <c r="V72" s="123" t="n">
         <f aca="false">V87/V100</f>
         <v>1.85630289423527</v>
       </c>
-      <c r="W72" s="122" t="n">
+      <c r="W72" s="123" t="n">
         <f aca="false">W87/W100</f>
         <v>1.88642988372135</v>
       </c>
-      <c r="X72" s="122" t="n">
+      <c r="X72" s="123" t="n">
         <f aca="false">X87/X100</f>
         <v>1.89546170741619</v>
       </c>
-      <c r="Y72" s="122" t="n">
+      <c r="Y72" s="123" t="n">
         <f aca="false">Y87/Y100</f>
         <v>1.91833416814706</v>
       </c>
-      <c r="Z72" s="122" t="n">
+      <c r="Z72" s="123" t="n">
         <f aca="false">Z87/Z100</f>
         <v>2.04132479120322</v>
       </c>
-      <c r="AA72" s="122" t="n">
+      <c r="AA72" s="123" t="n">
         <f aca="false">AA87/AA100</f>
         <v>2.06545283702612</v>
       </c>
@@ -22791,27 +22795,27 @@
       <c r="AF72" s="6"/>
       <c r="AG72" s="6"/>
       <c r="AH72" s="6"/>
-      <c r="AI72" s="122" t="n">
+      <c r="AI72" s="123" t="n">
         <f aca="false">AI87/AI100</f>
         <v>1.39218731029518</v>
       </c>
-      <c r="AJ72" s="122" t="n">
+      <c r="AJ72" s="123" t="n">
         <f aca="false">AJ87/AJ100</f>
         <v>1.55156209567759</v>
       </c>
-      <c r="AK72" s="122" t="n">
+      <c r="AK72" s="123" t="n">
         <f aca="false">AK87/AK100</f>
         <v>1.74692090759358</v>
       </c>
-      <c r="AL72" s="122" t="n">
+      <c r="AL72" s="123" t="n">
         <f aca="false">AL87/AL100</f>
         <v>1.73153730949821</v>
       </c>
-      <c r="AM72" s="122" t="n">
+      <c r="AM72" s="123" t="n">
         <f aca="false">AM87/AM100</f>
         <v>1.85654841549713</v>
       </c>
-      <c r="AN72" s="122" t="n">
+      <c r="AN72" s="123" t="n">
         <f aca="false">AN87/AN100</f>
         <v>1.91837074594916</v>
       </c>
@@ -22825,16 +22829,16 @@
       <c r="AV72" s="6"/>
       <c r="AW72" s="6"/>
       <c r="AX72" s="6"/>
-      <c r="AY72" s="113"/>
-      <c r="AZ72" s="113"/>
+      <c r="AY72" s="114"/>
+      <c r="AZ72" s="114"/>
       <c r="BA72" s="6"/>
       <c r="BB72" s="6"/>
-      <c r="BC72" s="123" t="s">
+      <c r="BC72" s="124" t="s">
         <v>134</v>
       </c>
-      <c r="BD72" s="124" t="n">
+      <c r="BD72" s="125" t="n">
         <f aca="false">+AY74*(1+BD69)/(BD70-BD69)</f>
-        <v>659571.757537328</v>
+        <v>678694.423152323</v>
       </c>
       <c r="BE72" s="6"/>
       <c r="BF72" s="6"/>
@@ -22901,290 +22905,290 @@
       <c r="DO72" s="42"/>
     </row>
     <row r="73" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="125" t="s">
+      <c r="A73" s="126" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="126" t="n">
+      <c r="B73" s="127" t="n">
         <f aca="false">+SUM(B84)-SUM(B89,B91,B92,B94)</f>
         <v>-7224.6</v>
       </c>
-      <c r="C73" s="126" t="n">
+      <c r="C73" s="127" t="n">
         <f aca="false">+SUM(C84)-SUM(C89,C91,C92,C94)</f>
         <v>-5716.2</v>
       </c>
-      <c r="D73" s="126" t="n">
+      <c r="D73" s="127" t="n">
         <f aca="false">+SUM(D84)-SUM(D89,D91,D92,D94)</f>
         <v>-6006.1</v>
       </c>
-      <c r="E73" s="126" t="n">
+      <c r="E73" s="127" t="n">
         <f aca="false">+SUM(E84)-SUM(E89,E91,E92,E94)</f>
         <v>-5749.6</v>
       </c>
-      <c r="F73" s="126" t="n">
+      <c r="F73" s="127" t="n">
         <f aca="false">+SUM(F84)-SUM(F89,F91,F92,F94)</f>
         <v>-5559</v>
       </c>
-      <c r="G73" s="126" t="n">
+      <c r="G73" s="127" t="n">
         <f aca="false">+SUM(G84)-SUM(G89,G91,G92,G94)</f>
         <v>-5306.8</v>
       </c>
-      <c r="H73" s="126" t="n">
+      <c r="H73" s="127" t="n">
         <f aca="false">+SUM(H84)-SUM(H89,H91,H92,H94)</f>
         <v>-5460.5</v>
       </c>
-      <c r="I73" s="126" t="n">
+      <c r="I73" s="127" t="n">
         <f aca="false">+SUM(I84)-SUM(I89,I91,I92,I94)</f>
         <v>-5746.9</v>
       </c>
-      <c r="J73" s="126" t="n">
+      <c r="J73" s="127" t="n">
         <f aca="false">+SUM(J84)-SUM(J89,J91,J92,J94)</f>
         <v>-5650.5</v>
       </c>
-      <c r="K73" s="126" t="n">
+      <c r="K73" s="127" t="n">
         <f aca="false">+SUM(K84)-SUM(K89,K91,K92,K94)</f>
         <v>-5478.86</v>
       </c>
-      <c r="L73" s="126" t="n">
+      <c r="L73" s="127" t="n">
         <f aca="false">+SUM(L84)-SUM(L89,L91,L92,L94)</f>
         <v>-5062.7</v>
       </c>
-      <c r="M73" s="126" t="n">
+      <c r="M73" s="127" t="n">
         <f aca="false">+SUM(M84)-SUM(M89,M91,M92,M94)</f>
         <v>-4722.8</v>
       </c>
-      <c r="N73" s="126" t="n">
+      <c r="N73" s="127" t="n">
         <f aca="false">+SUM(N84)-SUM(N89,N91,N92,N94)</f>
         <v>-5261.6</v>
       </c>
-      <c r="O73" s="126" t="n">
+      <c r="O73" s="127" t="n">
         <f aca="false">+SUM(O84)-SUM(O89,O91,O92,O94)</f>
         <v>-5347.3</v>
       </c>
-      <c r="P73" s="126" t="n">
+      <c r="P73" s="127" t="n">
         <f aca="false">+SUM(P84)-SUM(P89,P91,P92,P94)</f>
         <v>-5026.9</v>
       </c>
-      <c r="Q73" s="126" t="n">
+      <c r="Q73" s="127" t="n">
         <f aca="false">+SUM(Q84)-SUM(Q89,Q91,Q92,Q94)</f>
         <v>-5680.6</v>
       </c>
-      <c r="R73" s="126" t="n">
+      <c r="R73" s="127" t="n">
         <f aca="false">+SUM(R84)-SUM(R89,R91,R92,R94)</f>
         <v>-5613.8</v>
       </c>
-      <c r="S73" s="126" t="n">
+      <c r="S73" s="127" t="n">
         <f aca="false">+SUM(S84)-SUM(S89,S91,S92,S94)</f>
         <v>-5382.3</v>
       </c>
-      <c r="T73" s="126" t="n">
+      <c r="T73" s="127" t="n">
         <f aca="false">+SUM(T84)-SUM(T89,T91,T92,T94)</f>
         <v>-5981.5</v>
       </c>
-      <c r="U73" s="126" t="n">
+      <c r="U73" s="127" t="n">
         <f aca="false">+SUM(U84)-SUM(U89,U91,U92,U94)</f>
         <v>-5454.8</v>
       </c>
-      <c r="V73" s="126" t="n">
+      <c r="V73" s="127" t="n">
         <f aca="false">+SUM(V84)-SUM(V89,V91,V92,V94)</f>
         <v>-5385.5</v>
       </c>
-      <c r="W73" s="126" t="n">
+      <c r="W73" s="127" t="n">
         <f aca="false">+SUM(W84)-SUM(W89,W91,W92,W94)</f>
         <v>-5339.1</v>
       </c>
-      <c r="X73" s="126" t="n">
+      <c r="X73" s="127" t="n">
         <f aca="false">+SUM(X84)-SUM(X89,X91,X92,X94)</f>
         <v>-6093.7</v>
       </c>
-      <c r="Y73" s="126" t="n">
+      <c r="Y73" s="127" t="n">
         <f aca="false">+SUM(Y84)-SUM(Y89,Y91,Y92,Y94)</f>
         <v>-6023.9</v>
       </c>
-      <c r="Z73" s="126" t="n">
+      <c r="Z73" s="127" t="n">
         <f aca="false">+SUM(Z84)-SUM(Z89,Z91,Z92,Z94)</f>
         <v>-6349.861</v>
       </c>
-      <c r="AA73" s="126" t="n">
+      <c r="AA73" s="127" t="n">
         <f aca="false">+SUM(AA84)-SUM(AA89,AA91,AA92,AA94)</f>
         <v>-4925.747</v>
       </c>
-      <c r="AB73" s="126"/>
-      <c r="AC73" s="126"/>
-      <c r="AD73" s="126"/>
-      <c r="AE73" s="126"/>
-      <c r="AF73" s="126"/>
-      <c r="AG73" s="126"/>
-      <c r="AH73" s="126"/>
-      <c r="AI73" s="126" t="n">
+      <c r="AB73" s="127"/>
+      <c r="AC73" s="127"/>
+      <c r="AD73" s="127"/>
+      <c r="AE73" s="127"/>
+      <c r="AF73" s="127"/>
+      <c r="AG73" s="127"/>
+      <c r="AH73" s="127"/>
+      <c r="AI73" s="127" t="n">
         <f aca="false">+SUM(AI84)-SUM(AI89,AI91,AI92,AI94)</f>
         <v>-5749.6</v>
       </c>
-      <c r="AJ73" s="126" t="n">
+      <c r="AJ73" s="127" t="n">
         <f aca="false">+SUM(AJ84)-SUM(AJ89,AJ91,AJ92,AJ94)</f>
         <v>-5746.9</v>
       </c>
-      <c r="AK73" s="126" t="n">
+      <c r="AK73" s="127" t="n">
         <f aca="false">+SUM(AK84)-SUM(AK89,AK91,AK92,AK94)</f>
         <v>-4722.8</v>
       </c>
-      <c r="AL73" s="126" t="n">
+      <c r="AL73" s="127" t="n">
         <f aca="false">+SUM(AL84)-SUM(AL89,AL91,AL92,AL94)</f>
         <v>-5680.6</v>
       </c>
-      <c r="AM73" s="126" t="n">
+      <c r="AM73" s="127" t="n">
         <f aca="false">+SUM(AM84)-SUM(AM89,AM91,AM92,AM94)</f>
         <v>-5454.8</v>
       </c>
-      <c r="AN73" s="126" t="n">
+      <c r="AN73" s="127" t="n">
         <f aca="false">+SUM(AN84)-SUM(AN89,AN91,AN92,AN94)</f>
         <v>-6023.9</v>
       </c>
-      <c r="AO73" s="126" t="n">
+      <c r="AO73" s="127" t="n">
         <f aca="false">+SUM(AO84)-SUM(AO89,AO91,AO92,AO94)</f>
         <v>-5652.23724775456</v>
       </c>
-      <c r="AP73" s="126" t="n">
+      <c r="AP73" s="127" t="n">
         <f aca="false">+SUM(AP84)-SUM(AP89,AP91,AP92,AP94)</f>
         <v>-6430.3122529833</v>
       </c>
-      <c r="AQ73" s="126" t="n">
+      <c r="AQ73" s="127" t="n">
         <f aca="false">+SUM(AQ84)-SUM(AQ89,AQ91,AQ92,AQ94)</f>
         <v>-7295.9840503518</v>
       </c>
-      <c r="AR73" s="126" t="n">
+      <c r="AR73" s="127" t="n">
         <f aca="false">+SUM(AR84)-SUM(AR89,AR91,AR92,AR94)</f>
         <v>-8277.03652915624</v>
       </c>
-      <c r="AS73" s="126" t="n">
+      <c r="AS73" s="127" t="n">
         <f aca="false">+SUM(AS84)-SUM(AS89,AS91,AS92,AS94)</f>
         <v>-9305.62009732372</v>
       </c>
-      <c r="AT73" s="126" t="n">
+      <c r="AT73" s="127" t="n">
         <f aca="false">+SUM(AT84)-SUM(AT89,AT91,AT92,AT94)</f>
         <v>-10460.5927643072</v>
       </c>
-      <c r="AU73" s="126" t="n">
+      <c r="AU73" s="127" t="n">
         <f aca="false">+SUM(AU84)-SUM(AU89,AU91,AU92,AU94)</f>
         <v>-11652.3464207772</v>
       </c>
-      <c r="AV73" s="126" t="n">
+      <c r="AV73" s="127" t="n">
         <f aca="false">+SUM(AV84)-SUM(AV89,AV91,AV92,AV94)</f>
         <v>-12978.1336110213</v>
       </c>
-      <c r="AW73" s="126" t="n">
+      <c r="AW73" s="127" t="n">
         <f aca="false">+SUM(AW84)-SUM(AW89,AW91,AW92,AW94)</f>
         <v>-14485.4806628812</v>
       </c>
-      <c r="AX73" s="126" t="n">
+      <c r="AX73" s="127" t="n">
         <f aca="false">+SUM(AX84)-SUM(AX89,AX91,AX92,AX94)</f>
         <v>-16167.408649457</v>
       </c>
-      <c r="AY73" s="126" t="n">
+      <c r="AY73" s="127" t="n">
         <f aca="false">+SUM(AY84)-SUM(AY89,AY91,AY92,AY94)</f>
         <v>-18044.0864770586</v>
       </c>
-      <c r="AZ73" s="126"/>
-      <c r="BA73" s="126"/>
-      <c r="BB73" s="126"/>
+      <c r="AZ73" s="127"/>
+      <c r="BA73" s="127"/>
+      <c r="BB73" s="127"/>
       <c r="BC73" s="102" t="s">
         <v>113</v>
       </c>
       <c r="BD73" s="103" t="n">
         <f aca="false">+BD71/Main!G6-1</f>
-        <v>0.119761615172738</v>
-      </c>
-      <c r="BE73" s="126"/>
-      <c r="BF73" s="126"/>
-      <c r="BG73" s="126"/>
-      <c r="BH73" s="126"/>
-      <c r="BI73" s="126"/>
-      <c r="BJ73" s="126"/>
-      <c r="BK73" s="126"/>
-      <c r="BL73" s="126"/>
-      <c r="BM73" s="126"/>
-      <c r="BN73" s="126"/>
-      <c r="BO73" s="126"/>
-      <c r="BP73" s="126"/>
-      <c r="BQ73" s="126"/>
-      <c r="BR73" s="126"/>
-      <c r="BS73" s="126"/>
-      <c r="BT73" s="126"/>
-      <c r="BU73" s="126"/>
-      <c r="BV73" s="126"/>
-      <c r="BW73" s="126"/>
-      <c r="BX73" s="126"/>
-      <c r="BY73" s="126"/>
-      <c r="BZ73" s="126"/>
-      <c r="CA73" s="126"/>
-      <c r="CB73" s="126"/>
-      <c r="CC73" s="126"/>
-      <c r="CD73" s="126"/>
-      <c r="CE73" s="126"/>
-      <c r="CF73" s="126"/>
-      <c r="CG73" s="126"/>
-      <c r="CH73" s="126"/>
-      <c r="CI73" s="126"/>
-      <c r="CJ73" s="126"/>
-      <c r="CK73" s="126"/>
-      <c r="CL73" s="126"/>
-      <c r="CM73" s="126"/>
-      <c r="CN73" s="126"/>
-      <c r="CO73" s="126"/>
-      <c r="CP73" s="126"/>
-      <c r="CQ73" s="126"/>
-      <c r="CR73" s="126"/>
-      <c r="CS73" s="126"/>
-      <c r="CT73" s="126"/>
-      <c r="CU73" s="126"/>
-      <c r="CV73" s="126"/>
-      <c r="CW73" s="126"/>
-      <c r="CX73" s="126"/>
-      <c r="CY73" s="126"/>
-      <c r="CZ73" s="126"/>
-      <c r="DA73" s="126"/>
-      <c r="DB73" s="126"/>
-      <c r="DC73" s="126"/>
-      <c r="DD73" s="126"/>
-      <c r="DE73" s="126"/>
-      <c r="DF73" s="126"/>
-      <c r="DG73" s="126"/>
-      <c r="DH73" s="126"/>
-      <c r="DI73" s="126"/>
-      <c r="DJ73" s="126"/>
-      <c r="DK73" s="126"/>
-      <c r="DL73" s="126"/>
-      <c r="DM73" s="126"/>
-      <c r="DN73" s="126"/>
+        <v>0.158889016687439</v>
+      </c>
+      <c r="BE73" s="127"/>
+      <c r="BF73" s="127"/>
+      <c r="BG73" s="127"/>
+      <c r="BH73" s="127"/>
+      <c r="BI73" s="127"/>
+      <c r="BJ73" s="127"/>
+      <c r="BK73" s="127"/>
+      <c r="BL73" s="127"/>
+      <c r="BM73" s="127"/>
+      <c r="BN73" s="127"/>
+      <c r="BO73" s="127"/>
+      <c r="BP73" s="127"/>
+      <c r="BQ73" s="127"/>
+      <c r="BR73" s="127"/>
+      <c r="BS73" s="127"/>
+      <c r="BT73" s="127"/>
+      <c r="BU73" s="127"/>
+      <c r="BV73" s="127"/>
+      <c r="BW73" s="127"/>
+      <c r="BX73" s="127"/>
+      <c r="BY73" s="127"/>
+      <c r="BZ73" s="127"/>
+      <c r="CA73" s="127"/>
+      <c r="CB73" s="127"/>
+      <c r="CC73" s="127"/>
+      <c r="CD73" s="127"/>
+      <c r="CE73" s="127"/>
+      <c r="CF73" s="127"/>
+      <c r="CG73" s="127"/>
+      <c r="CH73" s="127"/>
+      <c r="CI73" s="127"/>
+      <c r="CJ73" s="127"/>
+      <c r="CK73" s="127"/>
+      <c r="CL73" s="127"/>
+      <c r="CM73" s="127"/>
+      <c r="CN73" s="127"/>
+      <c r="CO73" s="127"/>
+      <c r="CP73" s="127"/>
+      <c r="CQ73" s="127"/>
+      <c r="CR73" s="127"/>
+      <c r="CS73" s="127"/>
+      <c r="CT73" s="127"/>
+      <c r="CU73" s="127"/>
+      <c r="CV73" s="127"/>
+      <c r="CW73" s="127"/>
+      <c r="CX73" s="127"/>
+      <c r="CY73" s="127"/>
+      <c r="CZ73" s="127"/>
+      <c r="DA73" s="127"/>
+      <c r="DB73" s="127"/>
+      <c r="DC73" s="127"/>
+      <c r="DD73" s="127"/>
+      <c r="DE73" s="127"/>
+      <c r="DF73" s="127"/>
+      <c r="DG73" s="127"/>
+      <c r="DH73" s="127"/>
+      <c r="DI73" s="127"/>
+      <c r="DJ73" s="127"/>
+      <c r="DK73" s="127"/>
+      <c r="DL73" s="127"/>
+      <c r="DM73" s="127"/>
+      <c r="DN73" s="127"/>
       <c r="DO73" s="42"/>
     </row>
     <row r="74" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="B74" s="122"/>
-      <c r="C74" s="122"/>
-      <c r="D74" s="122"/>
-      <c r="E74" s="122"/>
-      <c r="F74" s="122"/>
-      <c r="G74" s="122"/>
-      <c r="H74" s="122"/>
-      <c r="I74" s="122"/>
-      <c r="J74" s="122"/>
-      <c r="K74" s="122"/>
-      <c r="L74" s="122"/>
-      <c r="M74" s="122"/>
-      <c r="N74" s="122"/>
-      <c r="O74" s="122"/>
-      <c r="P74" s="122"/>
-      <c r="Q74" s="122"/>
-      <c r="R74" s="122"/>
-      <c r="S74" s="122"/>
-      <c r="T74" s="122"/>
-      <c r="U74" s="122"/>
-      <c r="V74" s="122"/>
-      <c r="W74" s="122"/>
-      <c r="X74" s="122"/>
-      <c r="Y74" s="122"/>
+      <c r="B74" s="123"/>
+      <c r="C74" s="123"/>
+      <c r="D74" s="123"/>
+      <c r="E74" s="123"/>
+      <c r="F74" s="123"/>
+      <c r="G74" s="123"/>
+      <c r="H74" s="123"/>
+      <c r="I74" s="123"/>
+      <c r="J74" s="123"/>
+      <c r="K74" s="123"/>
+      <c r="L74" s="123"/>
+      <c r="M74" s="123"/>
+      <c r="N74" s="123"/>
+      <c r="O74" s="123"/>
+      <c r="P74" s="123"/>
+      <c r="Q74" s="123"/>
+      <c r="R74" s="123"/>
+      <c r="S74" s="123"/>
+      <c r="T74" s="123"/>
+      <c r="U74" s="123"/>
+      <c r="V74" s="123"/>
+      <c r="W74" s="123"/>
+      <c r="X74" s="123"/>
+      <c r="Y74" s="123"/>
       <c r="Z74" s="6"/>
       <c r="AA74" s="6"/>
       <c r="AB74" s="6"/>
@@ -23194,72 +23198,72 @@
       <c r="AF74" s="6"/>
       <c r="AG74" s="6"/>
       <c r="AH74" s="6"/>
-      <c r="AI74" s="122"/>
-      <c r="AJ74" s="125" t="n">
+      <c r="AI74" s="123"/>
+      <c r="AJ74" s="126" t="n">
         <f aca="false">+AJ69+AJ120-AJ133-(AJ73-AI73)</f>
         <v>5107.64223695318</v>
       </c>
-      <c r="AK74" s="125" t="n">
+      <c r="AK74" s="126" t="n">
         <f aca="false">+AK69+AK120-AK133-(AK73-AJ73)</f>
         <v>3554.45553672531</v>
       </c>
-      <c r="AL74" s="125" t="n">
+      <c r="AL74" s="126" t="n">
         <f aca="false">+AL69+AL120-AL133-(AL73-AK73)</f>
         <v>7026.33007826613</v>
       </c>
-      <c r="AM74" s="125" t="n">
+      <c r="AM74" s="126" t="n">
         <f aca="false">+AM69+AM120-AM133-(AM73-AL73)</f>
         <v>8769.39560538267</v>
       </c>
-      <c r="AN74" s="125" t="n">
+      <c r="AN74" s="126" t="n">
         <f aca="false">+AN69+AN120-AN133-(AN73-AM73)</f>
         <v>11716.3875414518</v>
       </c>
-      <c r="AO74" s="125" t="n">
+      <c r="AO74" s="126" t="n">
         <f aca="false">+AO69+AO120-AO133-(AO73-AN73)</f>
         <v>16479.4188709796</v>
       </c>
-      <c r="AP74" s="125" t="n">
+      <c r="AP74" s="126" t="n">
         <f aca="false">+AP69+AP120-AP133-(AP73-AO73)</f>
         <v>20710.5106853634</v>
       </c>
-      <c r="AQ74" s="125" t="n">
+      <c r="AQ74" s="126" t="n">
         <f aca="false">+AQ69+AQ120-AQ133-(AQ73-AP73)</f>
         <v>23975.3525427946</v>
       </c>
-      <c r="AR74" s="125" t="n">
+      <c r="AR74" s="126" t="n">
         <f aca="false">+AR69+AR120-AR133-(AR73-AQ73)</f>
         <v>27439.4641877223</v>
       </c>
-      <c r="AS74" s="125" t="n">
+      <c r="AS74" s="126" t="n">
         <f aca="false">+AS69+AS120-AS133-(AS73-AR73)</f>
         <v>29316.3828693535</v>
       </c>
-      <c r="AT74" s="125" t="n">
+      <c r="AT74" s="126" t="n">
         <f aca="false">+AT69+AT120-AT133-(AT73-AS73)</f>
         <v>33224.3616328872</v>
       </c>
-      <c r="AU74" s="125" t="n">
+      <c r="AU74" s="126" t="n">
         <f aca="false">+AU69+AU120-AU133-(AU73-AT73)</f>
         <v>37205.9926807257</v>
       </c>
-      <c r="AV74" s="125" t="n">
+      <c r="AV74" s="126" t="n">
         <f aca="false">+AV69+AV120-AV133-(AV73-AU73)</f>
         <v>41764.5805216751</v>
       </c>
-      <c r="AW74" s="125" t="n">
+      <c r="AW74" s="126" t="n">
         <f aca="false">+AW69+AW120-AW133-(AW73-AV73)</f>
         <v>46908.1928999848</v>
       </c>
-      <c r="AX74" s="125" t="n">
+      <c r="AX74" s="126" t="n">
         <f aca="false">+AX69+AX120-AX133-(AX73-AW73)</f>
         <v>52647.0188947166</v>
       </c>
-      <c r="AY74" s="125" t="n">
+      <c r="AY74" s="126" t="n">
         <f aca="false">+AY69+AY120-AY133-(AY73-AX73)</f>
         <v>58465.7844087634</v>
       </c>
-      <c r="AZ74" s="113"/>
+      <c r="AZ74" s="114"/>
       <c r="BA74" s="6"/>
       <c r="BB74" s="6"/>
       <c r="BC74" s="6"/>
@@ -23330,30 +23334,30 @@
     </row>
     <row r="75" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="36"/>
-      <c r="B75" s="122"/>
-      <c r="C75" s="122"/>
-      <c r="D75" s="122"/>
-      <c r="E75" s="122"/>
-      <c r="F75" s="122"/>
-      <c r="G75" s="122"/>
-      <c r="H75" s="122"/>
-      <c r="I75" s="122"/>
-      <c r="J75" s="122"/>
-      <c r="K75" s="122"/>
-      <c r="L75" s="122"/>
-      <c r="M75" s="122"/>
-      <c r="N75" s="122"/>
-      <c r="O75" s="122"/>
-      <c r="P75" s="122"/>
-      <c r="Q75" s="122"/>
-      <c r="R75" s="122"/>
-      <c r="S75" s="122"/>
-      <c r="T75" s="122"/>
-      <c r="U75" s="122"/>
-      <c r="V75" s="122"/>
-      <c r="W75" s="122"/>
-      <c r="X75" s="122"/>
-      <c r="Y75" s="122"/>
+      <c r="B75" s="123"/>
+      <c r="C75" s="123"/>
+      <c r="D75" s="123"/>
+      <c r="E75" s="123"/>
+      <c r="F75" s="123"/>
+      <c r="G75" s="123"/>
+      <c r="H75" s="123"/>
+      <c r="I75" s="123"/>
+      <c r="J75" s="123"/>
+      <c r="K75" s="123"/>
+      <c r="L75" s="123"/>
+      <c r="M75" s="123"/>
+      <c r="N75" s="123"/>
+      <c r="O75" s="123"/>
+      <c r="P75" s="123"/>
+      <c r="Q75" s="123"/>
+      <c r="R75" s="123"/>
+      <c r="S75" s="123"/>
+      <c r="T75" s="123"/>
+      <c r="U75" s="123"/>
+      <c r="V75" s="123"/>
+      <c r="W75" s="123"/>
+      <c r="X75" s="123"/>
+      <c r="Y75" s="123"/>
       <c r="Z75" s="6"/>
       <c r="AA75" s="6"/>
       <c r="AB75" s="6"/>
@@ -23363,12 +23367,12 @@
       <c r="AF75" s="6"/>
       <c r="AG75" s="6"/>
       <c r="AH75" s="6"/>
-      <c r="AI75" s="122"/>
-      <c r="AJ75" s="122"/>
-      <c r="AK75" s="122"/>
-      <c r="AL75" s="122"/>
-      <c r="AM75" s="122"/>
-      <c r="AN75" s="122"/>
+      <c r="AI75" s="123"/>
+      <c r="AJ75" s="123"/>
+      <c r="AK75" s="123"/>
+      <c r="AL75" s="123"/>
+      <c r="AM75" s="123"/>
+      <c r="AN75" s="123"/>
       <c r="AO75" s="6"/>
       <c r="AP75" s="6"/>
       <c r="AQ75" s="6"/>
@@ -23379,12 +23383,12 @@
       <c r="AV75" s="6"/>
       <c r="AW75" s="6"/>
       <c r="AX75" s="6"/>
-      <c r="AY75" s="113"/>
-      <c r="AZ75" s="113"/>
+      <c r="AY75" s="114"/>
+      <c r="AZ75" s="114"/>
       <c r="BA75" s="6"/>
       <c r="BB75" s="6"/>
-      <c r="BC75" s="113"/>
-      <c r="BD75" s="113"/>
+      <c r="BC75" s="114"/>
+      <c r="BD75" s="114"/>
       <c r="BE75" s="6"/>
       <c r="BF75" s="6"/>
       <c r="BG75" s="6"/>
@@ -23495,75 +23499,75 @@
       <c r="AQ76" s="6"/>
       <c r="AR76" s="6"/>
       <c r="AS76" s="6"/>
-      <c r="AX76" s="113"/>
+      <c r="AX76" s="114"/>
       <c r="AY76" s="6"/>
       <c r="AZ76" s="6"/>
-      <c r="BA76" s="113"/>
-      <c r="BB76" s="113"/>
+      <c r="BA76" s="114"/>
+      <c r="BB76" s="114"/>
       <c r="BC76" s="6"/>
       <c r="BD76" s="6"/>
-      <c r="BE76" s="113"/>
-      <c r="BF76" s="113"/>
-      <c r="BG76" s="113"/>
-      <c r="BH76" s="113"/>
-      <c r="BI76" s="113"/>
-      <c r="BJ76" s="113"/>
-      <c r="BK76" s="113"/>
-      <c r="BL76" s="113"/>
-      <c r="BM76" s="113"/>
-      <c r="BN76" s="113"/>
-      <c r="BO76" s="113"/>
-      <c r="BP76" s="113"/>
-      <c r="BQ76" s="113"/>
-      <c r="BR76" s="113"/>
-      <c r="BS76" s="113"/>
-      <c r="BT76" s="113"/>
-      <c r="BU76" s="113"/>
-      <c r="BV76" s="113"/>
-      <c r="BW76" s="113"/>
-      <c r="BX76" s="113"/>
-      <c r="BY76" s="113"/>
-      <c r="BZ76" s="113"/>
-      <c r="CA76" s="113"/>
-      <c r="CB76" s="113"/>
-      <c r="CC76" s="113"/>
-      <c r="CD76" s="113"/>
-      <c r="CE76" s="113"/>
-      <c r="CF76" s="113"/>
-      <c r="CG76" s="113"/>
-      <c r="CH76" s="113"/>
-      <c r="CI76" s="113"/>
-      <c r="CJ76" s="113"/>
-      <c r="CK76" s="113"/>
-      <c r="CL76" s="113"/>
-      <c r="CM76" s="113"/>
-      <c r="CN76" s="113"/>
-      <c r="CO76" s="113"/>
-      <c r="CP76" s="113"/>
-      <c r="CQ76" s="113"/>
-      <c r="CR76" s="113"/>
-      <c r="CS76" s="113"/>
-      <c r="CT76" s="113"/>
-      <c r="CU76" s="113"/>
-      <c r="CV76" s="113"/>
-      <c r="CW76" s="113"/>
-      <c r="CX76" s="113"/>
-      <c r="CY76" s="113"/>
-      <c r="CZ76" s="113"/>
-      <c r="DA76" s="113"/>
-      <c r="DB76" s="113"/>
-      <c r="DC76" s="113"/>
-      <c r="DD76" s="113"/>
-      <c r="DE76" s="113"/>
-      <c r="DF76" s="113"/>
-      <c r="DG76" s="113"/>
-      <c r="DH76" s="113"/>
-      <c r="DI76" s="113"/>
-      <c r="DJ76" s="113"/>
-      <c r="DK76" s="113"/>
-      <c r="DL76" s="113"/>
-      <c r="DM76" s="113"/>
-      <c r="DN76" s="113"/>
+      <c r="BE76" s="114"/>
+      <c r="BF76" s="114"/>
+      <c r="BG76" s="114"/>
+      <c r="BH76" s="114"/>
+      <c r="BI76" s="114"/>
+      <c r="BJ76" s="114"/>
+      <c r="BK76" s="114"/>
+      <c r="BL76" s="114"/>
+      <c r="BM76" s="114"/>
+      <c r="BN76" s="114"/>
+      <c r="BO76" s="114"/>
+      <c r="BP76" s="114"/>
+      <c r="BQ76" s="114"/>
+      <c r="BR76" s="114"/>
+      <c r="BS76" s="114"/>
+      <c r="BT76" s="114"/>
+      <c r="BU76" s="114"/>
+      <c r="BV76" s="114"/>
+      <c r="BW76" s="114"/>
+      <c r="BX76" s="114"/>
+      <c r="BY76" s="114"/>
+      <c r="BZ76" s="114"/>
+      <c r="CA76" s="114"/>
+      <c r="CB76" s="114"/>
+      <c r="CC76" s="114"/>
+      <c r="CD76" s="114"/>
+      <c r="CE76" s="114"/>
+      <c r="CF76" s="114"/>
+      <c r="CG76" s="114"/>
+      <c r="CH76" s="114"/>
+      <c r="CI76" s="114"/>
+      <c r="CJ76" s="114"/>
+      <c r="CK76" s="114"/>
+      <c r="CL76" s="114"/>
+      <c r="CM76" s="114"/>
+      <c r="CN76" s="114"/>
+      <c r="CO76" s="114"/>
+      <c r="CP76" s="114"/>
+      <c r="CQ76" s="114"/>
+      <c r="CR76" s="114"/>
+      <c r="CS76" s="114"/>
+      <c r="CT76" s="114"/>
+      <c r="CU76" s="114"/>
+      <c r="CV76" s="114"/>
+      <c r="CW76" s="114"/>
+      <c r="CX76" s="114"/>
+      <c r="CY76" s="114"/>
+      <c r="CZ76" s="114"/>
+      <c r="DA76" s="114"/>
+      <c r="DB76" s="114"/>
+      <c r="DC76" s="114"/>
+      <c r="DD76" s="114"/>
+      <c r="DE76" s="114"/>
+      <c r="DF76" s="114"/>
+      <c r="DG76" s="114"/>
+      <c r="DH76" s="114"/>
+      <c r="DI76" s="114"/>
+      <c r="DJ76" s="114"/>
+      <c r="DK76" s="114"/>
+      <c r="DL76" s="114"/>
+      <c r="DM76" s="114"/>
+      <c r="DN76" s="114"/>
       <c r="DO76" s="42"/>
     </row>
     <row r="77" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23680,191 +23684,191 @@
       <c r="DO77" s="42"/>
     </row>
     <row r="78" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="121" t="s">
+      <c r="A78" s="122" t="s">
         <v>137</v>
       </c>
-      <c r="B78" s="121" t="n">
+      <c r="B78" s="122" t="n">
         <f aca="false">B80+B81-B97</f>
         <v>-9018.8</v>
       </c>
-      <c r="C78" s="121" t="n">
+      <c r="C78" s="122" t="n">
         <f aca="false">C80+C81-C97</f>
         <v>-8141.7</v>
       </c>
-      <c r="D78" s="121" t="n">
+      <c r="D78" s="122" t="n">
         <f aca="false">D80+D81-D97</f>
         <v>-7155.3</v>
       </c>
-      <c r="E78" s="121" t="n">
+      <c r="E78" s="122" t="n">
         <f aca="false">E80+E81-E97</f>
         <v>-7603.5</v>
       </c>
-      <c r="F78" s="121" t="n">
+      <c r="F78" s="122" t="n">
         <f aca="false">F80+F81-F97</f>
         <v>-6456.8</v>
       </c>
-      <c r="G78" s="121" t="n">
+      <c r="G78" s="122" t="n">
         <f aca="false">G80+G81-G97</f>
         <v>-7149.3</v>
       </c>
-      <c r="H78" s="121" t="n">
+      <c r="H78" s="122" t="n">
         <f aca="false">H80+H81-H97</f>
         <v>-7267</v>
       </c>
-      <c r="I78" s="121" t="n">
+      <c r="I78" s="122" t="n">
         <f aca="false">I80+I81-I97</f>
         <v>-8665.2</v>
       </c>
-      <c r="J78" s="121" t="n">
+      <c r="J78" s="122" t="n">
         <f aca="false">J80+J81-J97</f>
         <v>-8525.6</v>
       </c>
-      <c r="K78" s="121" t="n">
+      <c r="K78" s="122" t="n">
         <f aca="false">K80+K81-K97</f>
         <v>-8403.9</v>
       </c>
-      <c r="L78" s="121" t="n">
+      <c r="L78" s="122" t="n">
         <f aca="false">L80+L81-L97</f>
         <v>-7774.4</v>
       </c>
-      <c r="M78" s="121" t="n">
+      <c r="M78" s="122" t="n">
         <f aca="false">M80+M81-M97</f>
         <v>-8294.7</v>
       </c>
-      <c r="N78" s="121" t="n">
+      <c r="N78" s="122" t="n">
         <f aca="false">N80+N81-N97</f>
         <v>-6209.6</v>
       </c>
-      <c r="O78" s="121" t="n">
+      <c r="O78" s="122" t="n">
         <f aca="false">O80+O81-O97</f>
         <v>-5493.2</v>
       </c>
-      <c r="P78" s="121" t="n">
+      <c r="P78" s="122" t="n">
         <f aca="false">P80+P81-P97</f>
         <v>-6033.3</v>
       </c>
-      <c r="Q78" s="121" t="n">
+      <c r="Q78" s="122" t="n">
         <f aca="false">Q80+Q81-Q97</f>
         <v>-7005.53</v>
       </c>
-      <c r="R78" s="121" t="n">
+      <c r="R78" s="122" t="n">
         <f aca="false">R80+R81-R97</f>
         <v>-6171.4</v>
       </c>
-      <c r="S78" s="121" t="n">
+      <c r="S78" s="122" t="n">
         <f aca="false">S80+S81-S97</f>
         <v>-5524.2</v>
       </c>
-      <c r="T78" s="121" t="n">
+      <c r="T78" s="122" t="n">
         <f aca="false">T80+T81-T97</f>
         <v>-4937</v>
       </c>
-      <c r="U78" s="121" t="n">
+      <c r="U78" s="122" t="n">
         <f aca="false">U80+U81-U97</f>
         <v>-4214.6</v>
       </c>
-      <c r="V78" s="121" t="n">
+      <c r="V78" s="122" t="n">
         <f aca="false">V80+V81-V97</f>
         <v>-5640.1</v>
       </c>
-      <c r="W78" s="121" t="n">
+      <c r="W78" s="122" t="n">
         <f aca="false">W80+W81-W97</f>
         <v>-6062.8</v>
       </c>
-      <c r="X78" s="121" t="n">
+      <c r="X78" s="122" t="n">
         <f aca="false">X80+X81-X97</f>
         <v>-5139</v>
       </c>
-      <c r="Y78" s="121" t="n">
+      <c r="Y78" s="122" t="n">
         <f aca="false">Y80+Y81-Y97</f>
         <v>-4401.62</v>
       </c>
-      <c r="Z78" s="121" t="n">
+      <c r="Z78" s="122" t="n">
         <f aca="false">Z80+Z81-Z97</f>
         <v>-1072.881</v>
       </c>
-      <c r="AA78" s="121" t="n">
+      <c r="AA78" s="122" t="n">
         <f aca="false">AA80+AA81-AA97</f>
         <v>-2697.638</v>
       </c>
-      <c r="AB78" s="121" t="n">
+      <c r="AB78" s="122" t="n">
         <f aca="false">AB80+AB81-AB97</f>
         <v>-13361.331</v>
       </c>
-      <c r="AC78" s="121" t="n">
+      <c r="AC78" s="122" t="n">
         <f aca="false">AC80+AC81-AC97</f>
         <v>-13361.331</v>
       </c>
-      <c r="AD78" s="113"/>
-      <c r="AE78" s="113"/>
-      <c r="AF78" s="113"/>
-      <c r="AG78" s="113"/>
-      <c r="AH78" s="113"/>
-      <c r="AI78" s="121" t="n">
+      <c r="AD78" s="114"/>
+      <c r="AE78" s="114"/>
+      <c r="AF78" s="114"/>
+      <c r="AG78" s="114"/>
+      <c r="AH78" s="114"/>
+      <c r="AI78" s="122" t="n">
         <f aca="false">AI80+AI81-AI97</f>
         <v>-7603.5</v>
       </c>
-      <c r="AJ78" s="121" t="n">
+      <c r="AJ78" s="122" t="n">
         <f aca="false">AJ80+AJ81-AJ97</f>
         <v>-8665.2</v>
       </c>
-      <c r="AK78" s="121" t="n">
+      <c r="AK78" s="122" t="n">
         <f aca="false">AK80+AK81-AK97</f>
         <v>-8294.7</v>
       </c>
-      <c r="AL78" s="121" t="n">
+      <c r="AL78" s="122" t="n">
         <f aca="false">AL80+AL81-AL97</f>
         <v>-7005.53</v>
       </c>
-      <c r="AM78" s="121" t="n">
+      <c r="AM78" s="122" t="n">
         <f aca="false">AM80+AM81-AM97</f>
         <v>-4214.6</v>
       </c>
-      <c r="AN78" s="121" t="n">
+      <c r="AN78" s="122" t="n">
         <f aca="false">AN80+AN81-AN97</f>
         <v>-4401.62</v>
       </c>
-      <c r="AO78" s="121" t="n">
+      <c r="AO78" s="122" t="n">
         <f aca="false">AN78+AO40</f>
         <v>8764.30464197</v>
       </c>
-      <c r="AP78" s="121" t="n">
+      <c r="AP78" s="122" t="n">
         <f aca="false">AO78+AP40</f>
         <v>24562.9555503177</v>
       </c>
-      <c r="AQ78" s="121" t="n">
+      <c r="AQ78" s="122" t="n">
         <f aca="false">AP78+AQ40</f>
         <v>43057.2694065646</v>
       </c>
-      <c r="AR78" s="121" t="n">
+      <c r="AR78" s="122" t="n">
         <f aca="false">AQ78+AR40</f>
         <v>64355.2446797087</v>
       </c>
-      <c r="AS78" s="121" t="n">
+      <c r="AS78" s="122" t="n">
         <f aca="false">AR78+AS40</f>
         <v>86966.2561883871</v>
       </c>
-      <c r="AT78" s="121" t="n">
+      <c r="AT78" s="122" t="n">
         <f aca="false">AS78+AT40</f>
         <v>112726.999406807</v>
       </c>
-      <c r="AU78" s="121" t="n">
+      <c r="AU78" s="122" t="n">
         <f aca="false">AT78+AU40</f>
         <v>141792.106099186</v>
       </c>
-      <c r="AV78" s="121" t="n">
+      <c r="AV78" s="122" t="n">
         <f aca="false">AU78+AV40</f>
         <v>174570.921211848</v>
       </c>
-      <c r="AW78" s="121" t="n">
+      <c r="AW78" s="122" t="n">
         <f aca="false">AV78+AW40</f>
         <v>211522.748506252</v>
       </c>
-      <c r="AX78" s="121" t="n">
+      <c r="AX78" s="122" t="n">
         <f aca="false">AW78+AX40</f>
         <v>253162.877402979</v>
       </c>
-      <c r="AY78" s="121" t="n">
+      <c r="AY78" s="122" t="n">
         <f aca="false">AX78+AY40</f>
         <v>299454.495891941</v>
       </c>
@@ -23893,7 +23897,7 @@
       <c r="T79" s="6"/>
       <c r="U79" s="6"/>
       <c r="V79" s="6"/>
-      <c r="W79" s="127"/>
+      <c r="W79" s="128"/>
       <c r="X79" s="6"/>
       <c r="Y79" s="6"/>
       <c r="AD79" s="6"/>
@@ -24452,47 +24456,47 @@
       <c r="AN84" s="58" t="n">
         <v>3958</v>
       </c>
-      <c r="AO84" s="128" t="n">
+      <c r="AO84" s="129" t="n">
         <f aca="false">+AO16*0.085</f>
         <v>4366.6820415</v>
       </c>
-      <c r="AP84" s="128" t="n">
+      <c r="AP84" s="129" t="n">
         <f aca="false">+AP16*0.085</f>
         <v>4964.9174811855</v>
       </c>
-      <c r="AQ84" s="128" t="n">
+      <c r="AQ84" s="129" t="n">
         <f aca="false">+AQ16*0.085</f>
         <v>5610.35675373962</v>
       </c>
-      <c r="AR84" s="128" t="n">
+      <c r="AR84" s="129" t="n">
         <f aca="false">+AR16*0.085</f>
         <v>6339.70313172577</v>
       </c>
-      <c r="AS84" s="128" t="n">
+      <c r="AS84" s="129" t="n">
         <f aca="false">+AS16*0.085</f>
         <v>7100.46750753286</v>
       </c>
-      <c r="AT84" s="128" t="n">
+      <c r="AT84" s="129" t="n">
         <f aca="false">+AT16*0.085</f>
         <v>7952.52360843681</v>
       </c>
-      <c r="AU84" s="128" t="n">
+      <c r="AU84" s="129" t="n">
         <f aca="false">+AU16*0.085</f>
         <v>8827.30120536485</v>
       </c>
-      <c r="AV84" s="128" t="n">
+      <c r="AV84" s="129" t="n">
         <f aca="false">+AV16*0.085</f>
         <v>9798.30433795499</v>
       </c>
-      <c r="AW84" s="128" t="n">
+      <c r="AW84" s="129" t="n">
         <f aca="false">+AW16*0.085</f>
         <v>10876.11781513</v>
       </c>
-      <c r="AX84" s="128" t="n">
+      <c r="AX84" s="129" t="n">
         <f aca="false">+AX16*0.085</f>
         <v>12072.4907747943</v>
       </c>
-      <c r="AY84" s="128" t="n">
+      <c r="AY84" s="129" t="n">
         <f aca="false">+AY16*0.085</f>
         <v>13400.4647600217</v>
       </c>
@@ -25065,47 +25069,47 @@
       <c r="AN89" s="58" t="n">
         <v>4084.8</v>
       </c>
-      <c r="AO89" s="128" t="n">
+      <c r="AO89" s="129" t="n">
         <f aca="false">+AO16*0.095</f>
         <v>4880.4093405</v>
       </c>
-      <c r="AP89" s="128" t="n">
+      <c r="AP89" s="129" t="n">
         <f aca="false">+AP16*0.095</f>
         <v>5549.0254201485</v>
       </c>
-      <c r="AQ89" s="128" t="n">
+      <c r="AQ89" s="129" t="n">
         <f aca="false">+AQ16*0.095</f>
         <v>6270.39872476781</v>
       </c>
-      <c r="AR89" s="128" t="n">
+      <c r="AR89" s="129" t="n">
         <f aca="false">+AR16*0.095</f>
         <v>7085.55055898762</v>
       </c>
-      <c r="AS89" s="128" t="n">
+      <c r="AS89" s="129" t="n">
         <f aca="false">+AS16*0.095</f>
         <v>7935.81662606614</v>
       </c>
-      <c r="AT89" s="128" t="n">
+      <c r="AT89" s="129" t="n">
         <f aca="false">+AT16*0.095</f>
         <v>8888.11462119408</v>
       </c>
-      <c r="AU89" s="128" t="n">
+      <c r="AU89" s="129" t="n">
         <f aca="false">+AU16*0.095</f>
         <v>9865.80722952543</v>
       </c>
-      <c r="AV89" s="128" t="n">
+      <c r="AV89" s="129" t="n">
         <f aca="false">+AV16*0.095</f>
         <v>10951.0460247732</v>
       </c>
-      <c r="AW89" s="128" t="n">
+      <c r="AW89" s="129" t="n">
         <f aca="false">+AW16*0.095</f>
         <v>12155.6610874983</v>
       </c>
-      <c r="AX89" s="128" t="n">
+      <c r="AX89" s="129" t="n">
         <f aca="false">+AX16*0.095</f>
         <v>13492.7838071231</v>
       </c>
-      <c r="AY89" s="128" t="n">
+      <c r="AY89" s="129" t="n">
         <f aca="false">+AY16*0.095</f>
         <v>14976.9900259066</v>
       </c>
@@ -25539,47 +25543,47 @@
       <c r="AN92" s="58" t="n">
         <v>3220.8</v>
       </c>
-      <c r="AO92" s="128" t="n">
+      <c r="AO92" s="129" t="n">
         <f aca="false">+AO16*0.05</f>
         <v>2568.636495</v>
       </c>
-      <c r="AP92" s="128" t="n">
+      <c r="AP92" s="129" t="n">
         <f aca="false">+AP16*0.05</f>
         <v>2920.539694815</v>
       </c>
-      <c r="AQ92" s="128" t="n">
+      <c r="AQ92" s="129" t="n">
         <f aca="false">+AQ16*0.05</f>
         <v>3300.20985514095</v>
       </c>
-      <c r="AR92" s="128" t="n">
+      <c r="AR92" s="129" t="n">
         <f aca="false">+AR16*0.05</f>
         <v>3729.23713630928</v>
       </c>
-      <c r="AS92" s="128" t="n">
+      <c r="AS92" s="129" t="n">
         <f aca="false">+AS16*0.05</f>
         <v>4176.74559266639</v>
       </c>
-      <c r="AT92" s="128" t="n">
+      <c r="AT92" s="129" t="n">
         <f aca="false">+AT16*0.05</f>
         <v>4677.95506378636</v>
       </c>
-      <c r="AU92" s="128" t="n">
+      <c r="AU92" s="129" t="n">
         <f aca="false">+AU16*0.05</f>
         <v>5192.53012080286</v>
       </c>
-      <c r="AV92" s="128" t="n">
+      <c r="AV92" s="129" t="n">
         <f aca="false">+AV16*0.05</f>
         <v>5763.70843409117</v>
       </c>
-      <c r="AW92" s="128" t="n">
+      <c r="AW92" s="129" t="n">
         <f aca="false">+AW16*0.05</f>
         <v>6397.7163618412</v>
       </c>
-      <c r="AX92" s="128" t="n">
+      <c r="AX92" s="129" t="n">
         <f aca="false">+AX16*0.05</f>
         <v>7101.46516164373</v>
       </c>
-      <c r="AY92" s="128" t="n">
+      <c r="AY92" s="129" t="n">
         <f aca="false">+AY16*0.05</f>
         <v>7882.62632942454</v>
       </c>
@@ -25867,47 +25871,47 @@
       <c r="AN94" s="58" t="n">
         <v>1775.7</v>
       </c>
-      <c r="AO94" s="128" t="n">
+      <c r="AO94" s="129" t="n">
         <f aca="false">+AO16*0.03</f>
         <v>1541.181897</v>
       </c>
-      <c r="AP94" s="128" t="n">
+      <c r="AP94" s="129" t="n">
         <f aca="false">+AP16*0.03</f>
         <v>1752.323816889</v>
       </c>
-      <c r="AQ94" s="128" t="n">
+      <c r="AQ94" s="129" t="n">
         <f aca="false">+AQ16*0.03</f>
         <v>1980.12591308457</v>
       </c>
-      <c r="AR94" s="128" t="n">
+      <c r="AR94" s="129" t="n">
         <f aca="false">+AR16*0.03</f>
         <v>2237.54228178557</v>
       </c>
-      <c r="AS94" s="128" t="n">
+      <c r="AS94" s="129" t="n">
         <f aca="false">+AS16*0.03</f>
         <v>2506.04735559983</v>
       </c>
-      <c r="AT94" s="128" t="n">
+      <c r="AT94" s="129" t="n">
         <f aca="false">+AT16*0.03</f>
         <v>2806.77303827181</v>
       </c>
-      <c r="AU94" s="128" t="n">
+      <c r="AU94" s="129" t="n">
         <f aca="false">+AU16*0.03</f>
         <v>3115.51807248171</v>
       </c>
-      <c r="AV94" s="128" t="n">
+      <c r="AV94" s="129" t="n">
         <f aca="false">+AV16*0.03</f>
         <v>3458.2250604547</v>
       </c>
-      <c r="AW94" s="128" t="n">
+      <c r="AW94" s="129" t="n">
         <f aca="false">+AW16*0.03</f>
         <v>3838.62981710472</v>
       </c>
-      <c r="AX94" s="128" t="n">
+      <c r="AX94" s="129" t="n">
         <f aca="false">+AX16*0.03</f>
         <v>4260.87909698624</v>
       </c>
-      <c r="AY94" s="128" t="n">
+      <c r="AY94" s="129" t="n">
         <f aca="false">+AY16*0.03</f>
         <v>4729.57579765473</v>
       </c>
@@ -26177,10 +26181,10 @@
       <c r="AA96" s="56" t="n">
         <v>2483.758</v>
       </c>
-      <c r="AB96" s="128" t="n">
+      <c r="AB96" s="129" t="n">
         <v>999.185</v>
       </c>
-      <c r="AC96" s="128" t="n">
+      <c r="AC96" s="129" t="n">
         <v>999.185</v>
       </c>
       <c r="AI96" s="58" t="n">
@@ -26309,11 +26313,11 @@
       <c r="AA97" s="56" t="n">
         <v>11825.548</v>
       </c>
-      <c r="AB97" s="128" t="n">
+      <c r="AB97" s="129" t="n">
         <f aca="false">+13361.331</f>
         <v>13361.331</v>
       </c>
-      <c r="AC97" s="128" t="n">
+      <c r="AC97" s="129" t="n">
         <f aca="false">+13361.331</f>
         <v>13361.331</v>
       </c>
@@ -26445,7 +26449,7 @@
       </c>
       <c r="DO98" s="42"/>
     </row>
-    <row r="99" s="129" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" s="130" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="58" t="s">
         <v>152</v>
       </c>
@@ -27150,10 +27154,10 @@
       <c r="AQ102" s="56"/>
       <c r="AR102" s="56"/>
       <c r="AS102" s="56"/>
-      <c r="AT102" s="90"/>
-      <c r="AU102" s="90"/>
-      <c r="AV102" s="90"/>
-      <c r="AW102" s="90"/>
+      <c r="AT102" s="104"/>
+      <c r="AU102" s="104"/>
+      <c r="AV102" s="104"/>
+      <c r="AW102" s="104"/>
       <c r="AX102" s="56"/>
       <c r="AY102" s="6"/>
       <c r="AZ102" s="6"/>
@@ -27326,12 +27330,12 @@
         <v>-580.3</v>
       </c>
       <c r="AX103" s="6"/>
-      <c r="AY103" s="90"/>
-      <c r="AZ103" s="90"/>
+      <c r="AY103" s="104"/>
+      <c r="AZ103" s="104"/>
       <c r="BA103" s="6"/>
       <c r="BB103" s="6"/>
-      <c r="BC103" s="90"/>
-      <c r="BD103" s="90"/>
+      <c r="BC103" s="104"/>
+      <c r="BD103" s="104"/>
       <c r="BE103" s="6"/>
       <c r="BF103" s="6"/>
       <c r="BG103" s="6"/>
@@ -27496,16 +27500,16 @@
       <c r="AN104" s="58" t="n">
         <v>42282.118</v>
       </c>
-      <c r="AX104" s="90"/>
-      <c r="BA104" s="90"/>
-      <c r="BB104" s="90"/>
-      <c r="BE104" s="90"/>
-      <c r="BF104" s="90"/>
-      <c r="BG104" s="90"/>
-      <c r="BH104" s="90"/>
-      <c r="BI104" s="90"/>
-      <c r="BJ104" s="90"/>
-      <c r="BK104" s="90"/>
+      <c r="AX104" s="104"/>
+      <c r="BA104" s="104"/>
+      <c r="BB104" s="104"/>
+      <c r="BE104" s="104"/>
+      <c r="BF104" s="104"/>
+      <c r="BG104" s="104"/>
+      <c r="BH104" s="104"/>
+      <c r="BI104" s="104"/>
+      <c r="BJ104" s="104"/>
+      <c r="BK104" s="104"/>
       <c r="BL104" s="77"/>
       <c r="BM104" s="77"/>
       <c r="BN104" s="77"/>
@@ -27862,13 +27866,13 @@
       <c r="A108" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="B108" s="130" t="s">
+      <c r="B108" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="C108" s="130" t="s">
+      <c r="C108" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="D108" s="130" t="s">
+      <c r="D108" s="131" t="s">
         <v>84</v>
       </c>
       <c r="E108" s="58" t="n">
@@ -27963,9 +27967,9 @@
       <c r="DO108" s="42"/>
     </row>
     <row r="109" s="53" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B109" s="131"/>
-      <c r="C109" s="131"/>
-      <c r="D109" s="131"/>
+      <c r="B109" s="132"/>
+      <c r="C109" s="132"/>
+      <c r="D109" s="132"/>
       <c r="I109" s="53" t="n">
         <f aca="false">+I108/E108-1</f>
         <v>0.205137677690595</v>
@@ -28066,30 +28070,30 @@
     </row>
     <row r="110" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="36"/>
-      <c r="B110" s="132"/>
-      <c r="C110" s="132"/>
-      <c r="D110" s="132"/>
-      <c r="E110" s="133"/>
-      <c r="F110" s="127"/>
-      <c r="G110" s="127"/>
-      <c r="H110" s="127"/>
-      <c r="I110" s="127"/>
-      <c r="J110" s="127"/>
-      <c r="K110" s="127"/>
-      <c r="L110" s="127"/>
-      <c r="M110" s="127"/>
-      <c r="N110" s="127"/>
-      <c r="O110" s="127"/>
-      <c r="P110" s="127"/>
-      <c r="Q110" s="127"/>
-      <c r="R110" s="127"/>
-      <c r="S110" s="127"/>
-      <c r="T110" s="127"/>
-      <c r="U110" s="127"/>
-      <c r="V110" s="127"/>
-      <c r="W110" s="127"/>
-      <c r="X110" s="127"/>
-      <c r="Y110" s="127"/>
+      <c r="B110" s="133"/>
+      <c r="C110" s="133"/>
+      <c r="D110" s="133"/>
+      <c r="E110" s="134"/>
+      <c r="F110" s="128"/>
+      <c r="G110" s="128"/>
+      <c r="H110" s="128"/>
+      <c r="I110" s="128"/>
+      <c r="J110" s="128"/>
+      <c r="K110" s="128"/>
+      <c r="L110" s="128"/>
+      <c r="M110" s="128"/>
+      <c r="N110" s="128"/>
+      <c r="O110" s="128"/>
+      <c r="P110" s="128"/>
+      <c r="Q110" s="128"/>
+      <c r="R110" s="128"/>
+      <c r="S110" s="128"/>
+      <c r="T110" s="128"/>
+      <c r="U110" s="128"/>
+      <c r="V110" s="128"/>
+      <c r="W110" s="128"/>
+      <c r="X110" s="128"/>
+      <c r="Y110" s="128"/>
       <c r="AD110" s="6"/>
       <c r="AE110" s="6"/>
       <c r="AF110" s="6"/>
@@ -28112,9 +28116,9 @@
       <c r="A111" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="B111" s="134"/>
-      <c r="C111" s="134"/>
-      <c r="D111" s="134"/>
+      <c r="B111" s="135"/>
+      <c r="C111" s="135"/>
+      <c r="D111" s="135"/>
       <c r="E111" s="66"/>
       <c r="F111" s="66"/>
       <c r="G111" s="66"/>
@@ -28136,49 +28140,49 @@
       <c r="W111" s="66"/>
       <c r="X111" s="66"/>
       <c r="Y111" s="66"/>
-      <c r="AD111" s="90"/>
-      <c r="AE111" s="90"/>
-      <c r="AF111" s="90"/>
-      <c r="AG111" s="90"/>
-      <c r="AH111" s="90"/>
-      <c r="AI111" s="90" t="n">
+      <c r="AD111" s="104"/>
+      <c r="AE111" s="104"/>
+      <c r="AF111" s="104"/>
+      <c r="AG111" s="104"/>
+      <c r="AH111" s="104"/>
+      <c r="AI111" s="104" t="n">
         <f aca="false">AI30/(AI113+(AI97-AI80))</f>
         <v>0.245607662956777</v>
       </c>
-      <c r="AJ111" s="90" t="n">
+      <c r="AJ111" s="104" t="n">
         <f aca="false">AJ30/(AJ113+(AJ97-AJ80))</f>
         <v>0.252680932969649</v>
       </c>
-      <c r="AK111" s="90" t="n">
+      <c r="AK111" s="104" t="n">
         <f aca="false">AK30/(AK113+(AK97-AK80))</f>
         <v>0.187860082444876</v>
       </c>
-      <c r="AL111" s="90" t="n">
+      <c r="AL111" s="104" t="n">
         <f aca="false">AL30/(AL113+(AL97-AL80))</f>
         <v>0.251816780231443</v>
       </c>
-      <c r="AM111" s="90" t="n">
+      <c r="AM111" s="104" t="n">
         <f aca="false">AM30/(AM113+(AM97-AM80))</f>
         <v>0.338922480884175</v>
       </c>
-      <c r="AN111" s="90" t="n">
+      <c r="AN111" s="104" t="n">
         <f aca="false">AN30/(AN113+(AN97-AN80))</f>
         <v>0.429240108603623</v>
       </c>
-      <c r="AO111" s="90"/>
-      <c r="AP111" s="90"/>
-      <c r="AQ111" s="90"/>
-      <c r="AR111" s="90"/>
-      <c r="AS111" s="90"/>
+      <c r="AO111" s="104"/>
+      <c r="AP111" s="104"/>
+      <c r="AQ111" s="104"/>
+      <c r="AR111" s="104"/>
+      <c r="AS111" s="104"/>
       <c r="DO111" s="42"/>
     </row>
     <row r="112" s="56" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="B112" s="130"/>
-      <c r="C112" s="130"/>
-      <c r="D112" s="130"/>
+      <c r="B112" s="131"/>
+      <c r="C112" s="131"/>
+      <c r="D112" s="131"/>
       <c r="E112" s="58"/>
       <c r="F112" s="58"/>
       <c r="G112" s="58"/>
@@ -29837,68 +29841,68 @@
         <f aca="false">SUM(V126:Y126)</f>
         <v>-790.4</v>
       </c>
-      <c r="AT126" s="129"/>
-      <c r="AU126" s="129"/>
-      <c r="AV126" s="129"/>
-      <c r="AW126" s="129"/>
-      <c r="BL126" s="129"/>
-      <c r="BM126" s="129"/>
-      <c r="BN126" s="129"/>
-      <c r="BO126" s="129"/>
-      <c r="BP126" s="129"/>
-      <c r="BQ126" s="129"/>
-      <c r="BR126" s="129"/>
-      <c r="BS126" s="129"/>
-      <c r="BT126" s="129"/>
-      <c r="BU126" s="129"/>
-      <c r="BV126" s="129"/>
-      <c r="BW126" s="129"/>
-      <c r="BX126" s="129"/>
-      <c r="BY126" s="129"/>
-      <c r="BZ126" s="129"/>
-      <c r="CA126" s="129"/>
-      <c r="CB126" s="129"/>
-      <c r="CC126" s="129"/>
-      <c r="CD126" s="129"/>
-      <c r="CE126" s="129"/>
-      <c r="CF126" s="129"/>
-      <c r="CG126" s="129"/>
-      <c r="CH126" s="129"/>
-      <c r="CI126" s="129"/>
-      <c r="CJ126" s="129"/>
-      <c r="CK126" s="129"/>
-      <c r="CL126" s="129"/>
-      <c r="CM126" s="129"/>
-      <c r="CN126" s="129"/>
-      <c r="CO126" s="129"/>
-      <c r="CP126" s="129"/>
-      <c r="CQ126" s="129"/>
-      <c r="CR126" s="129"/>
-      <c r="CS126" s="129"/>
-      <c r="CT126" s="129"/>
-      <c r="CU126" s="129"/>
-      <c r="CV126" s="129"/>
-      <c r="CW126" s="129"/>
-      <c r="CX126" s="129"/>
-      <c r="CY126" s="129"/>
-      <c r="CZ126" s="129"/>
-      <c r="DA126" s="129"/>
-      <c r="DB126" s="129"/>
-      <c r="DC126" s="129"/>
-      <c r="DD126" s="129"/>
-      <c r="DE126" s="129"/>
-      <c r="DF126" s="129"/>
-      <c r="DG126" s="129"/>
-      <c r="DH126" s="129"/>
-      <c r="DI126" s="129"/>
-      <c r="DJ126" s="129"/>
-      <c r="DK126" s="129"/>
-      <c r="DL126" s="129"/>
-      <c r="DM126" s="129"/>
-      <c r="DN126" s="129"/>
+      <c r="AT126" s="130"/>
+      <c r="AU126" s="130"/>
+      <c r="AV126" s="130"/>
+      <c r="AW126" s="130"/>
+      <c r="BL126" s="130"/>
+      <c r="BM126" s="130"/>
+      <c r="BN126" s="130"/>
+      <c r="BO126" s="130"/>
+      <c r="BP126" s="130"/>
+      <c r="BQ126" s="130"/>
+      <c r="BR126" s="130"/>
+      <c r="BS126" s="130"/>
+      <c r="BT126" s="130"/>
+      <c r="BU126" s="130"/>
+      <c r="BV126" s="130"/>
+      <c r="BW126" s="130"/>
+      <c r="BX126" s="130"/>
+      <c r="BY126" s="130"/>
+      <c r="BZ126" s="130"/>
+      <c r="CA126" s="130"/>
+      <c r="CB126" s="130"/>
+      <c r="CC126" s="130"/>
+      <c r="CD126" s="130"/>
+      <c r="CE126" s="130"/>
+      <c r="CF126" s="130"/>
+      <c r="CG126" s="130"/>
+      <c r="CH126" s="130"/>
+      <c r="CI126" s="130"/>
+      <c r="CJ126" s="130"/>
+      <c r="CK126" s="130"/>
+      <c r="CL126" s="130"/>
+      <c r="CM126" s="130"/>
+      <c r="CN126" s="130"/>
+      <c r="CO126" s="130"/>
+      <c r="CP126" s="130"/>
+      <c r="CQ126" s="130"/>
+      <c r="CR126" s="130"/>
+      <c r="CS126" s="130"/>
+      <c r="CT126" s="130"/>
+      <c r="CU126" s="130"/>
+      <c r="CV126" s="130"/>
+      <c r="CW126" s="130"/>
+      <c r="CX126" s="130"/>
+      <c r="CY126" s="130"/>
+      <c r="CZ126" s="130"/>
+      <c r="DA126" s="130"/>
+      <c r="DB126" s="130"/>
+      <c r="DC126" s="130"/>
+      <c r="DD126" s="130"/>
+      <c r="DE126" s="130"/>
+      <c r="DF126" s="130"/>
+      <c r="DG126" s="130"/>
+      <c r="DH126" s="130"/>
+      <c r="DI126" s="130"/>
+      <c r="DJ126" s="130"/>
+      <c r="DK126" s="130"/>
+      <c r="DL126" s="130"/>
+      <c r="DM126" s="130"/>
+      <c r="DN126" s="130"/>
       <c r="DO126" s="42"/>
     </row>
-    <row r="127" s="106" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" s="107" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="58" t="s">
         <v>146</v>
       </c>
@@ -30021,12 +30025,12 @@
       <c r="AV127" s="56"/>
       <c r="AW127" s="56"/>
       <c r="AX127" s="56"/>
-      <c r="AY127" s="129"/>
-      <c r="AZ127" s="129"/>
+      <c r="AY127" s="130"/>
+      <c r="AZ127" s="130"/>
       <c r="BA127" s="56"/>
       <c r="BB127" s="56"/>
-      <c r="BC127" s="129"/>
-      <c r="BD127" s="129"/>
+      <c r="BC127" s="130"/>
+      <c r="BD127" s="130"/>
       <c r="BE127" s="56"/>
       <c r="BF127" s="56"/>
       <c r="BG127" s="56"/>
@@ -30197,16 +30201,16 @@
         <f aca="false">SUM(V128:Y128)</f>
         <v>881.08</v>
       </c>
-      <c r="AX128" s="129"/>
-      <c r="BA128" s="129"/>
-      <c r="BB128" s="129"/>
-      <c r="BE128" s="129"/>
-      <c r="BF128" s="129"/>
-      <c r="BG128" s="129"/>
-      <c r="BH128" s="129"/>
-      <c r="BI128" s="129"/>
-      <c r="BJ128" s="129"/>
-      <c r="BK128" s="129"/>
+      <c r="AX128" s="130"/>
+      <c r="BA128" s="130"/>
+      <c r="BB128" s="130"/>
+      <c r="BE128" s="130"/>
+      <c r="BF128" s="130"/>
+      <c r="BG128" s="130"/>
+      <c r="BH128" s="130"/>
+      <c r="BI128" s="130"/>
+      <c r="BJ128" s="130"/>
+      <c r="BK128" s="130"/>
       <c r="DO128" s="42"/>
     </row>
     <row r="129" s="52" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30806,7 +30810,7 @@
       <c r="DM131" s="56"/>
       <c r="DN131" s="56"/>
     </row>
-    <row r="132" s="126" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" s="127" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="56"/>
       <c r="B132" s="58"/>
       <c r="C132" s="58"/>
@@ -31080,8 +31084,8 @@
       <c r="AZ133" s="6"/>
       <c r="BA133" s="6"/>
       <c r="BB133" s="6"/>
-      <c r="BC133" s="106"/>
-      <c r="BD133" s="106"/>
+      <c r="BC133" s="107"/>
+      <c r="BD133" s="107"/>
       <c r="BE133" s="6"/>
       <c r="BF133" s="6"/>
       <c r="BG133" s="6"/>
@@ -31329,7 +31333,7 @@
       </c>
       <c r="DO134" s="42"/>
     </row>
-    <row r="135" s="113" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" s="114" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="55" t="s">
         <v>179</v>
       </c>
@@ -31441,12 +31445,12 @@
         <f aca="false">AB131-AB133</f>
         <v>91.6718951899534</v>
       </c>
-      <c r="AC135" s="129"/>
-      <c r="AD135" s="129"/>
-      <c r="AE135" s="129"/>
-      <c r="AF135" s="129"/>
-      <c r="AG135" s="129"/>
-      <c r="AH135" s="129"/>
+      <c r="AC135" s="130"/>
+      <c r="AD135" s="130"/>
+      <c r="AE135" s="130"/>
+      <c r="AF135" s="130"/>
+      <c r="AG135" s="130"/>
+      <c r="AH135" s="130"/>
       <c r="AI135" s="55" t="n">
         <f aca="false">SUM(B135:E135)</f>
         <v>1927.94849739328</v>
@@ -31471,11 +31475,11 @@
         <f aca="false">SUM(V135:Y135)</f>
         <v>9460.10952176694</v>
       </c>
-      <c r="AO135" s="129"/>
-      <c r="AP135" s="129"/>
-      <c r="AQ135" s="129"/>
-      <c r="AR135" s="129"/>
-      <c r="AS135" s="129"/>
+      <c r="AO135" s="130"/>
+      <c r="AP135" s="130"/>
+      <c r="AQ135" s="130"/>
+      <c r="AR135" s="130"/>
+      <c r="AS135" s="130"/>
       <c r="AT135" s="6"/>
       <c r="AU135" s="6"/>
       <c r="AV135" s="6"/>
@@ -31720,71 +31724,71 @@
       <c r="AQ137" s="56"/>
       <c r="AR137" s="56"/>
       <c r="AS137" s="56"/>
-      <c r="AX137" s="113"/>
-      <c r="BA137" s="113"/>
-      <c r="BB137" s="113"/>
-      <c r="BE137" s="113"/>
-      <c r="BF137" s="113"/>
-      <c r="BG137" s="113"/>
-      <c r="BH137" s="113"/>
-      <c r="BI137" s="113"/>
-      <c r="BJ137" s="113"/>
-      <c r="BK137" s="113"/>
-      <c r="BL137" s="113"/>
-      <c r="BM137" s="113"/>
-      <c r="BN137" s="113"/>
-      <c r="BO137" s="113"/>
-      <c r="BP137" s="113"/>
-      <c r="BQ137" s="113"/>
-      <c r="BR137" s="113"/>
-      <c r="BS137" s="113"/>
-      <c r="BT137" s="113"/>
-      <c r="BU137" s="113"/>
-      <c r="BV137" s="113"/>
-      <c r="BW137" s="113"/>
-      <c r="BX137" s="113"/>
-      <c r="BY137" s="113"/>
-      <c r="BZ137" s="113"/>
-      <c r="CA137" s="113"/>
-      <c r="CB137" s="113"/>
-      <c r="CC137" s="113"/>
-      <c r="CD137" s="113"/>
-      <c r="CE137" s="113"/>
-      <c r="CF137" s="113"/>
-      <c r="CG137" s="113"/>
-      <c r="CH137" s="113"/>
-      <c r="CI137" s="113"/>
-      <c r="CJ137" s="113"/>
-      <c r="CK137" s="113"/>
-      <c r="CL137" s="113"/>
-      <c r="CM137" s="113"/>
-      <c r="CN137" s="113"/>
-      <c r="CO137" s="113"/>
-      <c r="CP137" s="113"/>
-      <c r="CQ137" s="113"/>
-      <c r="CR137" s="113"/>
-      <c r="CS137" s="113"/>
-      <c r="CT137" s="113"/>
-      <c r="CU137" s="113"/>
-      <c r="CV137" s="113"/>
-      <c r="CW137" s="113"/>
-      <c r="CX137" s="113"/>
-      <c r="CY137" s="113"/>
-      <c r="CZ137" s="113"/>
-      <c r="DA137" s="113"/>
-      <c r="DB137" s="113"/>
-      <c r="DC137" s="113"/>
-      <c r="DD137" s="113"/>
-      <c r="DE137" s="113"/>
-      <c r="DF137" s="113"/>
-      <c r="DG137" s="113"/>
-      <c r="DH137" s="113"/>
-      <c r="DI137" s="113"/>
-      <c r="DJ137" s="113"/>
-      <c r="DK137" s="113"/>
-      <c r="DL137" s="113"/>
-      <c r="DM137" s="113"/>
-      <c r="DN137" s="113"/>
+      <c r="AX137" s="114"/>
+      <c r="BA137" s="114"/>
+      <c r="BB137" s="114"/>
+      <c r="BE137" s="114"/>
+      <c r="BF137" s="114"/>
+      <c r="BG137" s="114"/>
+      <c r="BH137" s="114"/>
+      <c r="BI137" s="114"/>
+      <c r="BJ137" s="114"/>
+      <c r="BK137" s="114"/>
+      <c r="BL137" s="114"/>
+      <c r="BM137" s="114"/>
+      <c r="BN137" s="114"/>
+      <c r="BO137" s="114"/>
+      <c r="BP137" s="114"/>
+      <c r="BQ137" s="114"/>
+      <c r="BR137" s="114"/>
+      <c r="BS137" s="114"/>
+      <c r="BT137" s="114"/>
+      <c r="BU137" s="114"/>
+      <c r="BV137" s="114"/>
+      <c r="BW137" s="114"/>
+      <c r="BX137" s="114"/>
+      <c r="BY137" s="114"/>
+      <c r="BZ137" s="114"/>
+      <c r="CA137" s="114"/>
+      <c r="CB137" s="114"/>
+      <c r="CC137" s="114"/>
+      <c r="CD137" s="114"/>
+      <c r="CE137" s="114"/>
+      <c r="CF137" s="114"/>
+      <c r="CG137" s="114"/>
+      <c r="CH137" s="114"/>
+      <c r="CI137" s="114"/>
+      <c r="CJ137" s="114"/>
+      <c r="CK137" s="114"/>
+      <c r="CL137" s="114"/>
+      <c r="CM137" s="114"/>
+      <c r="CN137" s="114"/>
+      <c r="CO137" s="114"/>
+      <c r="CP137" s="114"/>
+      <c r="CQ137" s="114"/>
+      <c r="CR137" s="114"/>
+      <c r="CS137" s="114"/>
+      <c r="CT137" s="114"/>
+      <c r="CU137" s="114"/>
+      <c r="CV137" s="114"/>
+      <c r="CW137" s="114"/>
+      <c r="CX137" s="114"/>
+      <c r="CY137" s="114"/>
+      <c r="CZ137" s="114"/>
+      <c r="DA137" s="114"/>
+      <c r="DB137" s="114"/>
+      <c r="DC137" s="114"/>
+      <c r="DD137" s="114"/>
+      <c r="DE137" s="114"/>
+      <c r="DF137" s="114"/>
+      <c r="DG137" s="114"/>
+      <c r="DH137" s="114"/>
+      <c r="DI137" s="114"/>
+      <c r="DJ137" s="114"/>
+      <c r="DK137" s="114"/>
+      <c r="DL137" s="114"/>
+      <c r="DM137" s="114"/>
+      <c r="DN137" s="114"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="56" t="s">
@@ -31848,75 +31852,75 @@
       <c r="AS138" s="56"/>
     </row>
     <row r="139" s="77" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="126" t="s">
+      <c r="A139" s="127" t="s">
         <v>181</v>
       </c>
-      <c r="B139" s="126"/>
-      <c r="C139" s="126"/>
-      <c r="D139" s="126"/>
-      <c r="E139" s="126"/>
-      <c r="F139" s="126"/>
-      <c r="G139" s="126"/>
-      <c r="H139" s="126"/>
-      <c r="I139" s="126"/>
-      <c r="J139" s="126"/>
-      <c r="K139" s="126"/>
-      <c r="L139" s="126"/>
-      <c r="M139" s="126"/>
-      <c r="N139" s="126"/>
-      <c r="O139" s="126"/>
-      <c r="P139" s="126"/>
-      <c r="Q139" s="126"/>
-      <c r="R139" s="126"/>
-      <c r="S139" s="126"/>
-      <c r="T139" s="126"/>
-      <c r="U139" s="126"/>
-      <c r="V139" s="126"/>
-      <c r="W139" s="126"/>
-      <c r="X139" s="126"/>
-      <c r="Y139" s="126"/>
-      <c r="Z139" s="126"/>
-      <c r="AA139" s="126"/>
-      <c r="AB139" s="126"/>
-      <c r="AC139" s="126"/>
-      <c r="AD139" s="126"/>
-      <c r="AE139" s="126"/>
-      <c r="AF139" s="126"/>
-      <c r="AG139" s="126"/>
-      <c r="AH139" s="126"/>
-      <c r="AI139" s="126" t="n">
+      <c r="B139" s="127"/>
+      <c r="C139" s="127"/>
+      <c r="D139" s="127"/>
+      <c r="E139" s="127"/>
+      <c r="F139" s="127"/>
+      <c r="G139" s="127"/>
+      <c r="H139" s="127"/>
+      <c r="I139" s="127"/>
+      <c r="J139" s="127"/>
+      <c r="K139" s="127"/>
+      <c r="L139" s="127"/>
+      <c r="M139" s="127"/>
+      <c r="N139" s="127"/>
+      <c r="O139" s="127"/>
+      <c r="P139" s="127"/>
+      <c r="Q139" s="127"/>
+      <c r="R139" s="127"/>
+      <c r="S139" s="127"/>
+      <c r="T139" s="127"/>
+      <c r="U139" s="127"/>
+      <c r="V139" s="127"/>
+      <c r="W139" s="127"/>
+      <c r="X139" s="127"/>
+      <c r="Y139" s="127"/>
+      <c r="Z139" s="127"/>
+      <c r="AA139" s="127"/>
+      <c r="AB139" s="127"/>
+      <c r="AC139" s="127"/>
+      <c r="AD139" s="127"/>
+      <c r="AE139" s="127"/>
+      <c r="AF139" s="127"/>
+      <c r="AG139" s="127"/>
+      <c r="AH139" s="127"/>
+      <c r="AI139" s="127" t="n">
         <f aca="false">+(AI16*1000000)/AI138</f>
         <v>2659154.89361702</v>
       </c>
-      <c r="AJ139" s="126" t="n">
+      <c r="AJ139" s="127" t="n">
         <f aca="false">+(AJ16*1000000)/AJ138</f>
         <v>2628127.78761062</v>
       </c>
-      <c r="AK139" s="126" t="n">
+      <c r="AK139" s="127" t="n">
         <f aca="false">+(AK16*1000000)/AK138</f>
         <v>2469964.84375</v>
       </c>
-      <c r="AL139" s="126" t="n">
+      <c r="AL139" s="127" t="n">
         <f aca="false">+(AL16*1000000)/AL138</f>
         <v>2594099.76923077</v>
       </c>
-      <c r="AM139" s="126" t="n">
+      <c r="AM139" s="127" t="n">
         <f aca="false">+(AM16*1000000)/AM138</f>
         <v>2785785.42857143</v>
       </c>
-      <c r="AN139" s="126" t="n">
+      <c r="AN139" s="127" t="n">
         <f aca="false">+(AN16*1000000)/AN138</f>
         <v>2823918.75</v>
       </c>
-      <c r="AO139" s="126"/>
-      <c r="AP139" s="126"/>
-      <c r="AQ139" s="126"/>
-      <c r="AR139" s="126"/>
-      <c r="AS139" s="126"/>
-      <c r="AT139" s="126"/>
-      <c r="AU139" s="126"/>
-      <c r="AV139" s="126"/>
-      <c r="AW139" s="126"/>
+      <c r="AO139" s="127"/>
+      <c r="AP139" s="127"/>
+      <c r="AQ139" s="127"/>
+      <c r="AR139" s="127"/>
+      <c r="AS139" s="127"/>
+      <c r="AT139" s="127"/>
+      <c r="AU139" s="127"/>
+      <c r="AV139" s="127"/>
+      <c r="AW139" s="127"/>
       <c r="AX139" s="6"/>
       <c r="AY139" s="67"/>
       <c r="AZ139" s="67"/>
@@ -31991,8 +31995,8 @@
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AY140" s="67"/>
       <c r="AZ140" s="67"/>
-      <c r="BC140" s="126"/>
-      <c r="BD140" s="126"/>
+      <c r="BC140" s="127"/>
+      <c r="BD140" s="127"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="56" t="s">
@@ -32142,73 +32146,73 @@
       <c r="AU141" s="56"/>
       <c r="AV141" s="56"/>
       <c r="AW141" s="56"/>
-      <c r="AX141" s="126"/>
-      <c r="AY141" s="126"/>
-      <c r="AZ141" s="126"/>
-      <c r="BA141" s="126"/>
-      <c r="BB141" s="126"/>
-      <c r="BE141" s="126"/>
-      <c r="BF141" s="126"/>
-      <c r="BG141" s="126"/>
-      <c r="BH141" s="126"/>
-      <c r="BI141" s="126"/>
-      <c r="BJ141" s="126"/>
-      <c r="BK141" s="126"/>
-      <c r="BL141" s="126"/>
-      <c r="BM141" s="126"/>
-      <c r="BN141" s="126"/>
-      <c r="BO141" s="126"/>
-      <c r="BP141" s="126"/>
-      <c r="BQ141" s="126"/>
-      <c r="BR141" s="126"/>
-      <c r="BS141" s="126"/>
-      <c r="BT141" s="126"/>
-      <c r="BU141" s="126"/>
-      <c r="BV141" s="126"/>
-      <c r="BW141" s="126"/>
-      <c r="BX141" s="126"/>
-      <c r="BY141" s="126"/>
-      <c r="BZ141" s="126"/>
-      <c r="CA141" s="126"/>
-      <c r="CB141" s="126"/>
-      <c r="CC141" s="126"/>
-      <c r="CD141" s="126"/>
-      <c r="CE141" s="126"/>
-      <c r="CF141" s="126"/>
-      <c r="CG141" s="126"/>
-      <c r="CH141" s="126"/>
-      <c r="CI141" s="126"/>
-      <c r="CJ141" s="126"/>
-      <c r="CK141" s="126"/>
-      <c r="CL141" s="126"/>
-      <c r="CM141" s="126"/>
-      <c r="CN141" s="126"/>
-      <c r="CO141" s="126"/>
-      <c r="CP141" s="126"/>
-      <c r="CQ141" s="126"/>
-      <c r="CR141" s="126"/>
-      <c r="CS141" s="126"/>
-      <c r="CT141" s="126"/>
-      <c r="CU141" s="126"/>
-      <c r="CV141" s="126"/>
-      <c r="CW141" s="126"/>
-      <c r="CX141" s="126"/>
-      <c r="CY141" s="126"/>
-      <c r="CZ141" s="126"/>
-      <c r="DA141" s="126"/>
-      <c r="DB141" s="126"/>
-      <c r="DC141" s="126"/>
-      <c r="DD141" s="126"/>
-      <c r="DE141" s="126"/>
-      <c r="DF141" s="126"/>
-      <c r="DG141" s="126"/>
-      <c r="DH141" s="126"/>
-      <c r="DI141" s="126"/>
-      <c r="DJ141" s="126"/>
-      <c r="DK141" s="126"/>
-      <c r="DL141" s="126"/>
-      <c r="DM141" s="126"/>
-      <c r="DN141" s="126"/>
+      <c r="AX141" s="127"/>
+      <c r="AY141" s="127"/>
+      <c r="AZ141" s="127"/>
+      <c r="BA141" s="127"/>
+      <c r="BB141" s="127"/>
+      <c r="BE141" s="127"/>
+      <c r="BF141" s="127"/>
+      <c r="BG141" s="127"/>
+      <c r="BH141" s="127"/>
+      <c r="BI141" s="127"/>
+      <c r="BJ141" s="127"/>
+      <c r="BK141" s="127"/>
+      <c r="BL141" s="127"/>
+      <c r="BM141" s="127"/>
+      <c r="BN141" s="127"/>
+      <c r="BO141" s="127"/>
+      <c r="BP141" s="127"/>
+      <c r="BQ141" s="127"/>
+      <c r="BR141" s="127"/>
+      <c r="BS141" s="127"/>
+      <c r="BT141" s="127"/>
+      <c r="BU141" s="127"/>
+      <c r="BV141" s="127"/>
+      <c r="BW141" s="127"/>
+      <c r="BX141" s="127"/>
+      <c r="BY141" s="127"/>
+      <c r="BZ141" s="127"/>
+      <c r="CA141" s="127"/>
+      <c r="CB141" s="127"/>
+      <c r="CC141" s="127"/>
+      <c r="CD141" s="127"/>
+      <c r="CE141" s="127"/>
+      <c r="CF141" s="127"/>
+      <c r="CG141" s="127"/>
+      <c r="CH141" s="127"/>
+      <c r="CI141" s="127"/>
+      <c r="CJ141" s="127"/>
+      <c r="CK141" s="127"/>
+      <c r="CL141" s="127"/>
+      <c r="CM141" s="127"/>
+      <c r="CN141" s="127"/>
+      <c r="CO141" s="127"/>
+      <c r="CP141" s="127"/>
+      <c r="CQ141" s="127"/>
+      <c r="CR141" s="127"/>
+      <c r="CS141" s="127"/>
+      <c r="CT141" s="127"/>
+      <c r="CU141" s="127"/>
+      <c r="CV141" s="127"/>
+      <c r="CW141" s="127"/>
+      <c r="CX141" s="127"/>
+      <c r="CY141" s="127"/>
+      <c r="CZ141" s="127"/>
+      <c r="DA141" s="127"/>
+      <c r="DB141" s="127"/>
+      <c r="DC141" s="127"/>
+      <c r="DD141" s="127"/>
+      <c r="DE141" s="127"/>
+      <c r="DF141" s="127"/>
+      <c r="DG141" s="127"/>
+      <c r="DH141" s="127"/>
+      <c r="DI141" s="127"/>
+      <c r="DJ141" s="127"/>
+      <c r="DK141" s="127"/>
+      <c r="DL141" s="127"/>
+      <c r="DM141" s="127"/>
+      <c r="DN141" s="127"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="74" t="s">
@@ -32554,115 +32558,115 @@
     <row r="145" s="53" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="DO145" s="42"/>
     </row>
-    <row r="146" s="117" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="117" t="s">
+    <row r="146" s="118" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="118" t="s">
         <v>185</v>
       </c>
-      <c r="B146" s="117" t="n">
+      <c r="B146" s="118" t="n">
         <f aca="false">+B30/(-B32)</f>
         <v>5.20724983189451</v>
       </c>
-      <c r="C146" s="117" t="n">
+      <c r="C146" s="118" t="n">
         <f aca="false">+C30/(-C32)</f>
         <v>7.18063780551972</v>
       </c>
-      <c r="D146" s="117" t="n">
+      <c r="D146" s="118" t="n">
         <f aca="false">+D30/(-D32)</f>
         <v>6.67435289362818</v>
       </c>
-      <c r="E146" s="117" t="n">
+      <c r="E146" s="118" t="n">
         <f aca="false">+E30/(-E32)</f>
         <v>4.84125805151153</v>
       </c>
-      <c r="F146" s="117" t="n">
+      <c r="F146" s="118" t="n">
         <f aca="false">+F30/(-F32)</f>
         <v>10.0810449309502</v>
       </c>
-      <c r="G146" s="117" t="n">
+      <c r="G146" s="118" t="n">
         <f aca="false">+G30/(-G32)</f>
         <v>9.65824130053476</v>
       </c>
-      <c r="H146" s="117" t="n">
+      <c r="H146" s="118" t="n">
         <f aca="false">+H30/(-H32)</f>
         <v>9.23862992194654</v>
       </c>
-      <c r="I146" s="117" t="n">
+      <c r="I146" s="118" t="n">
         <f aca="false">+I30/(-I32)</f>
         <v>3.34167551386906</v>
       </c>
-      <c r="J146" s="117" t="n">
+      <c r="J146" s="118" t="n">
         <f aca="false">+J30/(-J32)</f>
         <v>10.5149107973105</v>
       </c>
-      <c r="K146" s="117" t="n">
+      <c r="K146" s="118" t="n">
         <f aca="false">+K30/(-K32)</f>
         <v>8.9979357453621</v>
       </c>
-      <c r="L146" s="117" t="n">
+      <c r="L146" s="118" t="n">
         <f aca="false">+L30/(-L32)</f>
         <v>8.17730516929548</v>
       </c>
-      <c r="M146" s="117" t="n">
+      <c r="M146" s="118" t="n">
         <f aca="false">+M30/(-M32)</f>
         <v>3.2233778746195</v>
       </c>
-      <c r="N146" s="117" t="n">
+      <c r="N146" s="118" t="n">
         <f aca="false">+N30/(-N32)</f>
         <v>9.84470586009345</v>
       </c>
-      <c r="O146" s="117" t="n">
+      <c r="O146" s="118" t="n">
         <f aca="false">+O30/(-O32)</f>
         <v>10.4624895079798</v>
       </c>
-      <c r="P146" s="117" t="n">
+      <c r="P146" s="118" t="n">
         <f aca="false">+P30/(-P32)</f>
         <v>10.9336624595346</v>
       </c>
-      <c r="Q146" s="117" t="n">
+      <c r="Q146" s="118" t="n">
         <f aca="false">+Q30/(-Q32)</f>
         <v>8.60057126741281</v>
       </c>
-      <c r="R146" s="117" t="n">
+      <c r="R146" s="118" t="n">
         <f aca="false">+R30/(-R32)</f>
         <v>15.1924713376659</v>
       </c>
-      <c r="S146" s="117" t="n">
+      <c r="S146" s="118" t="n">
         <f aca="false">+S30/(-S32)</f>
         <v>15.246299260148</v>
       </c>
-      <c r="T146" s="117" t="n">
+      <c r="T146" s="118" t="n">
         <f aca="false">+T30/(-T32)</f>
         <v>15.7514060230622</v>
       </c>
-      <c r="U146" s="117" t="n">
+      <c r="U146" s="118" t="n">
         <f aca="false">+U30/(-U32)</f>
         <v>11.8111579601699</v>
       </c>
-      <c r="V146" s="117" t="n">
+      <c r="V146" s="118" t="n">
         <f aca="false">+V30/(-V32)</f>
         <v>18.4294456838328</v>
       </c>
-      <c r="W146" s="117" t="n">
+      <c r="W146" s="118" t="n">
         <f aca="false">+W30/(-W32)</f>
         <v>20.6783202029989</v>
       </c>
-      <c r="X146" s="117" t="n">
+      <c r="X146" s="118" t="n">
         <f aca="false">+X30/(-X32)</f>
         <v>18.570614869058</v>
       </c>
-      <c r="Y146" s="117" t="n">
+      <c r="Y146" s="118" t="n">
         <f aca="false">+Y30/(-Y32)</f>
         <v>12.6130451993127</v>
       </c>
-      <c r="Z146" s="117" t="n">
+      <c r="Z146" s="118" t="n">
         <f aca="false">+Z30/(-Z32)</f>
         <v>15.0980433313236</v>
       </c>
-      <c r="AA146" s="117" t="n">
+      <c r="AA146" s="118" t="n">
         <f aca="false">+AA30/(-AA32)</f>
         <v>23.8635294884677</v>
       </c>
-      <c r="DO146" s="135"/>
+      <c r="DO146" s="136"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="BC147" s="77"/>
@@ -32861,153 +32865,153 @@
         <f aca="false">+AVERAGE(AM91:AN91)/AN18*365</f>
         <v>14.11757702759</v>
       </c>
-      <c r="AO149" s="136" t="n">
+      <c r="AO149" s="137" t="n">
         <f aca="false">+AN149+0.5</f>
         <v>14.61757702759</v>
       </c>
-      <c r="AP149" s="136" t="n">
+      <c r="AP149" s="137" t="n">
         <f aca="false">+AO149+0.5</f>
         <v>15.11757702759</v>
       </c>
-      <c r="AQ149" s="136" t="n">
+      <c r="AQ149" s="137" t="n">
         <f aca="false">+AP149+0.5</f>
         <v>15.61757702759</v>
       </c>
-      <c r="AR149" s="136" t="n">
+      <c r="AR149" s="137" t="n">
         <f aca="false">+AQ149+0.5</f>
         <v>16.11757702759</v>
       </c>
-      <c r="AS149" s="136" t="n">
+      <c r="AS149" s="137" t="n">
         <f aca="false">+AR149+0.5</f>
         <v>16.61757702759</v>
       </c>
-      <c r="AT149" s="136" t="n">
+      <c r="AT149" s="137" t="n">
         <f aca="false">+AS149+0.5</f>
         <v>17.11757702759</v>
       </c>
-      <c r="AU149" s="136" t="n">
+      <c r="AU149" s="137" t="n">
         <f aca="false">+AT149+0.5</f>
         <v>17.61757702759</v>
       </c>
-      <c r="AV149" s="136" t="n">
+      <c r="AV149" s="137" t="n">
         <f aca="false">+AU149+0.5</f>
         <v>18.11757702759</v>
       </c>
-      <c r="AW149" s="136" t="n">
+      <c r="AW149" s="137" t="n">
         <f aca="false">+AV149+0.5</f>
         <v>18.61757702759</v>
       </c>
-      <c r="AX149" s="136" t="n">
+      <c r="AX149" s="137" t="n">
         <f aca="false">+AW149+0.5</f>
         <v>19.11757702759</v>
       </c>
-      <c r="AY149" s="136" t="n">
+      <c r="AY149" s="137" t="n">
         <f aca="false">+AX149+0.5</f>
         <v>19.61757702759</v>
       </c>
-      <c r="DO149" s="137"/>
-    </row>
-    <row r="153" s="126" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="126" t="s">
+      <c r="DO149" s="138"/>
+    </row>
+    <row r="153" s="127" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="127" t="s">
         <v>187</v>
       </c>
-      <c r="B153" s="126" t="n">
+      <c r="B153" s="127" t="n">
         <v>43.694</v>
       </c>
-      <c r="C153" s="126" t="n">
+      <c r="C153" s="127" t="n">
         <v>89.06</v>
       </c>
-      <c r="D153" s="126" t="n">
+      <c r="D153" s="127" t="n">
         <v>68.665</v>
       </c>
-      <c r="E153" s="126" t="n">
+      <c r="E153" s="127" t="n">
         <v>33.987</v>
       </c>
-      <c r="F153" s="126" t="n">
+      <c r="F153" s="127" t="n">
         <v>48.071</v>
       </c>
-      <c r="G153" s="126" t="n">
+      <c r="G153" s="127" t="n">
         <v>19.479</v>
       </c>
-      <c r="H153" s="126" t="n">
+      <c r="H153" s="127" t="n">
         <v>18.445</v>
       </c>
-      <c r="I153" s="126" t="n">
+      <c r="I153" s="127" t="n">
         <v>88.149</v>
       </c>
-      <c r="J153" s="126" t="n">
+      <c r="J153" s="127" t="n">
         <v>13.678</v>
       </c>
-      <c r="K153" s="126" t="n">
+      <c r="K153" s="127" t="n">
         <v>11.25</v>
       </c>
-      <c r="L153" s="126" t="n">
+      <c r="L153" s="127" t="n">
         <v>4.113</v>
       </c>
-      <c r="M153" s="126" t="n">
+      <c r="M153" s="127" t="n">
         <v>6.705</v>
       </c>
-      <c r="N153" s="126" t="n">
+      <c r="N153" s="127" t="n">
         <v>26.028</v>
       </c>
-      <c r="O153" s="126" t="n">
+      <c r="O153" s="127" t="n">
         <v>34.717</v>
       </c>
-      <c r="P153" s="126" t="n">
+      <c r="P153" s="127" t="n">
         <v>57.818</v>
       </c>
-      <c r="Q153" s="126" t="n">
+      <c r="Q153" s="127" t="n">
         <v>51.427</v>
       </c>
-      <c r="R153" s="126" t="n">
+      <c r="R153" s="127" t="n">
         <v>268.881</v>
       </c>
-      <c r="S153" s="126" t="n">
+      <c r="S153" s="127" t="n">
         <v>118.75</v>
       </c>
-      <c r="T153" s="126" t="n">
+      <c r="T153" s="127" t="n">
         <v>143.244</v>
       </c>
-      <c r="U153" s="126" t="n">
+      <c r="U153" s="127" t="n">
         <v>302.012</v>
       </c>
-      <c r="V153" s="126" t="n">
+      <c r="V153" s="127" t="n">
         <v>351.602</v>
       </c>
-      <c r="W153" s="126" t="n">
+      <c r="W153" s="127" t="n">
         <v>169.022</v>
       </c>
-      <c r="X153" s="126" t="n">
+      <c r="X153" s="127" t="n">
         <v>70.215</v>
       </c>
-      <c r="Y153" s="126" t="n">
+      <c r="Y153" s="127" t="n">
         <v>76.082</v>
       </c>
-      <c r="Z153" s="126" t="n">
+      <c r="Z153" s="127" t="n">
         <v>49.31</v>
       </c>
-      <c r="AA153" s="126" t="n">
+      <c r="AA153" s="127" t="n">
         <v>59.98</v>
       </c>
-      <c r="AI153" s="126" t="n">
+      <c r="AI153" s="127" t="n">
         <v>235.406</v>
       </c>
-      <c r="AJ153" s="126" t="n">
+      <c r="AJ153" s="127" t="n">
         <v>174.414</v>
       </c>
-      <c r="AK153" s="126" t="n">
+      <c r="AK153" s="127" t="n">
         <v>35.746</v>
       </c>
-      <c r="AL153" s="126" t="n">
+      <c r="AL153" s="127" t="n">
         <v>169.99</v>
       </c>
-      <c r="AM153" s="126" t="n">
+      <c r="AM153" s="127" t="n">
         <v>832.887</v>
       </c>
-      <c r="AN153" s="126" t="n">
+      <c r="AN153" s="127" t="n">
         <v>666.965</v>
       </c>
-      <c r="DO153" s="138"/>
+      <c r="DO153" s="139"/>
     </row>
     <row r="154" s="53" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B154" s="53" t="n">
@@ -33245,107 +33249,107 @@
         <v>-0.199213098535576</v>
       </c>
     </row>
-    <row r="156" s="126" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="126" t="s">
+    <row r="156" s="127" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A156" s="127" t="s">
         <v>188</v>
       </c>
-      <c r="B156" s="126" t="n">
+      <c r="B156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="C156" s="126" t="n">
+      <c r="C156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="D156" s="126" t="n">
+      <c r="D156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="E156" s="126" t="n">
+      <c r="E156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="126" t="n">
+      <c r="F156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="G156" s="126" t="n">
+      <c r="G156" s="127" t="n">
         <v>500.022</v>
       </c>
-      <c r="H156" s="126" t="n">
+      <c r="H156" s="127" t="n">
         <v>100</v>
       </c>
-      <c r="I156" s="126" t="n">
+      <c r="I156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="J156" s="126" t="n">
+      <c r="J156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="K156" s="126" t="n">
+      <c r="K156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="L156" s="126" t="n">
+      <c r="L156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="M156" s="126" t="n">
+      <c r="M156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="N156" s="126" t="n">
+      <c r="N156" s="127" t="n">
         <v>400.101</v>
       </c>
-      <c r="O156" s="126" t="n">
+      <c r="O156" s="127" t="n">
         <v>645.146</v>
       </c>
-      <c r="P156" s="126" t="n">
+      <c r="P156" s="127" t="n">
         <v>2500.1</v>
       </c>
-      <c r="Q156" s="126" t="n">
+      <c r="Q156" s="127" t="n">
         <v>2500</v>
       </c>
-      <c r="R156" s="126" t="n">
+      <c r="R156" s="127" t="n">
         <v>2000</v>
       </c>
-      <c r="S156" s="126" t="n">
+      <c r="S156" s="127" t="n">
         <v>1599.998</v>
       </c>
-      <c r="T156" s="126" t="n">
+      <c r="T156" s="127" t="n">
         <v>1700</v>
       </c>
-      <c r="U156" s="126" t="n">
+      <c r="U156" s="127" t="n">
         <v>963.748</v>
       </c>
-      <c r="V156" s="126" t="n">
+      <c r="V156" s="127" t="n">
         <v>3536.396</v>
       </c>
-      <c r="W156" s="126" t="n">
+      <c r="W156" s="127" t="n">
         <v>1654.327</v>
       </c>
-      <c r="X156" s="126" t="n">
+      <c r="X156" s="127" t="n">
         <v>1856.885</v>
       </c>
-      <c r="Y156" s="126" t="n">
+      <c r="Y156" s="127" t="n">
         <v>2079.559</v>
       </c>
-      <c r="Z156" s="126" t="n">
+      <c r="Z156" s="127" t="n">
         <v>1270.588</v>
       </c>
-      <c r="AA156" s="126" t="n">
+      <c r="AA156" s="127" t="n">
         <v>4714.403</v>
       </c>
-      <c r="AI156" s="126" t="n">
+      <c r="AI156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="AJ156" s="126" t="n">
+      <c r="AJ156" s="127" t="n">
         <v>600.022</v>
       </c>
-      <c r="AK156" s="126" t="n">
+      <c r="AK156" s="127" t="n">
         <v>0</v>
       </c>
-      <c r="AL156" s="126" t="n">
+      <c r="AL156" s="127" t="n">
         <v>6045.347</v>
       </c>
-      <c r="AM156" s="126" t="n">
+      <c r="AM156" s="127" t="n">
         <v>6263.746</v>
       </c>
-      <c r="AN156" s="126" t="n">
+      <c r="AN156" s="127" t="n">
         <v>9127.167</v>
       </c>
-      <c r="DO156" s="138"/>
+      <c r="DO156" s="139"/>
     </row>
     <row r="157" s="53" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B157" s="53" t="n">
@@ -33583,139 +33587,139 @@
         <v>0.457141940302177</v>
       </c>
     </row>
-    <row r="160" s="126" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="126" t="s">
+    <row r="160" s="127" customFormat="true" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A160" s="127" t="s">
         <v>189</v>
       </c>
-      <c r="B160" s="126" t="n">
+      <c r="B160" s="127" t="n">
         <f aca="false">+B156-B153</f>
         <v>-43.694</v>
       </c>
-      <c r="C160" s="126" t="n">
+      <c r="C160" s="127" t="n">
         <f aca="false">+C156-C153</f>
         <v>-89.06</v>
       </c>
-      <c r="D160" s="126" t="n">
+      <c r="D160" s="127" t="n">
         <f aca="false">+D156-D153</f>
         <v>-68.665</v>
       </c>
-      <c r="E160" s="126" t="n">
+      <c r="E160" s="127" t="n">
         <f aca="false">+E156-E153</f>
         <v>-33.987</v>
       </c>
-      <c r="F160" s="126" t="n">
+      <c r="F160" s="127" t="n">
         <f aca="false">+F156-F153</f>
         <v>-48.071</v>
       </c>
-      <c r="G160" s="126" t="n">
+      <c r="G160" s="127" t="n">
         <f aca="false">+G156-G153</f>
         <v>480.543</v>
       </c>
-      <c r="H160" s="126" t="n">
+      <c r="H160" s="127" t="n">
         <f aca="false">+H156-H153</f>
         <v>81.555</v>
       </c>
-      <c r="I160" s="126" t="n">
+      <c r="I160" s="127" t="n">
         <f aca="false">+I156-I153</f>
         <v>-88.149</v>
       </c>
-      <c r="J160" s="126" t="n">
+      <c r="J160" s="127" t="n">
         <f aca="false">+J156-J153</f>
         <v>-13.678</v>
       </c>
-      <c r="K160" s="126" t="n">
+      <c r="K160" s="127" t="n">
         <f aca="false">+K156-K153</f>
         <v>-11.25</v>
       </c>
-      <c r="L160" s="126" t="n">
+      <c r="L160" s="127" t="n">
         <f aca="false">+L156-L153</f>
         <v>-4.113</v>
       </c>
-      <c r="M160" s="126" t="n">
+      <c r="M160" s="127" t="n">
         <f aca="false">+M156-M153</f>
         <v>-6.705</v>
       </c>
-      <c r="N160" s="126" t="n">
+      <c r="N160" s="127" t="n">
         <f aca="false">+N156-N153</f>
         <v>374.073</v>
       </c>
-      <c r="O160" s="126" t="n">
+      <c r="O160" s="127" t="n">
         <f aca="false">+O156-O153</f>
         <v>610.429</v>
       </c>
-      <c r="P160" s="126" t="n">
+      <c r="P160" s="127" t="n">
         <f aca="false">+P156-P153</f>
         <v>2442.282</v>
       </c>
-      <c r="Q160" s="126" t="n">
+      <c r="Q160" s="127" t="n">
         <f aca="false">+Q156-Q153</f>
         <v>2448.573</v>
       </c>
-      <c r="R160" s="126" t="n">
+      <c r="R160" s="127" t="n">
         <f aca="false">+R156-R153</f>
         <v>1731.119</v>
       </c>
-      <c r="S160" s="126" t="n">
+      <c r="S160" s="127" t="n">
         <f aca="false">+S156-S153</f>
         <v>1481.248</v>
       </c>
-      <c r="T160" s="126" t="n">
+      <c r="T160" s="127" t="n">
         <f aca="false">+T156-T153</f>
         <v>1556.756</v>
       </c>
-      <c r="U160" s="126" t="n">
+      <c r="U160" s="127" t="n">
         <f aca="false">+U156-U153</f>
         <v>661.736</v>
       </c>
-      <c r="V160" s="126" t="n">
+      <c r="V160" s="127" t="n">
         <f aca="false">+V156-V153</f>
         <v>3184.794</v>
       </c>
-      <c r="W160" s="126" t="n">
+      <c r="W160" s="127" t="n">
         <f aca="false">+W156-W153</f>
         <v>1485.305</v>
       </c>
-      <c r="X160" s="126" t="n">
+      <c r="X160" s="127" t="n">
         <f aca="false">+X156-X153</f>
         <v>1786.67</v>
       </c>
-      <c r="Y160" s="126" t="n">
+      <c r="Y160" s="127" t="n">
         <f aca="false">+Y156-Y153</f>
         <v>2003.477</v>
       </c>
-      <c r="Z160" s="126" t="n">
+      <c r="Z160" s="127" t="n">
         <f aca="false">+Z156-Z153</f>
         <v>1221.278</v>
       </c>
-      <c r="AA160" s="126" t="n">
+      <c r="AA160" s="127" t="n">
         <f aca="false">+AA156-AA153</f>
         <v>4654.423</v>
       </c>
-      <c r="AI160" s="126" t="n">
+      <c r="AI160" s="127" t="n">
         <f aca="false">+AI156-AI153</f>
         <v>-235.406</v>
       </c>
-      <c r="AJ160" s="126" t="n">
+      <c r="AJ160" s="127" t="n">
         <f aca="false">+AJ156-AJ153</f>
         <v>425.608</v>
       </c>
-      <c r="AK160" s="126" t="n">
+      <c r="AK160" s="127" t="n">
         <f aca="false">+AK156-AK153</f>
         <v>-35.746</v>
       </c>
-      <c r="AL160" s="126" t="n">
+      <c r="AL160" s="127" t="n">
         <f aca="false">+AL156-AL153</f>
         <v>5875.357</v>
       </c>
-      <c r="AM160" s="126" t="n">
+      <c r="AM160" s="127" t="n">
         <f aca="false">+AM156-AM153</f>
         <v>5430.859</v>
       </c>
-      <c r="AN160" s="126" t="n">
+      <c r="AN160" s="127" t="n">
         <f aca="false">+AN156-AN153</f>
         <v>8460.202</v>
       </c>
-      <c r="DO160" s="138"/>
+      <c r="DO160" s="139"/>
     </row>
     <row r="161" s="53" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="AJ161" s="53" t="n">
@@ -33783,370 +33787,370 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="140" t="s">
         <v>190</v>
       </c>
-      <c r="B4" s="140" t="n">
+      <c r="B4" s="141" t="n">
         <v>4375</v>
       </c>
-      <c r="C4" s="139" t="s">
+      <c r="C4" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="139" t="s">
+      <c r="D4" s="140" t="s">
         <v>192</v>
       </c>
-      <c r="E4" s="141" t="n">
+      <c r="E4" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="139" t="s">
+      <c r="F4" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G4" s="139" t="s">
+      <c r="G4" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="140" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="140" t="n">
+      <c r="B5" s="141" t="n">
         <v>3625</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="C5" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D5" s="139" t="s">
+      <c r="D5" s="140" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="141" t="n">
+      <c r="E5" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="139" t="s">
+      <c r="F5" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G5" s="139" t="s">
+      <c r="G5" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="140" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="140" t="n">
+      <c r="B6" s="141" t="n">
         <v>4875</v>
       </c>
-      <c r="C6" s="139" t="s">
+      <c r="C6" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="139" t="s">
+      <c r="D6" s="140" t="s">
         <v>199</v>
       </c>
-      <c r="E6" s="141" t="n">
+      <c r="E6" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="139" t="s">
+      <c r="F6" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G6" s="139" t="s">
+      <c r="G6" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="140" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="140" t="n">
+      <c r="B7" s="141" t="n">
         <v>5875</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="C7" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="139" t="s">
+      <c r="D7" s="140" t="s">
         <v>201</v>
       </c>
-      <c r="E7" s="141" t="n">
+      <c r="E7" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="139" t="s">
+      <c r="F7" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G7" s="139" t="s">
+      <c r="G7" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="139" t="s">
+      <c r="A8" s="140" t="s">
         <v>202</v>
       </c>
-      <c r="B8" s="140" t="n">
+      <c r="B8" s="141" t="n">
         <v>6375</v>
       </c>
-      <c r="C8" s="139" t="s">
+      <c r="C8" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="D8" s="140" t="s">
         <v>203</v>
       </c>
-      <c r="E8" s="141" t="n">
+      <c r="E8" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="139" t="s">
+      <c r="F8" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G8" s="139" t="s">
+      <c r="G8" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="140" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="140" t="n">
+      <c r="B9" s="141" t="n">
         <v>4625</v>
       </c>
-      <c r="C9" s="139" t="s">
+      <c r="C9" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="D9" s="140" t="s">
         <v>203</v>
       </c>
-      <c r="E9" s="141" t="n">
+      <c r="E9" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="139" t="s">
+      <c r="F9" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G9" s="139" t="s">
+      <c r="G9" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="140" t="s">
         <v>205</v>
       </c>
-      <c r="B10" s="140" t="n">
+      <c r="B10" s="141" t="n">
         <v>5375</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="C10" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="139" t="s">
+      <c r="D10" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="E10" s="141" t="n">
+      <c r="E10" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="139" t="s">
+      <c r="F10" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="139" t="s">
+      <c r="G10" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="139" t="s">
+      <c r="A11" s="140" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="140" t="n">
+      <c r="B11" s="141" t="n">
         <v>5375</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="C11" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="D11" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="E11" s="141" t="n">
+      <c r="E11" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="139" t="s">
+      <c r="F11" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G11" s="139" t="s">
+      <c r="G11" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="139" t="s">
+      <c r="A12" s="140" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="140" t="n">
+      <c r="B12" s="141" t="n">
         <v>3875</v>
       </c>
-      <c r="C12" s="139" t="s">
+      <c r="C12" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D12" s="139" t="s">
+      <c r="D12" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="E12" s="141" t="n">
+      <c r="E12" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="139" t="s">
+      <c r="F12" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="139" t="s">
+      <c r="G12" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="139" t="s">
+      <c r="A13" s="140" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="140" t="n">
+      <c r="B13" s="141" t="n">
         <v>3875</v>
       </c>
-      <c r="C13" s="139" t="s">
+      <c r="C13" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D13" s="139" t="s">
+      <c r="D13" s="140" t="s">
         <v>206</v>
       </c>
-      <c r="E13" s="141" t="n">
+      <c r="E13" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="139" t="s">
+      <c r="F13" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G13" s="139" t="s">
+      <c r="G13" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="139" t="s">
+      <c r="A14" s="140" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="140" t="n">
+      <c r="B14" s="141" t="n">
         <v>4875</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="C14" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="139" t="s">
+      <c r="D14" s="140" t="s">
         <v>211</v>
       </c>
-      <c r="E14" s="141" t="n">
+      <c r="E14" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="139" t="s">
+      <c r="F14" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G14" s="139" t="s">
+      <c r="G14" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="139" t="s">
+      <c r="A15" s="140" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="140" t="n">
+      <c r="B15" s="141" t="n">
         <v>4875</v>
       </c>
-      <c r="C15" s="139" t="s">
+      <c r="C15" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="139" t="s">
+      <c r="D15" s="140" t="s">
         <v>211</v>
       </c>
-      <c r="E15" s="141" t="n">
+      <c r="E15" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="139" t="s">
+      <c r="F15" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G15" s="139" t="s">
+      <c r="G15" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="139" t="s">
+      <c r="A16" s="140" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="140" t="n">
+      <c r="B16" s="141" t="n">
         <v>3625</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="C16" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="D16" s="140" t="s">
         <v>211</v>
       </c>
-      <c r="E16" s="141" t="n">
+      <c r="E16" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="139" t="s">
+      <c r="F16" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G16" s="139" t="s">
+      <c r="G16" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="140" t="s">
         <v>214</v>
       </c>
-      <c r="B17" s="140" t="n">
+      <c r="B17" s="141" t="n">
         <v>3625</v>
       </c>
-      <c r="C17" s="139" t="s">
+      <c r="C17" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="139" t="s">
+      <c r="D17" s="140" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="141" t="n">
+      <c r="E17" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="139" t="s">
+      <c r="F17" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="G17" s="139" t="s">
+      <c r="G17" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="139" t="s">
+      <c r="A18" s="140" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="140" t="n">
+      <c r="B18" s="141" t="n">
         <v>4900</v>
       </c>
-      <c r="C18" s="139" t="s">
+      <c r="C18" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D18" s="139" t="s">
+      <c r="D18" s="140" t="s">
         <v>216</v>
       </c>
-      <c r="E18" s="141" t="n">
+      <c r="E18" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="139" t="s">
+      <c r="F18" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="139" t="s">
+      <c r="G18" s="140" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="139" t="s">
+      <c r="A19" s="140" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="140" t="n">
+      <c r="B19" s="141" t="n">
         <v>5400</v>
       </c>
-      <c r="C19" s="139" t="s">
+      <c r="C19" s="140" t="s">
         <v>191</v>
       </c>
-      <c r="D19" s="139" t="s">
+      <c r="D19" s="140" t="s">
         <v>218</v>
       </c>
-      <c r="E19" s="141" t="n">
+      <c r="E19" s="142" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="139" t="s">
+      <c r="F19" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="G19" s="139" t="s">
+      <c r="G19" s="140" t="s">
         <v>194</v>
       </c>
     </row>
